--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747579772848891</v>
+        <v>9.747668997766535</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.721450582098282</v>
+        <v>9.721646329747106</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.71751888523821</v>
+        <v>9.717787193329418</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.694873383364131</v>
+        <v>9.695301961597201</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.699439015100703</v>
+        <v>9.699863471683372</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.692752218192012</v>
+        <v>9.693171442893609</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.688545840167517</v>
+        <v>9.688967900233635</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.702458721499729</v>
+        <v>9.702893225810087</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.714135640599709</v>
+        <v>9.71463905047975</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.722369532343219</v>
+        <v>9.722756423694985</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.730964092955261</v>
+        <v>9.731355743084258</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.707455225788637</v>
+        <v>9.707838527299014</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.663098910715643</v>
+        <v>9.663476337217087</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.627806110163403</v>
+        <v>9.628276748919827</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.596588203873432</v>
+        <v>9.596898789456016</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.559181301890664</v>
+        <v>9.559460212078591</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.497167740282748</v>
+        <v>9.497781261328717</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.422715219414634</v>
+        <v>9.423554296558613</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.347483638409267</v>
+        <v>9.348270816817005</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.279612663630655</v>
+        <v>9.280427837929889</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.260357335798195</v>
+        <v>9.260849653296992</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.274925140115359</v>
+        <v>9.275249409071495</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.244296336183737</v>
+        <v>9.243826047820708</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.180333015927076</v>
+        <v>9.179432177320628</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.121355369953026</v>
+        <v>9.120004948890516</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.029996380857904</v>
+        <v>9.028387873362504</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.963244862196722</v>
+        <v>8.961287231526105</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.965319400415385</v>
+        <v>8.962925134862154</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.978323325885736</v>
+        <v>8.975696059047984</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.114678222206457</v>
+        <v>9.111095916544606</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.170378505471767</v>
+        <v>9.166638002996148</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.325835730230121</v>
+        <v>9.323065160418503</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.411299229334851</v>
+        <v>9.409186304087463</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.425528299035289</v>
+        <v>9.423876251157111</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.505454806967425</v>
+        <v>9.504167864798436</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.599543539678125</v>
+        <v>9.600385150316546</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.581577043647314</v>
+        <v>9.583247303752406</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.584418196815784</v>
+        <v>9.587323766895459</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.564005557731106</v>
+        <v>9.568376783762488</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.538373846590822</v>
+        <v>9.543293055532242</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.56731904805082</v>
+        <v>9.572754285124098</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.4437180359566</v>
+        <v>9.448262581612624</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.379206005302564</v>
+        <v>9.383380347041072</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.255089414666555</v>
+        <v>9.257272757256946</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.178724903722353</v>
+        <v>9.170599726988842</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.081707516981103</v>
+        <v>9.082255217392207</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049651250590111</v>
+        <v>9.052433486113488</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.054219184481553</v>
+        <v>9.048591709112083</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024914324132773</v>
+        <v>9.018485517149566</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.010641320483412</v>
+        <v>9.000828618807097</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.049782966462281</v>
+        <v>9.023429911346621</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.123433637665897</v>
+        <v>9.067102362333415</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.192793584325447</v>
+        <v>9.098450680006538</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.208091006532266</v>
+        <v>9.065282966436181</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.211923341901429</v>
+        <v>9.020854298687334</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.20947809741555</v>
+        <v>8.968498810280916</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.198681777856336</v>
+        <v>8.891253795452062</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.166461699093574</v>
+        <v>8.794606649609952</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,15 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.075060000000001</v>
+        <v>8.598581527990833</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>8.804276033304522</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747668997766535</v>
+        <v>9.747710266456114</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.721646329747106</v>
+        <v>9.721736881910106</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.717787193329418</v>
+        <v>9.717911361444799</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.695301961597201</v>
+        <v>9.695500256624992</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.699863471683372</v>
+        <v>9.700059852368669</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.693171442893609</v>
+        <v>9.69336540017407</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.688967900233635</v>
+        <v>9.689163146312277</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.702893225810087</v>
+        <v>9.703094173077723</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71463905047975</v>
+        <v>9.714872039120152</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.722756423694985</v>
+        <v>9.722935526120374</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.731355743084258</v>
+        <v>9.731537048920375</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.707838527299014</v>
+        <v>9.708015974913625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.663476337217087</v>
+        <v>9.663651277935447</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.628276748919827</v>
+        <v>9.628494910278569</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.596898789456016</v>
+        <v>9.597042876482149</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.559460212078591</v>
+        <v>9.55958936731618</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.497781261328717</v>
+        <v>9.498065202703838</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.423554296558613</v>
+        <v>9.423943128914098</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.348270816817005</v>
+        <v>9.348635486836072</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.280427837929889</v>
+        <v>9.280805757068379</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.260849653296992</v>
+        <v>9.26108001166307</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.275249409071495</v>
+        <v>9.275402890849266</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.243826047820708</v>
+        <v>9.243610967706434</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.179432177320628</v>
+        <v>9.179018170665151</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.120004948890516</v>
+        <v>9.11938331814007</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.028387873362504</v>
+        <v>9.02764694937694</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.961287231526105</v>
+        <v>8.960384882086871</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.962925134862154</v>
+        <v>8.961820367043241</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.975696059047984</v>
+        <v>8.974480229089229</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.111095916544606</v>
+        <v>9.109435505973252</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.166638002996148</v>
+        <v>9.164904120441612</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.323065160418503</v>
+        <v>9.321775712292313</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.409186304087463</v>
+        <v>9.408201047243328</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.423876251157111</v>
+        <v>9.423101463831367</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.504167864798436</v>
+        <v>9.503559762463688</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.600385150316546</v>
+        <v>9.600764853222582</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.583247303752406</v>
+        <v>9.584009292446989</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.587323766895459</v>
+        <v>9.588660563252489</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.568376783762488</v>
+        <v>9.570399799984724</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.543293055532242</v>
+        <v>9.545572836013179</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.572754285124098</v>
+        <v>9.575275752058547</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.448262581612624</v>
+        <v>9.450379022042789</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.383380347041072</v>
+        <v>9.38532946200732</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.257272757256946</v>
+        <v>9.258297497285948</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.170599726988842</v>
+        <v>9.171211339292793</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.082255217392207</v>
+        <v>9.081988809701311</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052433486113488</v>
+        <v>9.056574868015426</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048591709112083</v>
+        <v>9.0514511906322</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.018485517149566</v>
+        <v>9.023866886741779</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000828618807097</v>
+        <v>9.00288055644593</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.023429911346621</v>
+        <v>9.020691273261864</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.067102362333415</v>
+        <v>9.058700193798588</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.098450680006538</v>
+        <v>9.085126340868774</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.065282966436181</v>
+        <v>9.05639174680328</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.020854298687334</v>
+        <v>9.021705474999141</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.968498810280916</v>
+        <v>8.983895984014293</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.891253795452062</v>
+        <v>8.929601116795435</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.794606649609952</v>
+        <v>8.864861732230423</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.598581527990833</v>
+        <v>8.732230390478115</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,15 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.804276033304522</v>
+        <v>8.926304553747171</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>9.006767086451315</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.0514511906322</v>
+        <v>9.051478423469501</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023866886741779</v>
+        <v>9.023945852119223</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.00288055644593</v>
+        <v>9.002996760709593</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.020691273261864</v>
+        <v>9.020957098311275</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.058700193798588</v>
+        <v>9.058921332258201</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.085126340868774</v>
+        <v>9.085311312434495</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.05639174680328</v>
+        <v>9.056587402567782</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.021705474999141</v>
+        <v>9.022041016376377</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.983895984014293</v>
+        <v>8.985686481278881</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.929601116795435</v>
+        <v>8.933149497923248</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.864861732230423</v>
+        <v>8.870326761590819</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.732230390478115</v>
+        <v>8.741588321814159</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.926304553747171</v>
+        <v>8.938291979801157</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.006767086451315</v>
+        <v>9.020685297091269</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.938291979801157</v>
+        <v>8.872602071814159</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,15 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.020685297091269</v>
+        <v>9.003615821814158</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>8.983796299211996</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747710266456114</v>
+        <v>9.747749523266663</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.721736881910106</v>
+        <v>9.72182302778582</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.717911361444799</v>
+        <v>9.718029516531436</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.695500256624992</v>
+        <v>9.695688923266413</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.700059852368669</v>
+        <v>9.700246693310383</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69336540017407</v>
+        <v>9.693549933781931</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.689163146312277</v>
+        <v>9.689348892591953</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.703094173077723</v>
+        <v>9.703285310540064</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.714872039120152</v>
+        <v>9.715093755242281</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.722935526120374</v>
+        <v>9.723105987666465</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.731537048920375</v>
+        <v>9.731709607824417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708015974913625</v>
+        <v>9.708184865604226</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.663651277935447</v>
+        <v>9.663817907180634</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.628494910278569</v>
+        <v>9.628702715822463</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597042876482149</v>
+        <v>9.597180192736829</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.55958936731618</v>
+        <v>9.559712314797427</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.498065202703838</v>
+        <v>9.498335399976664</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.423943128914098</v>
+        <v>9.424313432245835</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.348635486836072</v>
+        <v>9.348982714068477</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.280805757068379</v>
+        <v>9.281165765645824</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26108001166307</v>
+        <v>9.26130069305972</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.275402890849266</v>
+        <v>9.275550945516608</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.243610967706434</v>
+        <v>9.243407815203991</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.179018170665151</v>
+        <v>9.178625923883239</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.11938331814007</v>
+        <v>9.11879376660338</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.02764694937694</v>
+        <v>9.02694397621393</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.960384882086871</v>
+        <v>8.959528396508084</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.961820367043241</v>
+        <v>8.960771076132273</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.974480229089229</v>
+        <v>8.973323332618179</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.109435505973252</v>
+        <v>9.107854045152306</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.164904120441612</v>
+        <v>9.163252595560763</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.321775712292313</v>
+        <v>9.320544477402466</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.408201047243328</v>
+        <v>9.407259176323517</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.423101463831367</v>
+        <v>9.422358209701027</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.503559762463688</v>
+        <v>9.502973772062095</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.600764853222582</v>
+        <v>9.601120395649692</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.584009292446989</v>
+        <v>9.584727871341684</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.588660563252489</v>
+        <v>9.589927916917553</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.570399799984724</v>
+        <v>9.572324805044296</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.545572836013179</v>
+        <v>9.547744001280503</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.575275752058547</v>
+        <v>9.577678608661429</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.450379022042789</v>
+        <v>9.452400720045548</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.38532946200732</v>
+        <v>9.387194295568161</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.258297497285948</v>
+        <v>9.259281015195995</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.171211339292793</v>
+        <v>9.171799892387142</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.081988809701311</v>
+        <v>9.081736301816887</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.056574868015426</v>
+        <v>9.060154243584341</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.051478423469501</v>
+        <v>9.054645701445072</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023945852119223</v>
+        <v>9.030507008386149</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002996760709593</v>
+        <v>9.010468002767904</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.020957098311275</v>
+        <v>9.026947005643112</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.058921332258201</v>
+        <v>9.06196675885009</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.085311312434495</v>
+        <v>9.083821169753222</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.056587402567782</v>
+        <v>9.05674632407149</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.022041016376377</v>
+        <v>9.026490388454073</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.985686481278881</v>
+        <v>8.997294546049076</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.933149497923248</v>
+        <v>8.956169852553385</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.870326761590819</v>
+        <v>8.909118797751216</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.741588321814159</v>
+        <v>8.813130049360364</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.872602071814159</v>
+        <v>8.964402589652455</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.003615821814158</v>
+        <v>8.999296748122653</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,15 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.983796299211996</v>
+        <v>8.973794920265242</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>8.954794018221637</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747749523266663</v>
+        <v>9.747786911791092</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72182302778582</v>
+        <v>9.721905081231455</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718029516531436</v>
+        <v>9.718142084752511</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.695688923266413</v>
+        <v>9.695868645525353</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.700246693310383</v>
+        <v>9.700424672512796</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.693549933781931</v>
+        <v>9.693725713582893</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.689348892591953</v>
+        <v>9.689525815289429</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.703285310540064</v>
+        <v>9.703467338754601</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.715093755242281</v>
+        <v>9.715304996261606</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.723105987666465</v>
+        <v>9.723268418147148</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.731709607824417</v>
+        <v>9.731874037071346</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708184865604226</v>
+        <v>9.708345802968683</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.663817907180634</v>
+        <v>9.663976802256915</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.628702715822463</v>
+        <v>9.628900884058426</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597180192736829</v>
+        <v>9.597311203169305</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.559712314797427</v>
+        <v>9.559829490859094</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.498335399976664</v>
+        <v>9.498592825165741</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.424313432245835</v>
+        <v>9.424666494936091</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.348982714068477</v>
+        <v>9.34931371639653</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.281165765645824</v>
+        <v>9.281509103668023</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26130069305972</v>
+        <v>9.261512278490835</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.275550945516608</v>
+        <v>9.275693817705118</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.243407815203991</v>
+        <v>9.243215644846028</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.178625923883239</v>
+        <v>9.178253786158114</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.11879376660338</v>
+        <v>9.11823389974395</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.02694397621393</v>
+        <v>9.026276142783907</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.959528396508084</v>
+        <v>8.958714403861009</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.960771076132273</v>
+        <v>8.959773233918167</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.973323332618179</v>
+        <v>8.972221215827922</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.107854045152306</v>
+        <v>9.106346077920209</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.163252595560763</v>
+        <v>9.161677743272637</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.320544477402466</v>
+        <v>9.319367652669406</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.407259176323517</v>
+        <v>9.406357942301547</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.422358209701027</v>
+        <v>9.421644691404783</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.502973772062095</v>
+        <v>9.502408851330491</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.601120395649692</v>
+        <v>9.601453873279311</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.584727871341684</v>
+        <v>9.585406530994614</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.589927916917553</v>
+        <v>9.591131016155803</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.572324805044296</v>
+        <v>9.574158686640594</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.547744001280503</v>
+        <v>9.549814043967075</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.577678608661429</v>
+        <v>9.579970948834681</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.452400720045548</v>
+        <v>9.454333809115848</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.387194295568161</v>
+        <v>9.38898008169156</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.259281015195995</v>
+        <v>9.260225639219295</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.171799892387142</v>
+        <v>9.172366583122731</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.081736301816887</v>
+        <v>9.081496667674148</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.060154243584341</v>
+        <v>9.059702833486551</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.054645701445072</v>
+        <v>9.054622000753735</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.030507008386149</v>
+        <v>9.029957729011297</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.010468002767904</v>
+        <v>9.011403180826015</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.026947005643112</v>
+        <v>9.022954533189651</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.06196675885009</v>
+        <v>9.049894264552075</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.083821169753222</v>
+        <v>9.065352282714453</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.05674632407149</v>
+        <v>9.037421192859766</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.026490388454073</v>
+        <v>9.005539312269011</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.997294546049076</v>
+        <v>8.975485376894902</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.956169852553385</v>
+        <v>8.933261366264869</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.909118797751216</v>
+        <v>8.890574288194319</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.813130049360364</v>
+        <v>8.805085159547165</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.964402589652455</v>
+        <v>8.893388944812083</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.999296748122653</v>
+        <v>8.869112202058915</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.973794920265242</v>
+        <v>8.824750884066376</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.954794018221637</v>
+        <v>8.718943172019117</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747786911791092</v>
+        <v>9.747822562277484</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.721905081231455</v>
+        <v>9.721983326998375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718142084752511</v>
+        <v>9.71824945295554</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.695868645525353</v>
+        <v>9.696040044172637</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.700424672512796</v>
+        <v>9.700594405274966</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.693725713582893</v>
+        <v>9.69389334748046</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.689525815289429</v>
+        <v>9.689694527986555</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.703467338754601</v>
+        <v>9.703640893182657</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.715304996261606</v>
+        <v>9.715506486234398</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.723268418147148</v>
+        <v>9.723423371383149</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.731874037071346</v>
+        <v>9.732030897260545</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708345802968683</v>
+        <v>9.708499335209275</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.663976802256915</v>
+        <v>9.664128488328148</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.628900884058426</v>
+        <v>9.629090068685512</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597311203169305</v>
+        <v>9.597436331232188</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.559829490859094</v>
+        <v>9.55994129194508</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.498592825165741</v>
+        <v>9.498838360948657</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.424666494936091</v>
+        <v>9.42500348909862</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.34931371639653</v>
+        <v>9.34962960129549</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.281509103668023</v>
+        <v>9.281836899598893</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.261512278490835</v>
+        <v>9.26171530500951</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.275693817705118</v>
+        <v>9.275831742160285</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.243215644846028</v>
+        <v>9.243033606979612</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.178253786158114</v>
+        <v>9.177900267847885</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.11823389974395</v>
+        <v>9.117701553384858</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.026276142783907</v>
+        <v>9.025640906272965</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.958714403861009</v>
+        <v>8.957939852375343</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.959773233918167</v>
+        <v>8.958823188868728</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.972221215827922</v>
+        <v>8.971170103699915</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.106346077920209</v>
+        <v>9.104906635638478</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.161677743272637</v>
+        <v>9.160174385810507</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.319367652669406</v>
+        <v>9.31824175438703</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.406357942301547</v>
+        <v>9.405494818292198</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.421644691404783</v>
+        <v>9.420959236311333</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.502408851330491</v>
+        <v>9.501864005898568</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.601453873279311</v>
+        <v>9.601767155622618</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.585406530994614</v>
+        <v>9.586048406235982</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.591131016155803</v>
+        <v>9.592274552006103</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.574158686640594</v>
+        <v>9.575907707728053</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.549814043967075</v>
+        <v>9.551789790973846</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.579970948834681</v>
+        <v>9.582160153917842</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.454333809115848</v>
+        <v>9.456183912811962</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.38898008169156</v>
+        <v>9.390691640960814</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.260225639219295</v>
+        <v>9.261133536744996</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.172366583122731</v>
+        <v>9.172912535442567</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.081496667674148</v>
+        <v>9.081268977083589</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.059702833486551</v>
+        <v>9.059270790923787</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.054622000753735</v>
+        <v>9.054286406019699</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.029957729011297</v>
+        <v>9.032569970354752</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.011403180826015</v>
+        <v>9.01549663693924</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.022954533189651</v>
+        <v>9.026711731311885</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.049894264552075</v>
+        <v>9.052249199809676</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.065352282714453</v>
+        <v>9.066828426280287</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.037421192859766</v>
+        <v>9.040129070986513</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.005539312269011</v>
+        <v>9.01193611412755</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.975485376894902</v>
+        <v>8.987628336813172</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.933261366264869</v>
+        <v>8.953243946585877</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.890574288194319</v>
+        <v>8.920594799936758</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.805085159547165</v>
+        <v>8.851413520908119</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.893388944812083</v>
+        <v>8.929759150963488</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.869112202058915</v>
+        <v>8.899498393316</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.824750884066376</v>
+        <v>8.848686590296248</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.718943172019117</v>
+        <v>8.773650390702706</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45142</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45170</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45205</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45233</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45261</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45296</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45324</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45352</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45387</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45415</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45443</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45478</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45506</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45541</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45569</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45597</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45632</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45660</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45688</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45716</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45751</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45779</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45814</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45821</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45828</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45835</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45842</v>
       </c>
       <c r="B41">
@@ -692,507 +718,515 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747822562277484</v>
+        <v>9.747856593143876</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.721983326998375</v>
+        <v>9.722058024028446</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.71824945295554</v>
+        <v>9.718351973101104</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696040044172637</v>
+        <v>9.696203683881754</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.700594405274966</v>
+        <v>9.700756451269847</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69389334748046</v>
+        <v>9.694053388412197</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.689694527986555</v>
+        <v>9.689855588711957</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.703640893182657</v>
+        <v>9.703806551572315</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.715506486234398</v>
+        <v>9.715698884090898</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.723423371383149</v>
+        <v>9.72357135147678</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732030897260545</v>
+        <v>9.732180698666673</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708499335209275</v>
+        <v>9.708645961337451</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.664128488328148</v>
+        <v>9.664273444161591</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.629090068685512</v>
+        <v>9.629270865723289</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597436331232188</v>
+        <v>9.597555963396365</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.55994129194508</v>
+        <v>9.560048079056688</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.498838360948657</v>
+        <v>9.499072810673479</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.42500348909862</v>
+        <v>9.425325483352609</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.34962960129549</v>
+        <v>9.349931378023978</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.281836899598893</v>
+        <v>9.282150182588349</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26171530500951</v>
+        <v>9.261910269586998</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.275831742160285</v>
+        <v>9.275964943456467</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.243033606979612</v>
+        <v>9.242860936077518</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.177900267847885</v>
+        <v>9.177564021455275</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.117701553384858</v>
+        <v>9.117194766881394</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.025640906272965</v>
+        <v>9.025035961160619</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.957939852375343</v>
+        <v>8.957201972882171</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.958823188868728</v>
+        <v>8.95791762353751</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.971170103699915</v>
+        <v>8.970166558071737</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.104906635638478</v>
+        <v>9.103531184358808</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.160174385810507</v>
+        <v>9.158737797825715</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.31824175438703</v>
+        <v>9.317163585943783</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.405494818292198</v>
+        <v>9.404667478193332</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.420959236311333</v>
+        <v>9.420300287128638</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.501864005898568</v>
+        <v>9.501338289250629</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.601767155622618</v>
+        <v>9.602061914898087</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.586048406235982</v>
+        <v>9.58665631952506</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.592274552006103</v>
+        <v>9.59336277573</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.575907707728053</v>
+        <v>9.577577575143145</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.551789790973846</v>
+        <v>9.553677474927053</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.582160153917842</v>
+        <v>9.584252968580149</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.456183912811962</v>
+        <v>9.457956195710567</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.390691640960814</v>
+        <v>9.392333419258454</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.261133536744996</v>
+        <v>9.262006726506751</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.172912535442567</v>
+        <v>9.173438804717685</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.081268977083589</v>
+        <v>9.081052385060378</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.059270790923787</v>
+        <v>9.058856922203073</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.054286406019699</v>
+        <v>9.053964476538525</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.032569970354752</v>
+        <v>9.032106654317392</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.01549663693924</v>
+        <v>9.01167366464421</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.026711731311885</v>
+        <v>9.020277414121368</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.052249199809676</v>
+        <v>9.043355616322081</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.066828426280287</v>
+        <v>9.053637251048725</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.040129070986513</v>
+        <v>9.026584980296299</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.01193611412755</v>
+        <v>8.999105235121995</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.987628336813172</v>
+        <v>8.971643583352584</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.953243946585877</v>
+        <v>8.939267642940088</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.920594799936758</v>
+        <v>8.911279737406002</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.851413520908119</v>
+        <v>8.849360473857471</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.929759150963488</v>
+        <v>8.909163575371126</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.899498393316</v>
+        <v>8.876626294421683</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.848686590296248</v>
+        <v>8.821937217465946</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.773650390702706</v>
+        <v>8.7439429814238</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>8.612621025351487</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747856593143876</v>
+        <v>9.747889112291334</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722058024028446</v>
+        <v>9.722129408312455</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718351973101104</v>
+        <v>9.718449966106533</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696203683881754</v>
+        <v>9.696360079420398</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.700756451269847</v>
+        <v>9.700911320686307</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694053388412197</v>
+        <v>9.694206340419758</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.689855588711957</v>
+        <v>9.690009506083914</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.703806551572315</v>
+        <v>9.703964840359623</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.715698884090898</v>
+        <v>9.715882790785706</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72357135147678</v>
+        <v>9.723712818262371</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732180698666673</v>
+        <v>9.732323906756271</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708645961337451</v>
+        <v>9.708786136563862</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.664273444161591</v>
+        <v>9.664412107130389</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.629270865723289</v>
+        <v>9.629443819721846</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597555963396365</v>
+        <v>9.597670453090787</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560048079056688</v>
+        <v>9.560150181621042</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.499072810673479</v>
+        <v>9.49929690705636</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.425325483352609</v>
+        <v>9.425633453955543</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.349931378023978</v>
+        <v>9.350219968239754</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.282150182588349</v>
+        <v>9.282449893131126</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.261910269586998</v>
+        <v>9.262097632612505</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.275964943456467</v>
+        <v>9.276093635929954</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.242860936077518</v>
+        <v>9.242696940702704</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.177564021455275</v>
+        <v>9.177243825210926</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.117194766881394</v>
+        <v>9.116711759930276</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.025035961160619</v>
+        <v>9.024459212400483</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.957201972882171</v>
+        <v>8.956498247127016</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.95791762353751</v>
+        <v>8.957053517568729</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.970166558071737</v>
+        <v>8.969207441118389</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.103531184358808</v>
+        <v>9.102215578659479</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.158737797825715</v>
+        <v>9.157363658409512</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.317163585943783</v>
+        <v>9.316130209304854</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.404667478193332</v>
+        <v>9.403873777653999</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.420300287128638</v>
+        <v>9.41966639314</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.501338289250629</v>
+        <v>9.500830802002358</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.602061914898087</v>
+        <v>9.602339650685227</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.58665631952506</v>
+        <v>9.587232818212708</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.59336277573</v>
+        <v>9.594399548563835</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.577577575143145</v>
+        <v>9.579173499461469</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.553677474927053</v>
+        <v>9.555482796739511</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.584252968580149</v>
+        <v>9.586255567325425</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.457956195710567</v>
+        <v>9.459655408503727</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.392333419258454</v>
+        <v>9.393909522377982</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.262006726506751</v>
+        <v>9.262847089917809</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.173438804717685</v>
+        <v>9.17394638197373</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.081052385060378</v>
+        <v>9.080846122514194</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.058856922203073</v>
+        <v>9.05846012737355</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.053964476538525</v>
+        <v>9.05365541871592</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.032106654317392</v>
+        <v>9.031660850186389</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.01167366464421</v>
+        <v>9.0112450126677</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.020277414121368</v>
+        <v>9.017020132396876</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.043355616322081</v>
+        <v>9.036937933492666</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.053637251048725</v>
+        <v>9.045778764485595</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.026584980296299</v>
+        <v>9.018590220245169</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>8.999105235121995</v>
+        <v>8.991109080880415</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.971643583352584</v>
+        <v>8.963933727434032</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.939267642940088</v>
+        <v>8.934167224429379</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.911279737406002</v>
+        <v>8.904589497072397</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.849360473857471</v>
+        <v>8.847588925920842</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.909163575371126</v>
+        <v>8.894309130013056</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.876626294421683</v>
+        <v>8.862289397792146</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.821937217465946</v>
+        <v>8.813101405300275</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.7439429814238</v>
+        <v>8.736568787376218</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,15 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.612621025351487</v>
+        <v>8.63888483976211</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>8.624941523447431</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747889112291334</v>
+        <v>9.747920218245969</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722129408312455</v>
+        <v>9.722197695377004</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718449966106533</v>
+        <v>9.718543725192616</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696360079420398</v>
+        <v>9.696509701040299</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.700911320686307</v>
+        <v>9.701059479575573</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694206340419758</v>
+        <v>9.694352663932502</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.690009506083914</v>
+        <v>9.690156744656406</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.703964840359623</v>
+        <v>9.704116240236957</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.715882790785706</v>
+        <v>9.716058755527696</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.723712818262371</v>
+        <v>9.723848192055868</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732323906756271</v>
+        <v>9.732460946995097</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708786136563862</v>
+        <v>9.708920276995681</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.664412107130389</v>
+        <v>9.664544877583864</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.629443819721846</v>
+        <v>9.629609429188244</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597670453090787</v>
+        <v>9.597780124150514</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560150181621042</v>
+        <v>9.560247900864365</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.49929690705636</v>
+        <v>9.499511319761703</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.425633453955543</v>
+        <v>9.425928294534788</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.350219968239754</v>
+        <v>9.350496215272361</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.282449893131126</v>
+        <v>9.282736892385726</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.262097632612505</v>
+        <v>9.26227782105822</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276093635929954</v>
+        <v>9.276218023770719</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.242696940702704</v>
+        <v>9.242540994861749</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.177243825210926</v>
+        <v>9.176938568863699</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.116711759930276</v>
+        <v>9.116250912456787</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.024459212400483</v>
+        <v>9.023908752130318</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.956498247127016</v>
+        <v>8.955826380218411</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.957053517568729</v>
+        <v>8.956228115467862</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.969207441118389</v>
+        <v>8.968289883454236</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.102215578659479</v>
+        <v>9.100956021197376</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.157363658409512</v>
+        <v>9.156048009045573</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.316130209304854</v>
+        <v>9.315138919765996</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.403873777653999</v>
+        <v>9.403111737093859</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.41966639314</v>
+        <v>9.419056202063949</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.500830802002358</v>
+        <v>9.500340690696241</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.602339650685227</v>
+        <v>9.602601711046564</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.587232818212708</v>
+        <v>9.587780206672992</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.594399548563835</v>
+        <v>9.595388384938332</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.579173499461469</v>
+        <v>9.580700247353025</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.555482796739511</v>
+        <v>9.557210980524516</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.586255567325425</v>
+        <v>9.588173612920272</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.459655408503727</v>
+        <v>9.461285927987674</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.393909522377982</v>
+        <v>9.395423747022427</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.262847089917809</v>
+        <v>9.263656381572616</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.17394638197373</v>
+        <v>9.174436197962443</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.080846122514194</v>
+        <v>9.08064948810628</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05846012737355</v>
+        <v>9.058079391468077</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.05365541871592</v>
+        <v>9.053358497036397</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.031660850186389</v>
+        <v>9.031231615925481</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.0112450126677</v>
+        <v>9.010831256923833</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.017020132396876</v>
+        <v>9.016843825926564</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.036937933492666</v>
+        <v>9.037052879293508</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.045778764485595</v>
+        <v>9.049875455868708</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.018590220245169</v>
+        <v>9.025638401497801</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>8.991109080880415</v>
+        <v>9.001137551133299</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.963933727434032</v>
+        <v>8.977762098333082</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.934167224429379</v>
+        <v>8.952553220440691</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.904589497072397</v>
+        <v>8.928655926569967</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.847588925920842</v>
+        <v>8.880485994342731</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.894309130013056</v>
+        <v>8.926912184625625</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.862289397792146</v>
+        <v>8.903315513753665</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.813101405300275</v>
+        <v>8.85056138240995</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.736568787376218</v>
+        <v>8.787639293564531</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.63888483976211</v>
+        <v>8.773354811655667</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,15 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.624941523447431</v>
+        <v>8.829555052858469</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>8.966572552858469</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.025638401497801</v>
+        <v>9.025678918194034</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.001137551133299</v>
+        <v>9.000912682012986</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.977762098333082</v>
+        <v>8.976424241344574</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.952553220440691</v>
+        <v>8.949908828297509</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.928655926569967</v>
+        <v>8.924489773721339</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.880485994342731</v>
+        <v>8.874641793445406</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.926912184625625</v>
+        <v>8.919133407386351</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.903315513753665</v>
+        <v>8.893790517642596</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.85056138240995</v>
+        <v>8.837390016552394</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.787639293564531</v>
+        <v>8.7684677369372</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.773354811655667</v>
+        <v>8.732777021728673</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.829555052858469</v>
+        <v>8.77464921001847</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.966572552858469</v>
+        <v>8.904010563348113</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747920218245969</v>
+        <v>9.747950001155301</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722197695377004</v>
+        <v>9.722263082454987</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718543725192616</v>
+        <v>9.718633518806769</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696509701040299</v>
+        <v>9.696652979183881</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701059479575573</v>
+        <v>9.701201354519686</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694352663932502</v>
+        <v>9.694492780381063</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.690156744656406</v>
+        <v>9.690297729586307</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.704116240236957</v>
+        <v>9.704261191012236</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.716058755527696</v>
+        <v>9.716227281224612</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.723848192055868</v>
+        <v>9.723977857806428</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732460946995097</v>
+        <v>9.732592209050164</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.708920276995681</v>
+        <v>9.709048763742736</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.664544877583864</v>
+        <v>9.664672122676635</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.629609429188244</v>
+        <v>9.629768151342063</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597780124150514</v>
+        <v>9.597885273842955</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560247900864365</v>
+        <v>9.56034151276245</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.499511319761703</v>
+        <v>9.499716662028522</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.425928294534788</v>
+        <v>9.426210824618636</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.350496215272361</v>
+        <v>9.350760892246043</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.282736892385726</v>
+        <v>9.283011970345404</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26227782105822</v>
+        <v>9.262451231341759</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276218023770719</v>
+        <v>9.276338301227913</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.242540994861749</v>
+        <v>9.24239253052988</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.176938568863699</v>
+        <v>9.176647241341715</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.116250912456787</v>
+        <v>9.115810747116678</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.023908752130318</v>
+        <v>9.023382839385079</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.955826380218411</v>
+        <v>8.955184276600621</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.956228115467862</v>
+        <v>8.955438898443003</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.968289883454236</v>
+        <v>8.967411256191811</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.100956021197376</v>
+        <v>9.099749027173242</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.156048009045573</v>
+        <v>9.154787216662189</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.315138919765996</v>
+        <v>9.314187223558859</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.403111737093859</v>
+        <v>9.402379526532645</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.419056202063949</v>
+        <v>9.418468452520329</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.500340690696241</v>
+        <v>9.499867146268841</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.602601711046564</v>
+        <v>9.602849310684853</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.587780206672992</v>
+        <v>9.588300574099346</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.595388384938332</v>
+        <v>9.596332490134891</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.580700247353025</v>
+        <v>9.582162187500508</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.557210980524516</v>
+        <v>9.558866821917377</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.588173612920272</v>
+        <v>9.590012307853986</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.461285927987674</v>
+        <v>9.462851792589294</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.395423747022427</v>
+        <v>9.396879608597079</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.263656381572616</v>
+        <v>9.264436238948383</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.174436197962443</v>
+        <v>9.174909127049217</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.08064948810628</v>
+        <v>9.08046184111042</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.058079391468077</v>
+        <v>9.05771377667284</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.053358497036397</v>
+        <v>9.053073029096664</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.031231615925481</v>
+        <v>9.030818072957167</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.010831256923833</v>
+        <v>9.010431674455667</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.016843825926564</v>
+        <v>9.016672419342495</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037052879293508</v>
+        <v>9.03716206934268</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.049875455868708</v>
+        <v>9.053405596285783</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.025678918194034</v>
+        <v>9.031756387463538</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.000912682012986</v>
+        <v>9.009257080218678</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.976424241344574</v>
+        <v>8.986958825197735</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.949908828297509</v>
+        <v>8.963039800647371</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.924489773721339</v>
+        <v>8.94086531133032</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.874641793445406</v>
+        <v>8.896533204119427</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.919133407386351</v>
+        <v>8.938257731147244</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.893790517642596</v>
+        <v>8.917217022163221</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.837390016552394</v>
+        <v>8.855451152155737</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.7684677369372</v>
+        <v>8.79108845392714</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.732777021728673</v>
+        <v>8.779554679336645</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.77464921001847</v>
+        <v>8.824431357924894</v>
       </c>
     </row>
     <row r="107" spans="1:2">

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747950001155301</v>
+        <v>9.747978543660235</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722263082454987</v>
+        <v>9.722325750385641</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718633518806769</v>
+        <v>9.718719593183819</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696652979183881</v>
+        <v>9.696790308606502</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701201354519686</v>
+        <v>9.701337336720105</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694492780381063</v>
+        <v>9.694627076237754</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.690297729586307</v>
+        <v>9.690432850720066</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.704261191012236</v>
+        <v>9.704400095861999</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.716227281224612</v>
+        <v>9.716388829255299</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.723977857806428</v>
+        <v>9.72410216873593</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732592209050164</v>
+        <v>9.73271805047356</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709048763742736</v>
+        <v>9.709171946517447</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.664672122676635</v>
+        <v>9.66479417973304</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.629768151342063</v>
+        <v>9.629920406294708</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597885273842955</v>
+        <v>9.597986175531179</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56034151276245</v>
+        <v>9.560431270628772</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.499716662028522</v>
+        <v>9.499913496479955</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.426210824618636</v>
+        <v>9.426481797135494</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.350760892246043</v>
+        <v>9.351014709215471</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.283011970345404</v>
+        <v>9.283275853022388</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.262451231341759</v>
+        <v>9.262618231915717</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276338301227913</v>
+        <v>9.276454652894909</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24239253052988</v>
+        <v>9.242251031168019</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.176647241341715</v>
+        <v>9.176368920004835</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.115810747116678</v>
+        <v>9.115389914027121</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.023382839385079</v>
+        <v>9.022879882373774</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.955184276600621</v>
+        <v>8.954570019039306</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.955438898443003</v>
+        <v>8.954683559734354</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.967411256191811</v>
+        <v>8.966569146399808</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.099749027173242</v>
+        <v>9.098591393032931</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.154787216662189</v>
+        <v>9.153577941082405</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.314187223558859</v>
+        <v>9.313272817946503</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.402379526532645</v>
+        <v>9.401675452017795</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.418468452520329</v>
+        <v>9.417901967075757</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.499867146268841</v>
+        <v>9.499409402304721</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.602849310684853</v>
+        <v>9.603083546602335</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.588300574099346</v>
+        <v>9.588795818624359</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.596332490134891</v>
+        <v>9.597234793188484</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.582162187500508</v>
+        <v>9.583563330977686</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.558866821917377</v>
+        <v>9.560454730698927</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.590012307853986</v>
+        <v>9.591776439770358</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.462851792589294</v>
+        <v>9.464356733987575</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.396879608597079</v>
+        <v>9.398280366156737</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.264436238948383</v>
+        <v>9.265188191348432</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.174909127049217</v>
+        <v>9.175365990900096</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.08046184111042</v>
+        <v>9.080282595139465</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05771377667284</v>
+        <v>9.057362415317897</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.053073029096664</v>
+        <v>9.052798381105218</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.030818072957167</v>
+        <v>9.030419401239675</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.010431674455667</v>
+        <v>9.010045584626235</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.016672419342495</v>
+        <v>9.01650575551575</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03716206934268</v>
+        <v>9.037265907101062</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.053405596285783</v>
+        <v>9.053632684976995</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.031756387463538</v>
+        <v>9.033724033729587</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.009257080218678</v>
+        <v>9.013229192807248</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.986958825197735</v>
+        <v>8.99263300591794</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.963039800647371</v>
+        <v>8.971583476029858</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.94086531133032</v>
+        <v>8.952725649798211</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.896533204119427</v>
+        <v>8.913132137866409</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.938257731147244</v>
+        <v>8.950738349400394</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.917217022163221</v>
+        <v>8.929862433303677</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.855451152155737</v>
+        <v>8.875242656065822</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.79108845392714</v>
+        <v>8.820099930298339</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.779554679336645</v>
+        <v>8.810553935416443</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.824431357924894</v>
+        <v>8.839258539385359</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,15 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.904010563348113</v>
+        <v>8.884854654381808</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>8.886991632966094</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.747978543660235</v>
+        <v>9.748005921660367</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722325750385641</v>
+        <v>9.722385865282668</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718719593183819</v>
+        <v>9.71880217459573</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696790308606502</v>
+        <v>9.696922051997241</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701337336720105</v>
+        <v>9.701467785588736</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694627076237754</v>
+        <v>9.694755906565225</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.690432850720066</v>
+        <v>9.690562466182405</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.704400095861999</v>
+        <v>9.70453332506478</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.716388829255299</v>
+        <v>9.716543823664347</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72410216873593</v>
+        <v>9.724221449538557</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73271805047356</v>
+        <v>9.732838799940961</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709171946517447</v>
+        <v>9.709290146799756</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66479417973304</v>
+        <v>9.664911359211214</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.629920406294708</v>
+        <v>9.63006658073212</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.597986175531179</v>
+        <v>9.598083081023884</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560431270628772</v>
+        <v>9.560517407391057</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.499913496479955</v>
+        <v>9.500102340230704</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.426481797135494</v>
+        <v>9.426741905023365</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.351014709215471</v>
+        <v>9.351258319450899</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.283275853022388</v>
+        <v>9.283529208781168</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.262618231915717</v>
+        <v>9.262779165611429</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276454652894909</v>
+        <v>9.27656725404816</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.242251031168019</v>
+        <v>9.242116026082741</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.176368920004835</v>
+        <v>9.17610276125558</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.115389914027121</v>
+        <v>9.114987177404277</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.022879882373774</v>
+        <v>9.022398422952421</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.954570019039306</v>
+        <v>8.953981850191585</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.954683559734354</v>
+        <v>8.953959982941978</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.966569146399808</v>
+        <v>8.965761335490079</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.098591393032931</v>
+        <v>9.097480168831252</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.153577941082405</v>
+        <v>9.152417106277801</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.313272817946503</v>
+        <v>9.312393573497932</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.401675452017795</v>
+        <v>9.400997943464695</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.417901967075757</v>
+        <v>9.417355645836285</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.499409402304721</v>
+        <v>9.49896673316286</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.603083546602335</v>
+        <v>9.60330541164765</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.588795818624359</v>
+        <v>9.589267668311319</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.597234793188484</v>
+        <v>9.598097975716225</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.583563330977686</v>
+        <v>9.584907366846107</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.560454730698927</v>
+        <v>9.561978768480994</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.591776439770358</v>
+        <v>9.593470421670984</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.464356733987575</v>
+        <v>9.46580420531135</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.398280366156737</v>
+        <v>9.399629044826071</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.265188191348432</v>
+        <v>9.265913668134026</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.175365990900096</v>
+        <v>9.175807561960525</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.080282595139465</v>
+        <v>9.080111212619926</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.057362415317897</v>
+        <v>9.057024503594539</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.052798381105218</v>
+        <v>9.052533963803738</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.030419401239675</v>
+        <v>9.030034834748943</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.010045584626235</v>
+        <v>9.009672346508705</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01650575551575</v>
+        <v>9.016343679114584</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037265907101062</v>
+        <v>9.03736476032412</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.053632684976995</v>
+        <v>9.053851535772017</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.033724033729587</v>
+        <v>9.036542105276887</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.013229192807248</v>
+        <v>9.017992734828193</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.99263300591794</v>
+        <v>8.998888209900038</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.971583476029858</v>
+        <v>8.980525572893107</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.952725649798211</v>
+        <v>8.964601357980365</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.913132137866409</v>
+        <v>8.929099125618325</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.950738349400394</v>
+        <v>8.963067258647513</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.929862433303677</v>
+        <v>8.942493118133942</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.875242656065822</v>
+        <v>8.894627558312303</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.820099930298339</v>
+        <v>8.846588018135563</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.810553935416443</v>
+        <v>8.842988271194635</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.839258539385359</v>
+        <v>8.864613216770891</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.884854654381808</v>
+        <v>8.890297027010932</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.886991632966094</v>
+        <v>8.909347554660725</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748005921660367</v>
+        <v>9.748032204987545</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722385865282668</v>
+        <v>9.722443580002793</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.71880217459573</v>
+        <v>9.718881471333482</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.696922051997241</v>
+        <v>9.697048543167915</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701467785588736</v>
+        <v>9.701593031910594</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694755906565225</v>
+        <v>9.694879598141751</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.690562466182405</v>
+        <v>9.690686905536349</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70453332506478</v>
+        <v>9.704661219287294</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.716543823664347</v>
+        <v>9.716692654859024</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724221449538557</v>
+        <v>9.724335999201191</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732838799940961</v>
+        <v>9.732954760106399</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709290146799756</v>
+        <v>9.709403660627185</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.664911359211214</v>
+        <v>9.665023947321247</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63006658073212</v>
+        <v>9.630207031168256</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598083081023884</v>
+        <v>9.598176222654141</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560517407391057</v>
+        <v>9.560600137599145</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.500102340230704</v>
+        <v>9.500283669389365</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.426741905023365</v>
+        <v>9.426991787070062</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.351258319450899</v>
+        <v>9.351492324988513</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.283529208781168</v>
+        <v>9.283772653935962</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.262779165611429</v>
+        <v>9.262934351761579</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.27656725404816</v>
+        <v>9.276676271020358</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.242116026082741</v>
+        <v>9.241987085505073</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.17610276125558</v>
+        <v>9.175847992313592</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.114987177404277</v>
+        <v>9.114601403837046</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.022398422952421</v>
+        <v>9.021937122984035</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.953981850191585</v>
+        <v>8.953418156399604</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.953959982941978</v>
+        <v>8.953266222938346</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.965761335490079</v>
+        <v>8.964985780136004</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.097480168831252</v>
+        <v>9.096412633771271</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.152417106277801</v>
+        <v>9.151301874920817</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.312393573497932</v>
+        <v>9.311547518273111</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.400997943464695</v>
+        <v>9.400345543746754</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.417355645836285</v>
+        <v>9.416828460552491</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.49896673316286</v>
+        <v>9.498538452039206</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60330541164765</v>
+        <v>9.603515806270419</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.589267668311319</v>
+        <v>9.589717699475374</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.598097975716225</v>
+        <v>9.598924497243154</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.584907366846107</v>
+        <v>9.586197693612997</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.561978768480994</v>
+        <v>9.563442682101631</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.593470421670984</v>
+        <v>9.595098327572096</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.46580420531135</v>
+        <v>9.46719740632984</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.399629044826071</v>
+        <v>9.400928455974345</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.265913668134026</v>
+        <v>9.266614006292986</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.175807561960525</v>
+        <v>9.176234566724474</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.080111212619926</v>
+        <v>9.079947199914649</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.057024503594539</v>
+        <v>9.05669929591658</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.052533963803738</v>
+        <v>9.052279228769384</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.030034834748943</v>
+        <v>9.029663657335163</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.009672346508705</v>
+        <v>9.009311356400296</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.016343679114584</v>
+        <v>9.016186037411588</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03736476032412</v>
+        <v>9.037458964834059</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.053851535772017</v>
+        <v>9.054062577584961</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.036542105276887</v>
+        <v>9.046014381570298</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.017992734828193</v>
+        <v>9.030865134831808</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>8.998888209900038</v>
+        <v>9.013761883844838</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>8.980525572893107</v>
+        <v>9.000320347179848</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.964601357980365</v>
+        <v>8.988529637155533</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.929099125618325</v>
+        <v>8.958091682553448</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.963067258647513</v>
+        <v>8.991599078433167</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.942493118133942</v>
+        <v>8.973528603556685</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.894627558312303</v>
+        <v>8.932548208994975</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.846588018135563</v>
+        <v>8.893532951166693</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.842988271194635</v>
+        <v>8.902053878521112</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.864613216770891</v>
+        <v>8.923766494161086</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.890297027010932</v>
+        <v>8.944947745631714</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.909347554660725</v>
+        <v>9.004892059560673</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748032204987545</v>
+        <v>9.748081740109569</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722443580002793</v>
+        <v>9.722552361682864</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.718881471333482</v>
+        <v>9.719030964347853</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697048543167915</v>
+        <v>9.697286976283499</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701593031910594</v>
+        <v>9.701829113355195</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.694879598141751</v>
+        <v>9.695112746974225</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.690686905536349</v>
+        <v>9.69092144778149</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.704661219287294</v>
+        <v>9.704902234466637</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.716692654859024</v>
+        <v>9.716973240274713</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724335999201191</v>
+        <v>9.724551987188725</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.732954760106399</v>
+        <v>9.733173407889282</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709403660627185</v>
+        <v>9.709617700369581</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665023947321247</v>
+        <v>9.665236386686338</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.630207031168256</v>
+        <v>9.63047205219776</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598176222654141</v>
+        <v>9.598352057136045</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560600137599145</v>
+        <v>9.560756155113518</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.500283669389365</v>
+        <v>9.500625506754799</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.426991787070062</v>
+        <v>9.427463188498056</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.351492324988513</v>
+        <v>9.351933702872373</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.283772653935962</v>
+        <v>9.284232046638895</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.262934351761579</v>
+        <v>9.263228652626399</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276676271020358</v>
+        <v>9.276884175399433</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241987085505073</v>
+        <v>9.241745858109025</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.175847992313592</v>
+        <v>9.175369844321857</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.114601403837046</v>
+        <v>9.113876663397692</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.021937122984035</v>
+        <v>9.021070178217798</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.953418156399604</v>
+        <v>8.952358373711043</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.953266222938346</v>
+        <v>8.951961129970435</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.964985780136004</v>
+        <v>8.963524039675661</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.096412633771271</v>
+        <v>9.094398765835138</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.151301874920817</v>
+        <v>9.14919793376739</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.311547518273111</v>
+        <v>9.309947791846721</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.400345543746754</v>
+        <v>9.399110749265784</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.416828460552491</v>
+        <v>9.415827711008006</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.498538452039206</v>
+        <v>9.49772248910582</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.603515806270419</v>
+        <v>9.603905384120409</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.589717699475374</v>
+        <v>9.590557946995609</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.598924497243154</v>
+        <v>9.600476416154336</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.586197693612997</v>
+        <v>9.58862952516867</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.563442682101631</v>
+        <v>9.56620372503037</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.595098327572096</v>
+        <v>9.598170699212794</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.46719740632984</v>
+        <v>9.469832662662277</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.400928455974345</v>
+        <v>9.403389759692621</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.266614006292986</v>
+        <v>9.267944193970958</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.176234566724474</v>
+        <v>9.177047571756539</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.079947199914649</v>
+        <v>9.079639503681982</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05669929591658</v>
+        <v>9.056084271566101</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.052279228769384</v>
+        <v>9.051796796173688</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.029663657335163</v>
+        <v>9.028958832036128</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.009311356400296</v>
+        <v>9.008623877519522</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.016186037411588</v>
+        <v>9.015883463711905</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037458964834059</v>
+        <v>9.037634630818403</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.054062577584961</v>
+        <v>9.054462810511215</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.046014381570298</v>
+        <v>9.056999834359393</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.030865134831808</v>
+        <v>9.04634706363748</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.013761883844838</v>
+        <v>9.031915496264794</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.000320347179848</v>
+        <v>9.024713678678914</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>8.988529637155533</v>
+        <v>9.018524784858645</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.958091682553448</v>
+        <v>8.995314487044453</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>8.991599078433167</v>
+        <v>9.025998810952075</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>8.973528603556685</v>
+        <v>9.010535402136133</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.932548208994975</v>
+        <v>8.979860411122816</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.893532951166693</v>
+        <v>8.948172823151186</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.902053878521112</v>
+        <v>8.962504419136961</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.923766494161086</v>
+        <v>8.979167896040565</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.944947745631714</v>
+        <v>8.995358066703343</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.004892059560673</v>
+        <v>9.056450341143066</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748081740109569</v>
+        <v>9.748105106245372</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722552361682864</v>
+        <v>9.722603679011822</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719030964347853</v>
+        <v>9.719101502079569</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697286976283499</v>
+        <v>9.697399465237739</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701829113355195</v>
+        <v>9.701940490487377</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695112746974225</v>
+        <v>9.695222739659513</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69092144778149</v>
+        <v>9.691032090538698</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.704902234466637</v>
+        <v>9.705015913173494</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.716973240274713</v>
+        <v>9.717105634707325</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724551987188725</v>
+        <v>9.724653915999909</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733173407889282</v>
+        <v>9.733276592012144</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709617700369581</v>
+        <v>9.709718711971604</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665236386686338</v>
+        <v>9.665336708716834</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63047205219776</v>
+        <v>9.630597209316198</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598352057136045</v>
+        <v>9.598435132866038</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560756155113518</v>
+        <v>9.560829794626569</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.500625506754799</v>
+        <v>9.500786795749915</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.427463188498056</v>
+        <v>9.427685758434436</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.351933702872373</v>
+        <v>9.35214206464639</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.284232046638895</v>
+        <v>9.28444900849186</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.263228652626399</v>
+        <v>9.263368304950902</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276884175399433</v>
+        <v>9.276983354324372</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241745858109025</v>
+        <v>9.241632880184065</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.175369844321857</v>
+        <v>9.175145212955046</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.113876663397692</v>
+        <v>9.113535854623493</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.021070178217798</v>
+        <v>9.020662355901385</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.952358373711043</v>
+        <v>8.951859655418009</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.951961129970435</v>
+        <v>8.951346620872943</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.963524039675661</v>
+        <v>8.962834501520964</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.094398765835138</v>
+        <v>9.093447953531468</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.14919793376739</v>
+        <v>9.148204551791695</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.309947791846721</v>
+        <v>9.309190844201781</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.399110749265784</v>
+        <v>9.398525921615422</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.415827711008006</v>
+        <v>9.415352401877694</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.49772248910582</v>
+        <v>9.497333610392921</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.603905384120409</v>
+        <v>9.604085991980362</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.590557946995609</v>
+        <v>9.59095069199936</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.600476416154336</v>
+        <v>9.601205810163821</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.58862952516867</v>
+        <v>9.589776609762717</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.56620372503037</v>
+        <v>9.567507025167039</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.598170699212794</v>
+        <v>9.599621886415662</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.469832662662277</v>
+        <v>9.471080042222654</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.403389759692621</v>
+        <v>9.404556361120317</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.267944193970958</v>
+        <v>9.268576315390863</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.177047571756539</v>
+        <v>9.177434821824502</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.079639503681982</v>
+        <v>9.079495016116713</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.056084271566101</v>
+        <v>9.055793211704064</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.051796796173688</v>
+        <v>9.051568177276195</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.028958832036128</v>
+        <v>9.028623968593298</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.008623877519522</v>
+        <v>9.008296346925802</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015883463711905</v>
+        <v>9.015738244006908</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037634630818403</v>
+        <v>9.037716632158979</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.054462810511215</v>
+        <v>9.054652726455689</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.056999834359393</v>
+        <v>9.061039980824809</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04634706363748</v>
+        <v>9.05208698519154</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.031915496264794</v>
+        <v>9.038671609328459</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.024713678678914</v>
+        <v>9.033875973904996</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.018524784858645</v>
+        <v>9.030058468661464</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>8.995314487044453</v>
+        <v>9.009992106184278</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.025998810952075</v>
+        <v>9.039616235530861</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.010535402136133</v>
+        <v>9.02406543774141</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.979860411122816</v>
+        <v>8.995467979116379</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.948172823151186</v>
+        <v>8.96579932298771</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.962504419136961</v>
+        <v>8.981281958293279</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.979167896040565</v>
+        <v>8.999686886160347</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.995358066703343</v>
+        <v>9.016018747388646</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.056450341143066</v>
+        <v>9.072462556079337</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748105106245372</v>
+        <v>9.74812760727116</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722603679011822</v>
+        <v>9.722653098824383</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719101502079569</v>
+        <v>9.71916944064704</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697399465237739</v>
+        <v>9.697507800170891</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.701940490487377</v>
+        <v>9.702047753236783</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695222739659513</v>
+        <v>9.695328668548441</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691032090538698</v>
+        <v>9.691138641058899</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705015913173494</v>
+        <v>9.705125376699677</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717105634707325</v>
+        <v>9.717233151204768</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724653915999909</v>
+        <v>9.724752098350478</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733276592012144</v>
+        <v>9.733375983595922</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709718711971604</v>
+        <v>9.709816012160456</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665336708716834</v>
+        <v>9.665433384392957</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.630597209316198</v>
+        <v>9.630717819789151</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598435132866038</v>
+        <v>9.598515213252263</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560829794626569</v>
+        <v>9.560900734642328</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.500786795749915</v>
+        <v>9.500942137646833</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.427685758434436</v>
+        <v>9.427900211371441</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35214206464639</v>
+        <v>9.352342807912672</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28444900849186</v>
+        <v>9.284658095766991</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.263368304950902</v>
+        <v>9.263503287973149</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.276983354324372</v>
+        <v>9.277079532903917</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241632880184065</v>
+        <v>9.241524578297785</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.175145212955046</v>
+        <v>9.1749294561677</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.113535854623493</v>
+        <v>9.113208309917175</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.020662355901385</v>
+        <v>9.020270320282377</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.951859655418009</v>
+        <v>8.951380132269472</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.951346620872943</v>
+        <v>8.950755551303754</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.962834501520964</v>
+        <v>8.962170487636261</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.093447953531468</v>
+        <v>9.092531838971997</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.148204551791695</v>
+        <v>9.147247395031535</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.309190844201781</v>
+        <v>9.308460511331603</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.398525921615422</v>
+        <v>9.397961321904113</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.415352401877694</v>
+        <v>9.414892730197387</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.497333610392921</v>
+        <v>9.496956722158505</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604085991980362</v>
+        <v>9.604257993341916</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59095069199936</v>
+        <v>9.591326699068112</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.601205810163821</v>
+        <v>9.601906569311318</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.589776609762717</v>
+        <v>9.59088118650731</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.567507025167039</v>
+        <v>9.568762587377009</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.599621886415662</v>
+        <v>9.601020488278042</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.471080042222654</v>
+        <v>9.472283834449321</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.404556361120317</v>
+        <v>9.405683140955308</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.268576315390863</v>
+        <v>9.269187853234122</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.177434821824502</v>
+        <v>9.177810010352394</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.079495016116713</v>
+        <v>9.079356283868149</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.055793211704064</v>
+        <v>9.055512361689601</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.051568177276195</v>
+        <v>9.051347392695188</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.028623968593298</v>
+        <v>9.028300056994926</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.008296346925802</v>
+        <v>9.007978976647198</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015738244006908</v>
+        <v>9.015596884127575</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037716632158979</v>
+        <v>9.037795069368384</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.054652726455689</v>
+        <v>9.054836286930332</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.061039980824809</v>
+        <v>9.061012968802526</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.05208698519154</v>
+        <v>9.054364020108691</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038671609328459</v>
+        <v>9.042453125907031</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.033875973904996</v>
+        <v>9.038125629051683</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.030058468661464</v>
+        <v>9.036658472838608</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.009992106184278</v>
+        <v>9.019418761991705</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.039616235530861</v>
+        <v>9.047221422088182</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.02406543774141</v>
+        <v>9.031661502715721</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.995467979116379</v>
+        <v>9.003338158077304</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.96579932298771</v>
+        <v>8.975493007990593</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.981281958293279</v>
+        <v>8.990935297567528</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.999686886160347</v>
+        <v>9.009539240087104</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.016018747388646</v>
+        <v>9.024789090930255</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,15 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.072462556079337</v>
+        <v>9.073909576616511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>9.073776524776033</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74812760727116</v>
+        <v>9.748149290353357</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722653098824383</v>
+        <v>9.722700724431357</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.71916944064704</v>
+        <v>9.719234921055143</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697507800170891</v>
+        <v>9.697612206888543</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702047753236783</v>
+        <v>9.702151125329785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695328668548441</v>
+        <v>9.695430754645601</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691138641058899</v>
+        <v>9.69124132212983</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705125376699677</v>
+        <v>9.705230855096776</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717233151204768</v>
+        <v>9.71735605421657</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724752098350478</v>
+        <v>9.724846736919012</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733375983595922</v>
+        <v>9.733471787807586</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709816012160456</v>
+        <v>9.709909801646489</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665433384392957</v>
+        <v>9.665526608722015</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.630717819789151</v>
+        <v>9.630834126610713</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598515213252263</v>
+        <v>9.598592457167495</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560900734642328</v>
+        <v>9.560969120789427</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.500942137646833</v>
+        <v>9.50109185497063</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.427900211371441</v>
+        <v>9.428106982389602</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.352342807912672</v>
+        <v>9.352536342179633</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.284658095766991</v>
+        <v>9.284859728817516</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.263503287973149</v>
+        <v>9.263633829071885</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277079532903917</v>
+        <v>9.277172838711948</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241524578297785</v>
+        <v>9.241420672230646</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.1749294561677</v>
+        <v>9.174722062458539</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.113208309917175</v>
+        <v>9.112893274980067</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.020270320282377</v>
+        <v>9.019893178528404</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.951380132269472</v>
+        <v>8.950918724824721</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.950755551303754</v>
+        <v>8.95018661487344</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.962170487636261</v>
+        <v>8.961530612342953</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.092531838971997</v>
+        <v>9.091648565412987</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.147247395031535</v>
+        <v>9.14632452651016</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.308460511331603</v>
+        <v>9.307755423762231</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.397961321904113</v>
+        <v>9.397415928825374</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.414892730197387</v>
+        <v>9.41444795298413</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.496956722158505</v>
+        <v>9.496591303131588</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604257993341916</v>
+        <v>9.604421956654093</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.591326699068112</v>
+        <v>9.591686990838237</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.601906569311318</v>
+        <v>9.602580329910619</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.59088118650731</v>
+        <v>9.591945562261509</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.568762587377009</v>
+        <v>9.56997297003721</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.601020488278042</v>
+        <v>9.602369296135056</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.472283834449321</v>
+        <v>9.473446267700261</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.405683140955308</v>
+        <v>9.406772081646505</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.269187853234122</v>
+        <v>9.269779776241018</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.177810010352394</v>
+        <v>9.178173676135671</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.079356283868149</v>
+        <v>9.079222977170177</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.055512361689601</v>
+        <v>9.055241200369682</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.051347392695188</v>
+        <v>9.051134053629895</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.028300056994926</v>
+        <v>9.027986579433582</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.007978976647198</v>
+        <v>9.007671316404071</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015596884127575</v>
+        <v>9.015459250771119</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037795069368384</v>
+        <v>9.037870161123571</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.054836286930332</v>
+        <v>9.055013799434308</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.061012968802526</v>
+        <v>9.06098821376483</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.054364020108691</v>
+        <v>9.054007884050661</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.042453125907031</v>
+        <v>9.042845912315336</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.038125629051683</v>
+        <v>9.038696429091676</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.036658472838608</v>
+        <v>9.038614972513988</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.019418761991705</v>
+        <v>9.023402659114389</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.047221422088182</v>
+        <v>9.048880066983941</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.031661502715721</v>
+        <v>9.032721885995104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.003338158077304</v>
+        <v>9.004396039116207</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.975493007990593</v>
+        <v>8.977563999405737</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.990935297567528</v>
+        <v>8.9909569793464</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.009539240087104</v>
+        <v>9.008913050688626</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.024789090930255</v>
+        <v>9.020887211712104</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.073909576616511</v>
+        <v>9.061152606329371</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.073776524776033</v>
+        <v>9.021211883727265</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.042845912315336</v>
+        <v>9.042851458093427</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.038696429091676</v>
+        <v>9.038720913016922</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.038614972513988</v>
+        <v>9.038660443272871</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.023402659114389</v>
+        <v>9.023423337395638</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.048880066983941</v>
+        <v>9.048940543682257</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.032721885995104</v>
+        <v>9.032929290150062</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.004396039116207</v>
+        <v>9.004979576267447</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.977563999405737</v>
+        <v>8.977705552408571</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.9909569793464</v>
+        <v>8.99153477684024</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.008913050688626</v>
+        <v>9.00911563959486</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.020887211712104</v>
+        <v>9.02077916290323</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.061152606329371</v>
+        <v>9.061066631814334</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.021211883727265</v>
+        <v>9.021017028701941</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.042851458093427</v>
+        <v>9.042847376356864</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.038720913016922</v>
+        <v>9.03875291892115</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.038660443272871</v>
+        <v>9.038780439810562</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.023423337395638</v>
+        <v>9.023677088754752</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.048940543682257</v>
+        <v>9.049281157851928</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.032929290150062</v>
+        <v>9.033208007835054</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.004979576267447</v>
+        <v>9.005321588634709</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.977705552408571</v>
+        <v>8.977413981743169</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.99153477684024</v>
+        <v>8.991062141981841</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.00911563959486</v>
+        <v>9.008606917626112</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.02077916290323</v>
+        <v>9.020703615583963</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.061066631814334</v>
+        <v>9.06084378219327</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.021017028701941</v>
+        <v>9.019805527634743</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748149290353357</v>
+        <v>9.748170199291213</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722700724431357</v>
+        <v>9.722746651779097</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719234921055143</v>
+        <v>9.719298074294462</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697612206888543</v>
+        <v>9.697712895130206</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702151125329785</v>
+        <v>9.702250814569352</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695430754645601</v>
+        <v>9.695529203223934</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69124132212983</v>
+        <v>9.691340340664098</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705230855096776</v>
+        <v>9.705332561983603</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71735605421657</v>
+        <v>9.717474589433769</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724846736919012</v>
+        <v>9.724938020033889</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733471787807586</v>
+        <v>9.7335641952881</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.709909801646489</v>
+        <v>9.710000266934333</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665526608722015</v>
+        <v>9.665616563066457</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.630834126610713</v>
+        <v>9.630946355785921</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598592457167495</v>
+        <v>9.598667012462208</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.560969120789427</v>
+        <v>9.561035088416165</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50109185497063</v>
+        <v>9.50123624736953</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.428106982389602</v>
+        <v>9.428306476090624</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.352536342179633</v>
+        <v>9.35272304818119</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.284859728817516</v>
+        <v>9.285054298651279</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.263633829071885</v>
+        <v>9.263760141321063</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277172838711948</v>
+        <v>9.277263392735883</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241420672230646</v>
+        <v>9.241320903458139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.174722062458539</v>
+        <v>9.174522558622671</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.112893274980067</v>
+        <v>9.112590051300275</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.019893178528404</v>
+        <v>9.019530103468499</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.950918724824721</v>
+        <v>8.950474432574831</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.95018661487344</v>
+        <v>8.949638599865343</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.961530612342953</v>
+        <v>8.960913588085717</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.091648565412987</v>
+        <v>9.090796405676338</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.14632452651016</v>
+        <v>9.145434144301134</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.307755423762231</v>
+        <v>9.307074303682452</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.397415928825374</v>
+        <v>9.396888787937552</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.41444795298413</v>
+        <v>9.414017372346617</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.496591303131588</v>
+        <v>9.496236859794475</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604421956654093</v>
+        <v>9.604578403111617</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.591686990838237</v>
+        <v>9.592032509791814</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.602580329910619</v>
+        <v>9.603228607057783</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.591945562261509</v>
+        <v>9.592971880816474</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.56997297003721</v>
+        <v>9.571140553114024</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.602369296135056</v>
+        <v>9.603670908313065</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.473446267700261</v>
+        <v>9.474569422197389</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.406772081646505</v>
+        <v>9.407825037817686</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.269779776241018</v>
+        <v>9.270352994853194</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.178173676135671</v>
+        <v>9.1785263275651</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.079222977170177</v>
+        <v>9.079094790525073</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.055241200369682</v>
+        <v>9.054979240982574</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.051134053629895</v>
+        <v>9.050927796069841</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.027986579433582</v>
+        <v>9.027683049433501</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.007671316404071</v>
+        <v>9.007372940959419</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015459250771119</v>
+        <v>9.015325215056542</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037870161123571</v>
+        <v>9.037942109056157</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055013799434308</v>
+        <v>9.055185552415487</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.06098821376483</v>
+        <v>9.06096553308112</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.054007884050661</v>
+        <v>9.054207188204771</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.042847376356864</v>
+        <v>9.043863809071116</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.03875291892115</v>
+        <v>9.040053874654857</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.038780439810562</v>
+        <v>9.04162640572596</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.023677088754752</v>
+        <v>9.028585084126789</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.049281157851928</v>
+        <v>9.052346407688521</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.033208007835054</v>
+        <v>9.035794528544059</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.005321588634709</v>
+        <v>9.007953321640013</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.977413981743169</v>
+        <v>8.980415063293844</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.991062141981841</v>
+        <v>8.992337016255927</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.008606917626112</v>
+        <v>9.009754140270555</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.020703615583963</v>
+        <v>9.019789728753356</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.06084378219327</v>
+        <v>9.053625936872399</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.019805527634743</v>
+        <v>9.009884947799147</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748170199291213</v>
+        <v>9.748190374811996</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722746651779097</v>
+        <v>9.72279097009411</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719298074294462</v>
+        <v>9.719359022214482</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697712895130206</v>
+        <v>9.697810059972502</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702250814569352</v>
+        <v>9.702347014226241</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695529203223934</v>
+        <v>9.695624205199319</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691340340664098</v>
+        <v>9.69143588908771</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705332561983603</v>
+        <v>9.705430695986973</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717474589433769</v>
+        <v>9.717588985421701</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.724938020033889</v>
+        <v>9.725026122920339</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.7335641952881</v>
+        <v>9.733653383414719</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710000266934333</v>
+        <v>9.710087581556937</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665616563066457</v>
+        <v>9.665703416315329</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.630946355785921</v>
+        <v>9.631054717787974</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598667012462208</v>
+        <v>9.598739016902581</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561035088416165</v>
+        <v>9.561098763481132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50123624736953</v>
+        <v>9.501375593605264</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.428306476090624</v>
+        <v>9.428499069214384</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35272304818119</v>
+        <v>9.352903280355507</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.285054298651279</v>
+        <v>9.285242169443281</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.263760141321063</v>
+        <v>9.263882424576448</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277263392735883</v>
+        <v>9.277351309737877</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241320903458139</v>
+        <v>9.241225033110709</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.174522558622671</v>
+        <v>9.174330506254906</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.112590051300275</v>
+        <v>9.112297991116611</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.019530103468499</v>
+        <v>9.019180327699928</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.950474432574831</v>
+        <v>8.950046326899553</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.949638599865343</v>
+        <v>8.949110380864536</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.960913588085717</v>
+        <v>8.960318216931533</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.090796405676338</v>
+        <v>9.089973751092032</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.145434144301134</v>
+        <v>9.144574570013326</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.307074303682452</v>
+        <v>9.306415957463246</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.396888787937552</v>
+        <v>9.396379006347736</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.414017372346617</v>
+        <v>9.413600332234896</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.496236859794475</v>
+        <v>9.495892924772871</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604578403111617</v>
+        <v>9.604727811344983</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.592032509791814</v>
+        <v>9.592364125846952</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.603228607057783</v>
+        <v>9.603852805561464</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.592971880816474</v>
+        <v>9.593962136979112</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.571140553114024</v>
+        <v>9.572267553347148</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.603670908313065</v>
+        <v>9.604927746432438</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.474569422197389</v>
+        <v>9.475655242027754</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.407825037817686</v>
+        <v>9.408843746260992</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.270352994853194</v>
+        <v>9.27090836538726</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.1785263275651</v>
+        <v>9.178868444625842</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.079094790525073</v>
+        <v>9.078971440546473</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054979240982574</v>
+        <v>9.054726028409966</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050927796069841</v>
+        <v>9.050728278897248</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.027683049433501</v>
+        <v>9.027389009590916</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.007372940959419</v>
+        <v>9.007083448516623</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015325215056542</v>
+        <v>9.015194652546633</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.037942109056157</v>
+        <v>9.038011099346832</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055185552415487</v>
+        <v>9.055351816679071</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.06096553308112</v>
+        <v>9.060944760773362</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.054207188204771</v>
+        <v>9.052277970230298</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.043863809071116</v>
+        <v>9.042168831058561</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.040053874654857</v>
+        <v>9.038325907082115</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.04162640572596</v>
+        <v>9.040665670918292</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.028585084126789</v>
+        <v>9.029073694224735</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.052346407688521</v>
+        <v>9.050534127251822</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.035794528544059</v>
+        <v>9.032573936643509</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.007953321640013</v>
+        <v>9.004201786008391</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.980415063293844</v>
+        <v>8.977888142185762</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.992337016255927</v>
+        <v>8.987274833834231</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.009754140270555</v>
+        <v>9.002591647421143</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.019789728753356</v>
+        <v>9.009777930212078</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.053625936872399</v>
+        <v>9.036627383901378</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.009884947799147</v>
+        <v>8.978179751883502</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.042168831058561</v>
+        <v>9.042170112103801</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.038325907082115</v>
+        <v>9.038374963994606</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.040665670918292</v>
+        <v>9.040808812992935</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.029073694224735</v>
+        <v>9.0293100701147</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.050534127251822</v>
+        <v>9.050876287111905</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.032573936643509</v>
+        <v>9.032986363734057</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.004201786008391</v>
+        <v>9.004987228968131</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.977888142185762</v>
+        <v>8.977761932300504</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.987274833834231</v>
+        <v>8.987361678902204</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.002591647421143</v>
+        <v>9.002343839767235</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.009777930212078</v>
+        <v>9.009631219550684</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.036627383901378</v>
+        <v>9.036390202388816</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.978179751883502</v>
+        <v>8.977501541680006</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748190374811996</v>
+        <v>9.748209854835626</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72279097009411</v>
+        <v>9.7228337624611</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719359022214482</v>
+        <v>9.719417878307004</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697810059972502</v>
+        <v>9.697903883087879</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702347014226241</v>
+        <v>9.702439904286878</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695624205199319</v>
+        <v>9.695715938363573</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69143588908771</v>
+        <v>9.691528146585469</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705430695986973</v>
+        <v>9.705525442033569</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717588985421701</v>
+        <v>9.717699455085279</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725026122920339</v>
+        <v>9.725111208819779</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733653383414719</v>
+        <v>9.733739517434016</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710087581556937</v>
+        <v>9.710171907183295</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665703416315329</v>
+        <v>9.665787325937222</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631054717787974</v>
+        <v>9.631159408868207</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598739016902581</v>
+        <v>9.598808599014541</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561098763481132</v>
+        <v>9.561160263352871</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.501375593605264</v>
+        <v>9.501510153339467</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.428499069214384</v>
+        <v>9.428685112991442</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.352903280355507</v>
+        <v>9.353077369072331</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.285242169443281</v>
+        <v>9.285423680794885</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.263882424576448</v>
+        <v>9.264000866466985</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277351309737877</v>
+        <v>9.277436698600484</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241225033110709</v>
+        <v>9.241132840157805</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.174330506254906</v>
+        <v>9.174145498627285</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.112297991116611</v>
+        <v>9.112016492915741</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.019180327699928</v>
+        <v>9.018843138315242</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.950046326899553</v>
+        <v>8.949633544761046</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.949110380864536</v>
+        <v>8.948600911254402</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.960318216931533</v>
+        <v>8.959743382934125</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.089973751092032</v>
+        <v>9.089179101548963</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.144574570013326</v>
+        <v>9.143744238428953</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.306415957463246</v>
+        <v>9.305779268891582</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.396379006347736</v>
+        <v>9.395885747887647</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.413600332234896</v>
+        <v>9.413196215453372</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.495892924772871</v>
+        <v>9.495559055308593</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604727811344983</v>
+        <v>9.604870621573088</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.592364125846952</v>
+        <v>9.592682643111756</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.603852805561464</v>
+        <v>9.60445422972008</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.593962136979112</v>
+        <v>9.594918189228416</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.572267553347148</v>
+        <v>9.573356037918987</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.604927746432438</v>
+        <v>9.606142070095101</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.475655242027754</v>
+        <v>9.476705546007848</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.408843746260992</v>
+        <v>9.409829835022872</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.27090836538726</v>
+        <v>9.271446693871702</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.178868444625842</v>
+        <v>9.179200480754295</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078971440546473</v>
+        <v>9.078852664025087</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054726028409966</v>
+        <v>9.054481136683844</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050728278897248</v>
+        <v>9.050535182155972</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.027389009590916</v>
+        <v>9.027104029498844</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.007083448516623</v>
+        <v>9.006802459224897</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015194652546633</v>
+        <v>9.015067443229189</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038011099346832</v>
+        <v>9.038077304147123</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055351816679071</v>
+        <v>9.055512846678132</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060944760773362</v>
+        <v>9.060925745794425</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.052277970230298</v>
+        <v>9.050308867462128</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.042170112103801</v>
+        <v>9.040438958554414</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.038374963994606</v>
+        <v>9.036632790576244</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.040808812992935</v>
+        <v>9.040096408004386</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.0293100701147</v>
+        <v>9.030058053550109</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.050876287111905</v>
+        <v>9.048627581224531</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.032986363734057</v>
+        <v>9.029337342201639</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.004987228968131</v>
+        <v>9.000959756079332</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.977761932300504</v>
+        <v>8.973840956300227</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.987361678902204</v>
+        <v>8.980459953392844</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.002343839767235</v>
+        <v>8.992912926391927</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.009631219550684</v>
+        <v>8.997477821029921</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.036390202388816</v>
+        <v>9.017933940923687</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.977501541680006</v>
+        <v>8.948650709872297</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748209854835626</v>
+        <v>9.748246867437294</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.7228337624611</v>
+        <v>9.722915074045511</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719417878307004</v>
+        <v>9.719529731343775</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697903883087879</v>
+        <v>9.698082170481934</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702439904286878</v>
+        <v>9.702616415760984</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695715938363573</v>
+        <v>9.695890250344082</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691528146585469</v>
+        <v>9.691703445939828</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705525442033569</v>
+        <v>9.705705448310216</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717699455085279</v>
+        <v>9.717909396531365</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725111208819779</v>
+        <v>9.725272928644157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733739517434016</v>
+        <v>9.73390322949597</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710171907183295</v>
+        <v>9.710332184681903</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665787325937222</v>
+        <v>9.66594689266854</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631159408868207</v>
+        <v>9.631358499122523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598808599014541</v>
+        <v>9.59894096864636</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561160263352871</v>
+        <v>9.561277168285912</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.501510153339467</v>
+        <v>9.501765865928276</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.428685112991442</v>
+        <v>9.429038842385745</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353077369072331</v>
+        <v>9.353408329104479</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.285423680794885</v>
+        <v>9.28576887272598</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264000866466985</v>
+        <v>9.264226920890245</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277436698600484</v>
+        <v>9.277600300000081</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241132840157805</v>
+        <v>9.240958681961629</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.174145498627285</v>
+        <v>9.1737951325922</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.112016492915741</v>
+        <v>9.111482983856964</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.018843138315242</v>
+        <v>9.018203911662331</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.949633544761046</v>
+        <v>8.948850793483704</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.948600911254402</v>
+        <v>8.947634387977677</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.959743382934125</v>
+        <v>8.95865123201019</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.089179101548963</v>
+        <v>9.087668307001081</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.143744238428953</v>
+        <v>9.142165553227644</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.305779268891582</v>
+        <v>9.304566750710432</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.395885747887647</v>
+        <v>9.39494571340034</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.413196215453372</v>
+        <v>9.412424461111947</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.495559055308593</v>
+        <v>9.494919856512452</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604870621573088</v>
+        <v>9.605138038530267</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.592682643111756</v>
+        <v>9.593283304143249</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.60445422972008</v>
+        <v>9.605593521325446</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.594918189228416</v>
+        <v>9.596734501509069</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.573356037918987</v>
+        <v>9.575425053792694</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.606142070095101</v>
+        <v>9.608451480621664</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.476705546007848</v>
+        <v>9.478706313522052</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.409829835022872</v>
+        <v>9.411710170854638</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.271446693871702</v>
+        <v>9.272475218259157</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.179200480754295</v>
+        <v>9.179836001439734</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078852664025087</v>
+        <v>9.078627869150948</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054481136683844</v>
+        <v>9.054014744265533</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050535182155972</v>
+        <v>9.050167066602377</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.027104029498844</v>
+        <v>9.026559650632993</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.006802459224897</v>
+        <v>9.006264572156446</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015067443229189</v>
+        <v>9.014822625919887</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038077304147123</v>
+        <v>9.038201983224756</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055512846678132</v>
+        <v>9.055820146935122</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060925745794425</v>
+        <v>9.060892449329961</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.050308867462128</v>
+        <v>9.04848313751766</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040438958554414</v>
+        <v>9.036015458994996</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.036632790576244</v>
+        <v>9.03206006836681</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.040096408004386</v>
+        <v>9.035412960670019</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.030058053550109</v>
+        <v>9.026269850422791</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.048627581224531</v>
+        <v>9.039736406309991</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.029337342201639</v>
+        <v>9.018480679605741</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.000959756079332</v>
+        <v>8.989305692348765</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.973840956300227</v>
+        <v>8.962900662864378</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.980459953392844</v>
+        <v>8.964356202379562</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.992912926391927</v>
+        <v>8.970721109731997</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.997477821029921</v>
+        <v>8.970208575013</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.017933940923687</v>
+        <v>8.980212735231458</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.948650709872297</v>
+        <v>8.898491255932125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>8.761473755932125</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748246867437294</v>
+        <v>9.748209854835626</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722915074045511</v>
+        <v>9.7228337624611</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719529731343775</v>
+        <v>9.719417878307004</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698082170481934</v>
+        <v>9.697903883087879</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702616415760984</v>
+        <v>9.702439904286878</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695890250344082</v>
+        <v>9.695715938363573</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691703445939828</v>
+        <v>9.691528146585469</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705705448310216</v>
+        <v>9.705525442033569</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717909396531365</v>
+        <v>9.717699455085279</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725272928644157</v>
+        <v>9.725111208819779</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73390322949597</v>
+        <v>9.733739517434016</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710332184681903</v>
+        <v>9.710171907183295</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66594689266854</v>
+        <v>9.665787325937222</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631358499122523</v>
+        <v>9.631159408868207</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.59894096864636</v>
+        <v>9.598808599014541</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561277168285912</v>
+        <v>9.561160263352871</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.501765865928276</v>
+        <v>9.501510153339467</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.429038842385745</v>
+        <v>9.428685112991442</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353408329104479</v>
+        <v>9.353077369072331</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28576887272598</v>
+        <v>9.285423680794885</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264226920890245</v>
+        <v>9.264000866466985</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277600300000081</v>
+        <v>9.277436698600484</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240958681961629</v>
+        <v>9.241132840157805</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.1737951325922</v>
+        <v>9.174145498627285</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.111482983856964</v>
+        <v>9.112016492915741</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.018203911662331</v>
+        <v>9.018843138315242</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.948850793483704</v>
+        <v>8.949633544761046</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.947634387977677</v>
+        <v>8.948600911254402</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.95865123201019</v>
+        <v>8.959743382934125</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.087668307001081</v>
+        <v>9.089179101548963</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.142165553227644</v>
+        <v>9.143744238428953</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.304566750710432</v>
+        <v>9.305779268891582</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.39494571340034</v>
+        <v>9.395885747887647</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.412424461111947</v>
+        <v>9.413196215453372</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.494919856512452</v>
+        <v>9.495559055308593</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605138038530267</v>
+        <v>9.604870621573088</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.593283304143249</v>
+        <v>9.592682643111756</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.605593521325446</v>
+        <v>9.60445422972008</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.596734501509069</v>
+        <v>9.594918189228416</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.575425053792694</v>
+        <v>9.573356037918987</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.608451480621664</v>
+        <v>9.606142070095101</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.478706313522052</v>
+        <v>9.476705546007848</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.411710170854638</v>
+        <v>9.409829835022872</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.272475218259157</v>
+        <v>9.271446693871702</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.179836001439734</v>
+        <v>9.179200480754295</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078627869150948</v>
+        <v>9.078852664025087</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054014744265533</v>
+        <v>9.054481136683844</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050167066602377</v>
+        <v>9.050535182155972</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.026559650632993</v>
+        <v>9.027104029498844</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.006264572156446</v>
+        <v>9.006802459224897</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014822625919887</v>
+        <v>9.015067443229189</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038201983224756</v>
+        <v>9.038077304147123</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055820146935122</v>
+        <v>9.055512846678132</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060892449329961</v>
+        <v>9.060925745794425</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04848313751766</v>
+        <v>9.052204773102897</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.036015458994996</v>
+        <v>9.038918253625107</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.03206006836681</v>
+        <v>9.03459587867399</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.035412960670019</v>
+        <v>9.036507706587154</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.026269850422791</v>
+        <v>9.024651529318959</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.039736406309991</v>
+        <v>9.043796030441637</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.018480679605741</v>
+        <v>9.025058872972545</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.989305692348765</v>
+        <v>8.995596471904639</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.962900662864378</v>
+        <v>8.968353640403901</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.964356202379562</v>
+        <v>8.974272021625568</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.970721109731997</v>
+        <v>8.983741754819405</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.970208575013</v>
+        <v>8.986632655223795</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.980212735231458</v>
+        <v>9.004411516592373</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.898491255932125</v>
+        <v>8.919518962088713</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.761473755932125</v>
+        <v>8.782501462088712</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.03459587867399</v>
+        <v>9.034590876100257</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.036507706587154</v>
+        <v>9.036495827988389</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.024651529318959</v>
+        <v>9.024662595467781</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.043796030441637</v>
+        <v>9.042675222146686</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.025058872972545</v>
+        <v>9.023243849197222</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.995596471904639</v>
+        <v>8.994258622450861</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.968353640403901</v>
+        <v>8.967212781750749</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.974272021625568</v>
+        <v>8.973334078185621</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.983741754819405</v>
+        <v>8.983010246673537</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.986632655223795</v>
+        <v>8.985899972945838</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.004411516592373</v>
+        <v>9.003686765122954</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.919518962088713</v>
+        <v>8.918160982116131</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.782501462088712</v>
+        <v>8.78114348211613</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748209854835626</v>
+        <v>9.748228674712458</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.7228337624611</v>
+        <v>9.722875106342393</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719417878307004</v>
+        <v>9.719474748410383</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697903883087879</v>
+        <v>9.697994533875894</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702439904286878</v>
+        <v>9.702529652574894</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695715938363573</v>
+        <v>9.69580456849258</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691528146585469</v>
+        <v>9.6916172802201</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705525442033569</v>
+        <v>9.705616972510549</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717699455085279</v>
+        <v>9.717806196986523</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725111208819779</v>
+        <v>9.725193429996427</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733739517434016</v>
+        <v>9.733822751480776</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710171907183295</v>
+        <v>9.710253394614625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665787325937222</v>
+        <v>9.665868438928474</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631159408868207</v>
+        <v>9.631260612235875</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598808599014541</v>
+        <v>9.598875878844511</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561160263352871</v>
+        <v>9.561219697529271</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.501510153339467</v>
+        <v>9.501640168740044</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.428685112991442</v>
+        <v>9.4288649352617</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353077369072331</v>
+        <v>9.353245622638138</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.285423680794885</v>
+        <v>9.285599149768887</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264000866466985</v>
+        <v>9.26411564330024</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277436698600484</v>
+        <v>9.277519662656124</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241132840157805</v>
+        <v>9.241044119788084</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.174145498627285</v>
+        <v>9.173967157895129</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.112016492915741</v>
+        <v>9.111744997398112</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.018843138315242</v>
+        <v>9.018517872175094</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.949633544761046</v>
+        <v>8.949235283046537</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.948600911254402</v>
+        <v>8.948109216478365</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.959743382934125</v>
+        <v>8.959188045263087</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.089179101548963</v>
+        <v>9.088411056527194</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.143744238428953</v>
+        <v>9.1429416881628</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.305779268891582</v>
+        <v>9.305163193040944</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.395885747887647</v>
+        <v>9.395408228730073</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.413196215453372</v>
+        <v>9.412804440914421</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.495559055308593</v>
+        <v>9.495234831814804</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.604870621573088</v>
+        <v>9.605007239287833</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.592682643111756</v>
+        <v>9.59298880590638</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.60445422972008</v>
+        <v>9.605034092084402</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.594918189228416</v>
+        <v>9.59584177110948</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.573356037918987</v>
+        <v>9.574407936781787</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.606142070095101</v>
+        <v>9.607315990139391</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.476705546007848</v>
+        <v>9.477722037533351</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.409829835022872</v>
+        <v>9.410784831675301</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.271446693871702</v>
+        <v>9.271968739576092</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.179200480754295</v>
+        <v>9.17952286456255</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078852664025087</v>
+        <v>9.078738216191152</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054481136683844</v>
+        <v>9.054244166721549</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050535182155972</v>
+        <v>9.050348205470749</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.027104029498844</v>
+        <v>9.026827703839968</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.006802459224897</v>
+        <v>9.006529613786077</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.015067443229189</v>
+        <v>9.014943471466431</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038077304147123</v>
+        <v>9.038140882849589</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055512846678132</v>
+        <v>9.055668881696686</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060925745794425</v>
+        <v>9.060908350505905</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.052204773102897</v>
+        <v>9.052134512164091</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038918253625107</v>
+        <v>9.036269496878164</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.034590876100257</v>
+        <v>9.031596157546476</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.036495827988389</v>
+        <v>9.033176199734839</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.024662595467781</v>
+        <v>9.021339475145783</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.042675222146686</v>
+        <v>9.036369408983822</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.023243849197222</v>
+        <v>9.015768244358629</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.994258622450861</v>
+        <v>8.986347577355529</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.967212781750749</v>
+        <v>8.958855855905018</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.973334078185621</v>
+        <v>8.962615517834415</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.983010246673537</v>
+        <v>8.967914977278477</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.985899972945838</v>
+        <v>8.96760965802283</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.003686765122954</v>
+        <v>8.978929191442541</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.918160982116131</v>
+        <v>8.883213000489395</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.78114348211613</v>
+        <v>8.746195500489394</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748228674712458</v>
+        <v>9.748264463842336</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722875106342393</v>
+        <v>9.722953733144886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719474748410383</v>
+        <v>9.719582919479331</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.697994533875894</v>
+        <v>9.69816694071611</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702529652574894</v>
+        <v>9.70270034027385</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69580456849258</v>
+        <v>9.695973128557688</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.6916172802201</v>
+        <v>9.691786789487146</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705616972510549</v>
+        <v>9.705791019771965</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717806196986523</v>
+        <v>9.71800922704063</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725193429996427</v>
+        <v>9.725349837704997</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733822751480776</v>
+        <v>9.733981086055246</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710253394614625</v>
+        <v>9.710408409055933</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.665868438928474</v>
+        <v>9.666022815692951</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631260612235875</v>
+        <v>9.631453229743927</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.598875878844511</v>
+        <v>9.599003973502718</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561219697529271</v>
+        <v>9.561332771261398</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.501640168740044</v>
+        <v>9.50188745628477</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.4288649352617</v>
+        <v>9.429207120972196</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353245622638138</v>
+        <v>9.353565757901629</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.285599149768887</v>
+        <v>9.285933126984798</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26411564330024</v>
+        <v>9.264334855315132</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277519662656124</v>
+        <v>9.277678703787091</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.241044119788084</v>
+        <v>9.240876350113393</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.173967157895129</v>
+        <v>9.173629095380761</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.111744997398112</v>
+        <v>9.111229966922082</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.018517872175094</v>
+        <v>9.017900680861413</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.949235283046537</v>
+        <v>8.948479378062542</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.948109216478365</v>
+        <v>8.947175577727883</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.959188045263087</v>
+        <v>8.958132034596511</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.088411056527194</v>
+        <v>9.086949628116514</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.1429416881628</v>
+        <v>9.141414555405353</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.305163193040944</v>
+        <v>9.303989023372456</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.395408228730073</v>
+        <v>9.394497511142617</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.412804440914421</v>
+        <v>9.412055759795818</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.495234831814804</v>
+        <v>9.49461375214571</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605007239287833</v>
+        <v>9.605263364809428</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59298880590638</v>
+        <v>9.593566778143016</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.605034092084402</v>
+        <v>9.606133569311845</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.59584177110948</v>
+        <v>9.597597893938033</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.574407936781787</v>
+        <v>9.576409076788369</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.607315990139391</v>
+        <v>9.60955038966436</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.477722037533351</v>
+        <v>9.479659872544888</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.410784831675301</v>
+        <v>9.412607201141292</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.271968739576092</v>
+        <v>9.2729668051599</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.17952286456255</v>
+        <v>9.180140275039104</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078738216191152</v>
+        <v>9.078521410477677</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054244166721549</v>
+        <v>9.053792518006887</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050348205470749</v>
+        <v>9.049991500125792</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.026827703839968</v>
+        <v>9.026299509618923</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.006529613786077</v>
+        <v>9.006007012337554</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014943471466431</v>
+        <v>9.01470479945657</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038140882849589</v>
+        <v>9.03826074244054</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055668881696686</v>
+        <v>9.05596685450675</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060908350505905</v>
+        <v>9.060877927553053</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.052134512164091</v>
+        <v>9.04844584329104</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.036269496878164</v>
+        <v>9.033698199183489</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.031596157546476</v>
+        <v>9.029602668542928</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.033176199734839</v>
+        <v>9.032695298717181</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.021339475145783</v>
+        <v>9.023809845615865</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.036369408983822</v>
+        <v>9.034972840284853</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.015768244358629</v>
+        <v>9.012988223226078</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.986347577355529</v>
+        <v>8.983573544585337</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.958855855905018</v>
+        <v>8.957082545102875</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.962615517834415</v>
+        <v>8.956902870828387</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967914977278477</v>
+        <v>8.959897424129732</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.96760965802283</v>
+        <v>8.957101451874822</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.978929191442541</v>
+        <v>8.962923182718363</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.883213000489395</v>
+        <v>8.878381099033238</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.746195500489394</v>
+        <v>8.741363599033237</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748264463842336</v>
+        <v>9.748246867437294</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722953733144886</v>
+        <v>9.722915074045511</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719582919479331</v>
+        <v>9.719529731343775</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.69816694071611</v>
+        <v>9.698082170481934</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70270034027385</v>
+        <v>9.702616415760984</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695973128557688</v>
+        <v>9.695890250344082</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691786789487146</v>
+        <v>9.691703445939828</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705791019771965</v>
+        <v>9.705705448310216</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71800922704063</v>
+        <v>9.717909396531365</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725349837704997</v>
+        <v>9.725272928644157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.733981086055246</v>
+        <v>9.73390322949597</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710408409055933</v>
+        <v>9.710332184681903</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666022815692951</v>
+        <v>9.66594689266854</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631453229743927</v>
+        <v>9.631358499122523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599003973502718</v>
+        <v>9.59894096864636</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561332771261398</v>
+        <v>9.561277168285912</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50188745628477</v>
+        <v>9.501765865928276</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.429207120972196</v>
+        <v>9.429038842385745</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353565757901629</v>
+        <v>9.353408329104479</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.285933126984798</v>
+        <v>9.28576887272598</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264334855315132</v>
+        <v>9.264226920890245</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277678703787091</v>
+        <v>9.277600300000081</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240876350113393</v>
+        <v>9.240958681961629</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.173629095380761</v>
+        <v>9.1737951325922</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.111229966922082</v>
+        <v>9.111482983856964</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.017900680861413</v>
+        <v>9.018203911662331</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.948479378062542</v>
+        <v>8.948850793483704</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.947175577727883</v>
+        <v>8.947634387977677</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.958132034596511</v>
+        <v>8.95865123201019</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.086949628116514</v>
+        <v>9.087668307001081</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.141414555405353</v>
+        <v>9.142165553227644</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.303989023372456</v>
+        <v>9.304566750710432</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.394497511142617</v>
+        <v>9.39494571340034</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.412055759795818</v>
+        <v>9.412424461111947</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.49461375214571</v>
+        <v>9.494919856512452</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605263364809428</v>
+        <v>9.605138038530267</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.593566778143016</v>
+        <v>9.593283304143249</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.606133569311845</v>
+        <v>9.605593521325446</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.597597893938033</v>
+        <v>9.596734501509069</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.576409076788369</v>
+        <v>9.575425053792694</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.60955038966436</v>
+        <v>9.608451480621664</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.479659872544888</v>
+        <v>9.478706313522052</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.412607201141292</v>
+        <v>9.411710170854638</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.2729668051599</v>
+        <v>9.272475218259157</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.180140275039104</v>
+        <v>9.179836001439734</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078521410477677</v>
+        <v>9.078627869150948</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.053792518006887</v>
+        <v>9.054014744265533</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.049991500125792</v>
+        <v>9.050167066602377</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.026299509618923</v>
+        <v>9.026559650632993</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.006007012337554</v>
+        <v>9.006264572156446</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01470479945657</v>
+        <v>9.014822625919887</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03826074244054</v>
+        <v>9.038201983224756</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.05596685450675</v>
+        <v>9.055820146935122</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060877927553053</v>
+        <v>9.060892449329961</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04844584329104</v>
+        <v>9.052067025375926</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.033698199183489</v>
+        <v>9.036296524020084</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.029602668542928</v>
+        <v>9.032024346740792</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.032695298717181</v>
+        <v>9.033789837076853</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.023809845615865</v>
+        <v>9.023139842621148</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.034972840284853</v>
+        <v>9.035815665346481</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.012988223226078</v>
+        <v>9.014387682293233</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.983573544585337</v>
+        <v>8.984650188352244</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.957082545102875</v>
+        <v>8.95690050559268</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.956902870828387</v>
+        <v>8.959977769636922</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.959897424129732</v>
+        <v>8.962226792017528</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.957101451874822</v>
+        <v>8.95988292780542</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.962923182718363</v>
+        <v>8.967312299199801</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.878381099033238</v>
+        <v>8.87431023216137</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.741363599033237</v>
+        <v>8.714368228758845</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748246867437294</v>
+        <v>9.748281492771511</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722915074045511</v>
+        <v>9.722991146862816</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719529731343775</v>
+        <v>9.719634399259371</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698082170481934</v>
+        <v>9.698248982883614</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702616415760984</v>
+        <v>9.70278156312329</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.695890250344082</v>
+        <v>9.696053338468133</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691703445939828</v>
+        <v>9.691867447219874</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705705448310216</v>
+        <v>9.705873827533168</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.717909396531365</v>
+        <v>9.718105850718157</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725272928644157</v>
+        <v>9.725424281609092</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73390322949597</v>
+        <v>9.734056447117975</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710332184681903</v>
+        <v>9.710482190979754</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66594689266854</v>
+        <v>9.666096328392999</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631358499122523</v>
+        <v>9.631544954170939</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.59894096864636</v>
+        <v>9.599064991887865</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561277168285912</v>
+        <v>9.56138659598675</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.501765865928276</v>
+        <v>9.502005137630078</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.429038842385745</v>
+        <v>9.42937003944132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353408329104479</v>
+        <v>9.353718161316939</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28576887272598</v>
+        <v>9.286092172324986</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264226920890245</v>
+        <v>9.264439593611305</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277600300000081</v>
+        <v>9.277754962511766</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240958681961629</v>
+        <v>9.240796959989849</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.1737951325922</v>
+        <v>9.173468741026987</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.111482983856964</v>
+        <v>9.110985493626343</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.018203911662331</v>
+        <v>9.01760764211447</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.948850793483704</v>
+        <v>8.948120384906161</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.947634387977677</v>
+        <v>8.946731993306408</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.95865123201019</v>
+        <v>8.957629602713682</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.087668307001081</v>
+        <v>9.086253872557684</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.142165553227644</v>
+        <v>9.140687497335703</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.304566750710432</v>
+        <v>9.303429148575924</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.39494571340034</v>
+        <v>9.394062972605216</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.412424461111947</v>
+        <v>9.411697849829892</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.494919856512452</v>
+        <v>9.49431616077362</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605138038530267</v>
+        <v>9.60538353770777</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.593283304143249</v>
+        <v>9.593839822953505</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.605593521325446</v>
+        <v>9.606655217487205</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.596734501509069</v>
+        <v>9.598433364930408</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.575425053792694</v>
+        <v>9.577361586714334</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.608451480621664</v>
+        <v>9.610614449292918</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.478706313522052</v>
+        <v>9.48058412222904</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.411710170854638</v>
+        <v>9.41347719134537</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.272475218259157</v>
+        <v>9.273444137753961</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.179836001439734</v>
+        <v>9.180436048659232</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078627869150948</v>
+        <v>9.078418641939352</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.054014744265533</v>
+        <v>9.053577157874118</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.050167066602377</v>
+        <v>9.049821256219404</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.026559650632993</v>
+        <v>9.026046940775093</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.006264572156446</v>
+        <v>9.005756629250017</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014822625919887</v>
+        <v>9.014589889041295</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038201983224756</v>
+        <v>9.038317287977931</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.055820146935122</v>
+        <v>9.056109204353483</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060892449329961</v>
+        <v>9.060864680262704</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.052067025375926</v>
+        <v>9.048409969849837</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.036296524020084</v>
+        <v>9.037238469020831</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.032024346740792</v>
+        <v>9.034233464599506</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.033789837076853</v>
+        <v>9.037709526121255</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.023139842621148</v>
+        <v>9.029070282246959</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.035815665346481</v>
+        <v>9.038127161988204</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.014387682293233</v>
+        <v>9.015095260858391</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.984650188352244</v>
+        <v>8.985543309820992</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.95690050559268</v>
+        <v>8.958870889762141</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.959977769636922</v>
+        <v>8.95767412765456</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.962226792017528</v>
+        <v>8.956572535119868</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.95988292780542</v>
+        <v>8.951405488250479</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.967312299199801</v>
+        <v>8.953519094744232</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.87431023216137</v>
+        <v>8.870063277790759</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.714368228758845</v>
+        <v>8.793679864117854</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748281492771511</v>
+        <v>9.748297981238174</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.722991146862816</v>
+        <v>9.723027374414224</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719634399259371</v>
+        <v>9.719684251664534</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698248982883614</v>
+        <v>9.698328426536353</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70278156312329</v>
+        <v>9.70286021264525</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696053338468133</v>
+        <v>9.696131006841362</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.691867447219874</v>
+        <v>9.69194554685426</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705873827533168</v>
+        <v>9.705954003299064</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718105850718157</v>
+        <v>9.718199419527394</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725424281609092</v>
+        <v>9.725496376944857</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734056447117975</v>
+        <v>9.734129430705568</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710482190979754</v>
+        <v>9.71055364593194</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666096328392999</v>
+        <v>9.666167543650083</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631544954170939</v>
+        <v>9.631633813119047</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599064991887865</v>
+        <v>9.599124116178492</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56138659598675</v>
+        <v>9.561438726364909</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502005137630078</v>
+        <v>9.502119095293731</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.42937003944132</v>
+        <v>9.429527849442682</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353718161316939</v>
+        <v>9.353865775834729</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286092172324986</v>
+        <v>9.286246252350296</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264439593611305</v>
+        <v>9.264541274410041</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277754962511766</v>
+        <v>9.277829160273342</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240796959989849</v>
+        <v>9.240720358603264</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.173468741026987</v>
+        <v>9.173313784575864</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.110985493626343</v>
+        <v>9.110749140758458</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01760764211447</v>
+        <v>9.017324292911614</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.948120384906161</v>
+        <v>8.94777320454013</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.946731993306408</v>
+        <v>8.946302893432311</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.957629602713682</v>
+        <v>8.957143139740893</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.086253872557684</v>
+        <v>9.085579964529064</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.140687497335703</v>
+        <v>9.139983256245591</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.303429148575924</v>
+        <v>9.302886315758169</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.394062972605216</v>
+        <v>9.393641486813138</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.411697849829892</v>
+        <v>9.411350271217838</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.49431616077362</v>
+        <v>9.494026742634677</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60538353770777</v>
+        <v>9.605498853211351</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.593839822953505</v>
+        <v>9.594102992229887</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.606655217487205</v>
+        <v>9.60715938262646</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.598433364930408</v>
+        <v>9.599242241655137</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.577361586714334</v>
+        <v>9.578284065910381</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.610614449292918</v>
+        <v>9.611645284369347</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.48058412222904</v>
+        <v>9.481480386007316</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.41347719134537</v>
+        <v>9.414321336256339</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.273444137753961</v>
+        <v>9.27390781829531</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.180436048659232</v>
+        <v>9.180723666527086</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078418641939352</v>
+        <v>9.078319378348688</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.053577157874118</v>
+        <v>9.053368353470795</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.049821256219404</v>
+        <v>9.049656099555285</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.026046940775093</v>
+        <v>9.025801622945814</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.005756629250017</v>
+        <v>9.005513133684737</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014589889041295</v>
+        <v>9.014477795618964</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038317287977931</v>
+        <v>9.038371738454892</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056109204353483</v>
+        <v>9.056247385087907</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060864680262704</v>
+        <v>9.060852611400893</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048409969849837</v>
+        <v>9.048375444745938</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.037238469020831</v>
+        <v>9.040487905379713</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.034233464599506</v>
+        <v>9.038494451541672</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.037709526121255</v>
+        <v>9.042339045219084</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.029070282246959</v>
+        <v>9.033908909758381</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.038127161988204</v>
+        <v>9.041240366751538</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.015095260858391</v>
+        <v>9.017471625993037</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.985543309820992</v>
+        <v>8.987472577172291</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.958870889762141</v>
+        <v>8.960671890751687</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.95767412765456</v>
+        <v>8.958593590550244</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.956572535119868</v>
+        <v>8.953920652961743</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.951405488250479</v>
+        <v>8.946739350552644</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.953519094744232</v>
+        <v>8.945789172422991</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.870063277790759</v>
+        <v>8.864148612701932</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.793679864117854</v>
+        <v>8.832714023968382</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048375444745938</v>
+        <v>9.051879751477433</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040487905379713</v>
+        <v>9.041978717079788</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.038494451541672</v>
+        <v>9.04132808922899</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.042339045219084</v>
+        <v>9.044150883340205</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.033908909758381</v>
+        <v>9.035843117780368</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.041240366751538</v>
+        <v>9.043602653588444</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.017471625993037</v>
+        <v>9.020975685026928</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.987472577172291</v>
+        <v>8.992491662048856</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.960671890751687</v>
+        <v>8.966994119755</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.958593590550244</v>
+        <v>8.969859838550464</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.953920652961743</v>
+        <v>8.969155263870178</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.946739350552644</v>
+        <v>8.962938850631124</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.945789172422991</v>
+        <v>8.965893863658877</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.864148612701932</v>
+        <v>8.896679773115594</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.832714023968382</v>
+        <v>8.820144803324659</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>8.798961493266784</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748297981238174</v>
+        <v>9.748313954568058</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723027374414224</v>
+        <v>9.723062471319185</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719684251664534</v>
+        <v>9.719732552638312</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698328426536353</v>
+        <v>9.69840539315436</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.70286021264525</v>
+        <v>9.702936409177237</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696131006841362</v>
+        <v>9.696206252541863</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69194554685426</v>
+        <v>9.692021208138581</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.705954003299064</v>
+        <v>9.706031670540495</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718199419527394</v>
+        <v>9.71829007598638</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725496376944857</v>
+        <v>9.72556623306677</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734129430705568</v>
+        <v>9.734200147516747</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.71055364593194</v>
+        <v>9.710622882228225</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666167543650083</v>
+        <v>9.666236567411733</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631633813119047</v>
+        <v>9.631719938665441</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599124116178492</v>
+        <v>9.599181433117888</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561438726364909</v>
+        <v>9.561489241105829</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502119095293731</v>
+        <v>9.502229503083822</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.429527849442682</v>
+        <v>9.4296807871425</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.353865775834729</v>
+        <v>9.354008823352679</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286246252350296</v>
+        <v>9.286395595726695</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264541274410041</v>
+        <v>9.264640028521981</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277829160273342</v>
+        <v>9.277901377025213</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240720358603264</v>
+        <v>9.240646403290043</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.173313784575864</v>
+        <v>9.173163959703199</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.110749140758458</v>
+        <v>9.110520512469989</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.017324292911614</v>
+        <v>9.017050163078336</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.94777320454013</v>
+        <v>8.947437266516477</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.946302893432311</v>
+        <v>8.945887583926545</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.957143139740893</v>
+        <v>8.956671898586414</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.085579964529064</v>
+        <v>9.084926894287301</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.139983256245591</v>
+        <v>9.13930077825083</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.302886315758169</v>
+        <v>9.302359762424183</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.393641486813138</v>
+        <v>9.393232478399684</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.411350271217838</v>
+        <v>9.41101258928234</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.494026742634677</v>
+        <v>9.493745175080996</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605498853211351</v>
+        <v>9.605609585797518</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.594102992229887</v>
+        <v>9.594356801726768</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.60715938262646</v>
+        <v>9.607646922040214</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.599242241655137</v>
+        <v>9.600025768825024</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.578284065910381</v>
+        <v>9.579177905641162</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.611645284369347</v>
+        <v>9.612644420717217</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.481480386007316</v>
+        <v>9.482349909279636</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.414321336256339</v>
+        <v>9.415140761908493</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.27390781829531</v>
+        <v>9.274358416161654</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.180723666527086</v>
+        <v>9.181003454990332</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078319378348688</v>
+        <v>9.078223446521633</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.053368353470795</v>
+        <v>9.053165812647311</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.049656099555285</v>
+        <v>9.049495808280742</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.025801622945814</v>
+        <v>9.025563252579552</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.005513133684737</v>
+        <v>9.005276251326073</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014477795618964</v>
+        <v>9.014368423989936</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038371738454892</v>
+        <v>9.038424204368845</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056247385087907</v>
+        <v>9.056381574768254</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060852611400893</v>
+        <v>9.060841632919885</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051879751477433</v>
+        <v>9.048342200035568</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041978717079788</v>
+        <v>9.040405549576327</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04132808922899</v>
+        <v>9.040191018188208</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.044150883340205</v>
+        <v>9.043879445347599</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.035843117780368</v>
+        <v>9.035867971923961</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.043602653588444</v>
+        <v>9.041160666930127</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.020975685026928</v>
+        <v>9.016466319980811</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.992491662048856</v>
+        <v>8.987095238262123</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.966994119755</v>
+        <v>8.960582195103219</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.969859838550464</v>
+        <v>8.958001284465887</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.969155263870178</v>
+        <v>8.952776766998332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.962938850631124</v>
+        <v>8.942748127070221</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.965893863658877</v>
+        <v>8.939820528417805</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.896679773115594</v>
+        <v>8.861252432533355</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.820144803324659</v>
+        <v>8.826677414124628</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.798961493266784</v>
+        <v>8.771488153786256</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048342200035568</v>
+        <v>9.051821950873091</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040405549576327</v>
+        <v>9.041885729655471</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.040191018188208</v>
+        <v>9.042837506640689</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.043879445347599</v>
+        <v>9.045440465016789</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.035867971923961</v>
+        <v>9.037373947270769</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.041160666930127</v>
+        <v>9.04302523493724</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.016466319980811</v>
+        <v>9.019435730408961</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.987095238262123</v>
+        <v>8.991545840149879</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.960582195103219</v>
+        <v>8.966319790743707</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.958001284465887</v>
+        <v>8.968433243266801</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.952776766998332</v>
+        <v>8.967070186187097</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.942748127070221</v>
+        <v>8.958244323958905</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.939820528417805</v>
+        <v>8.959215546461273</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.861252432533355</v>
+        <v>8.892029608458145</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.826677414124628</v>
+        <v>8.820820031813222</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.771488153786256</v>
+        <v>8.796091305667421</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748313954568058</v>
+        <v>9.74832943652903</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723062471319185</v>
+        <v>9.723096489686622</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719732552638312</v>
+        <v>9.719779373472589</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.69840539315436</v>
+        <v>9.698479996764572</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.702936409177237</v>
+        <v>9.703010265671669</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696206252541863</v>
+        <v>9.696279187138614</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692021208138581</v>
+        <v>9.692094543464757</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706031670540495</v>
+        <v>9.706106945127305</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71829007598638</v>
+        <v>9.718377953889876</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72556623306677</v>
+        <v>9.725633952647577</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734200147516747</v>
+        <v>9.734268701486487</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710622882228225</v>
+        <v>9.710690001568107</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666236567411733</v>
+        <v>9.666303499215481</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631719938665441</v>
+        <v>9.631803454901185</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599181433117888</v>
+        <v>9.599237024238382</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561489241105829</v>
+        <v>9.561538214121857</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502229503083822</v>
+        <v>9.502336524167745</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.4296807871425</v>
+        <v>9.429829074394398</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354008823352679</v>
+        <v>9.354147512287739</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286395595726695</v>
+        <v>9.286540417308615</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264640028521981</v>
+        <v>9.264735979474223</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277901377025213</v>
+        <v>9.277971688809956</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240646403290043</v>
+        <v>9.240574960861295</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.173163959703199</v>
+        <v>9.173019017224995</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.110520512469989</v>
+        <v>9.110299238108713</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.017050163078336</v>
+        <v>9.016784812227623</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.947437266516477</v>
+        <v>8.947112036353705</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.945887583926545</v>
+        <v>8.945485414047404</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.956671898586414</v>
+        <v>8.956215177908595</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.084926894287301</v>
+        <v>9.084293713165518</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.13930077825083</v>
+        <v>9.138639073170584</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.302359762424183</v>
+        <v>9.301848770656331</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.393232478399684</v>
+        <v>9.392835405071814</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.41101258928234</v>
+        <v>9.410684392984553</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.493745175080996</v>
+        <v>9.493471151578365</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605609585797518</v>
+        <v>9.60571599030871</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.594356801726768</v>
+        <v>9.594601732446311</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.607646922040214</v>
+        <v>9.608118638287527</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.600025768825024</v>
+        <v>9.600785114976983</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.579177905641162</v>
+        <v>9.580044412950539</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.612644420717217</v>
+        <v>9.613613292521819</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.482349909279636</v>
+        <v>9.483193865044996</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.415140761908493</v>
+        <v>9.41593653040843</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.274358416161654</v>
+        <v>9.274796470020304</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.181003454990332</v>
+        <v>9.181275723625587</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078223446521633</v>
+        <v>9.078130684332933</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.053165812647311</v>
+        <v>9.05296926019377</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.049495808280742</v>
+        <v>9.049340173082893</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.025563252579552</v>
+        <v>9.025331542563453</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.005276251326073</v>
+        <v>9.005045721842022</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014368423989936</v>
+        <v>9.01426168268102</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038424204368845</v>
+        <v>9.038474788766925</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056381574768254</v>
+        <v>9.056511941612243</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060841632919885</v>
+        <v>9.060831664028255</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051821950873091</v>
+        <v>9.048310171957251</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041885729655471</v>
+        <v>9.040325633449481</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.042837506640689</v>
+        <v>9.041727597404922</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.045440465016789</v>
+        <v>9.045263225514079</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.037373947270769</v>
+        <v>9.037623563907559</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.04302523493724</v>
+        <v>9.04096313637727</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.019435730408961</v>
+        <v>9.015978199563657</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.991545840149879</v>
+        <v>8.986566962522193</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.966319790743707</v>
+        <v>8.960236626873497</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.968433243266801</v>
+        <v>8.957076362068289</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967070186187097</v>
+        <v>8.951243969345217</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.958244323958905</v>
+        <v>8.938430799887207</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.959215546461273</v>
+        <v>8.933590914524547</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.892029608458145</v>
+        <v>8.857309191846189</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.820820031813222</v>
+        <v>8.819492785535298</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.796091305667421</v>
+        <v>8.761684901167847</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048310171957251</v>
+        <v>9.05176626460619</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040325633449481</v>
+        <v>9.041795551048548</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.041727597404922</v>
+        <v>9.044864528912415</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.045263225514079</v>
+        <v>9.047444805762481</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.037623563907559</v>
+        <v>9.039729635116172</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.04096313637727</v>
+        <v>9.043620720592649</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.015978199563657</v>
+        <v>9.019911166422535</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.986566962522193</v>
+        <v>8.992112892045789</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.960236626873497</v>
+        <v>8.967278849129931</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.957076362068289</v>
+        <v>8.968968122537042</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.951243969345217</v>
+        <v>8.967198430421899</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.938430799887207</v>
+        <v>8.956393038034204</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.933590914524547</v>
+        <v>8.956017152445723</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.857309191846189</v>
+        <v>8.89211984483817</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.819492785535298</v>
+        <v>8.827283560702764</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.761684901167847</v>
+        <v>8.810912564253197</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74832943652903</v>
+        <v>9.74834444944903</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723096489686622</v>
+        <v>9.723129478472281</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719779373472589</v>
+        <v>9.719824781158316</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698479996764572</v>
+        <v>9.698552344503563</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703010265671669</v>
+        <v>9.703081888253598</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696279187138614</v>
+        <v>9.69634991545613</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692094543464757</v>
+        <v>9.69216565842447</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706106945127305</v>
+        <v>9.706179935904149</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718377953889876</v>
+        <v>9.718463178966271</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725633952647577</v>
+        <v>9.725699632180675</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734268701486487</v>
+        <v>9.734335190294576</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710690001568107</v>
+        <v>9.710755099532154</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666303499215481</v>
+        <v>9.666368432665969</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631803454901185</v>
+        <v>9.631884478525222</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599237024238382</v>
+        <v>9.599290966246404</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561538214121857</v>
+        <v>9.561585714887526</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502336524167745</v>
+        <v>9.502440311873423</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.429829074394398</v>
+        <v>9.429972919805714</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354147512287739</v>
+        <v>9.354282038583058</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286540417308615</v>
+        <v>9.286680919164937</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264735979474223</v>
+        <v>9.264829244004435</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.277971688809956</v>
+        <v>9.278040167980427</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240574960861295</v>
+        <v>9.240505906835359</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.173019017224995</v>
+        <v>9.172878723747093</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.110299238108713</v>
+        <v>9.110084970253832</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.016784812227623</v>
+        <v>9.016527827448222</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.947112036353705</v>
+        <v>8.946797012759067</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.945485414047404</v>
+        <v>8.94509577316127</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.956215177908595</v>
+        <v>8.955772318676646</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.084293713165518</v>
+        <v>9.083679529039159</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.138639073170584</v>
+        <v>9.13799720980167</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.301848770656331</v>
+        <v>9.301352663921957</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.392835405071814</v>
+        <v>9.392449755286956</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.410684392984553</v>
+        <v>9.410365293371964</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.493471151578365</v>
+        <v>9.493204380768708</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60571599030871</v>
+        <v>9.605818303637115</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.594601732446311</v>
+        <v>9.594838233480941</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.608118638287527</v>
+        <v>9.608575283450133</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.600785114976983</v>
+        <v>9.60152137818918</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.580044412950539</v>
+        <v>9.580884816909155</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.613613292521819</v>
+        <v>9.614553249079442</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.483193865044996</v>
+        <v>9.484013359055908</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.41593653040843</v>
+        <v>9.41670964436593</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.274796470020304</v>
+        <v>9.275222489829639</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.181275723625587</v>
+        <v>9.181540766269013</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078130684332933</v>
+        <v>9.078040939858466</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05296926019377</v>
+        <v>9.052778436642328</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.049340173082893</v>
+        <v>9.049188996328631</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.025331542563453</v>
+        <v>9.025106221146908</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.005045721842022</v>
+        <v>9.004821298036529</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01426168268102</v>
+        <v>9.014157483814074</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038474788766925</v>
+        <v>9.038523587851884</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056511941612243</v>
+        <v>9.056638644655134</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060831664028255</v>
+        <v>9.06082263051643</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.05176626460619</v>
+        <v>9.048279300634945</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041795551048548</v>
+        <v>9.04024805411791</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.044864528912415</v>
+        <v>9.043766407280602</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.047444805762481</v>
+        <v>9.047329265720009</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.039729635116172</v>
+        <v>9.040152491459512</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.043620720592649</v>
+        <v>9.041920217435365</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.019911166422535</v>
+        <v>9.016856040604209</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.992112892045789</v>
+        <v>8.987519713461184</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.967278849129931</v>
+        <v>8.961521574105983</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.968968122537042</v>
+        <v>8.95811898893518</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967198430421899</v>
+        <v>8.951961617806875</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.956393038034204</v>
+        <v>8.937078973492781</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.956017152445723</v>
+        <v>8.930991579547442</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.89211984483817</v>
+        <v>8.858227324619651</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.827283560702764</v>
+        <v>8.822127688992445</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.810912564253197</v>
+        <v>8.776662124544918</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048279300634945</v>
+        <v>9.051712585515943</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.04024805411791</v>
+        <v>9.04170805998741</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.043766407280602</v>
+        <v>9.046317886000473</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.047329265720009</v>
+        <v>9.048756551267481</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.040152491459512</v>
+        <v>9.041283674533968</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.041920217435365</v>
+        <v>9.043444600120107</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.016856040604209</v>
+        <v>9.019578763353991</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.987519713461184</v>
+        <v>8.991879828019325</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.961521574105983</v>
+        <v>8.967384697348788</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.95811898893518</v>
+        <v>8.968593142966574</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.951961617806875</v>
+        <v>8.96639933928903</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.937078973492781</v>
+        <v>8.953747718588499</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.930991579547442</v>
+        <v>8.952112570686873</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.858227324619651</v>
+        <v>8.890773074345592</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.822127688992445</v>
+        <v>8.830371416267383</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.776662124544918</v>
+        <v>8.814286484757694</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74834444944903</v>
+        <v>9.748373150913382</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723129478472281</v>
+        <v>9.723192548744198</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719824781158316</v>
+        <v>9.719911605431758</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698552344503563</v>
+        <v>9.698690669492411</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703081888253598</v>
+        <v>9.703218825046584</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69634991545613</v>
+        <v>9.696485141796197</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69216565842447</v>
+        <v>9.692301618604223</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706179935904149</v>
+        <v>9.706319469379995</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718463178966271</v>
+        <v>9.71862613675777</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725699632180675</v>
+        <v>9.725825228887034</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734335190294576</v>
+        <v>9.734462334608526</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710755099532154</v>
+        <v>9.710879585739537</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666368432665969</v>
+        <v>9.666492651834545</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631884478525222</v>
+        <v>9.632039480977465</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599290966246404</v>
+        <v>9.599394187699666</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561585714887526</v>
+        <v>9.561676557315781</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502440311873423</v>
+        <v>9.502638755580374</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.429972919805714</v>
+        <v>9.430248059055243</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354282038583058</v>
+        <v>9.354539330087119</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286680919164937</v>
+        <v>9.286949713583542</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264829244004435</v>
+        <v>9.265008149496456</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278040167980427</v>
+        <v>9.278171900676512</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240505906835359</v>
+        <v>9.240374505499037</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172878723747093</v>
+        <v>9.172611221925104</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.110084970253832</v>
+        <v>9.109676169991669</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.016527827448222</v>
+        <v>9.016037429422505</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.946797012759067</v>
+        <v>8.946195731121321</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.94509577316127</v>
+        <v>8.944351818469174</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.955772318676646</v>
+        <v>8.954925741448896</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.083679529039159</v>
+        <v>9.082504841518602</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.13799720980167</v>
+        <v>9.136769552769733</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.301352663921957</v>
+        <v>9.300402589049405</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.392449755286956</v>
+        <v>9.391710821310149</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.410365293371964</v>
+        <v>9.409752930323316</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.493204380768708</v>
+        <v>9.492691502459117</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605818303637115</v>
+        <v>9.606011523517148</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.594838233480941</v>
+        <v>9.595287598500262</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.608575283450133</v>
+        <v>9.609446139404486</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.60152137818918</v>
+        <v>9.60292872662983</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.580884816909155</v>
+        <v>9.582491874912961</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.614553249079442</v>
+        <v>9.616351425650354</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.484013359055908</v>
+        <v>9.485583076540358</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.41670964436593</v>
+        <v>9.418191645709797</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.275222489829639</v>
+        <v>9.276040334557077</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.181540766269013</v>
+        <v>9.18205027590859</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.078040939858466</v>
+        <v>9.077869942751093</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052778436642328</v>
+        <v>9.052413010582752</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.049188996328631</v>
+        <v>9.048899281330822</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.025106221146908</v>
+        <v>9.024673728025819</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.004821298036529</v>
+        <v>9.004389839670679</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014157483814074</v>
+        <v>9.013956379076204</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038523587851884</v>
+        <v>9.038616183912136</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056638644655134</v>
+        <v>9.056881653162669</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.06082263051643</v>
+        <v>9.06080710213983</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051712585515943</v>
+        <v>9.048220806560842</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.04170805998741</v>
+        <v>9.04009952137115</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046317886000473</v>
+        <v>9.047384507454908</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.048756551267481</v>
+        <v>9.050978883926437</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.041283674533968</v>
+        <v>9.044805032030368</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.043444600120107</v>
+        <v>9.045060912827156</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.019578763353991</v>
+        <v>9.020156870613269</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.991879828019325</v>
+        <v>8.991276532647642</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.967384697348788</v>
+        <v>8.965995078003198</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.968593142966574</v>
+        <v>8.962359359614146</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.96639933928903</v>
+        <v>8.956017762241387</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.953747718588499</v>
+        <v>8.938962026563027</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.952112570686873</v>
+        <v>8.932184079952332</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.890773074345592</v>
+        <v>8.868605697085606</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.830371416267383</v>
+        <v>8.841376084318322</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.814286484757694</v>
+        <v>8.816611970193094</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748373150913382</v>
+        <v>9.748359014323523</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723192548744198</v>
+        <v>9.723161483713655</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719911605431758</v>
+        <v>9.719868838704929</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698690669492411</v>
+        <v>9.698622537130058</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703218825046584</v>
+        <v>9.7031513767287</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696485141796197</v>
+        <v>9.696418536076314</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692301618604223</v>
+        <v>9.692234652315625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706319469379995</v>
+        <v>9.706250745214756</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71862613675777</v>
+        <v>9.718545869476038</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725825228887034</v>
+        <v>9.72576336243786</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734462334608526</v>
+        <v>9.734399705828949</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710879585739537</v>
+        <v>9.710818266035135</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666492651834545</v>
+        <v>9.666431455870109</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632039480977465</v>
+        <v>9.631963119386217</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599394187699666</v>
+        <v>9.59934333137392</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561676557315781</v>
+        <v>9.56163180876748</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502638755580374</v>
+        <v>9.502541010419307</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430248059055243</v>
+        <v>9.430112519709994</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354539330087119</v>
+        <v>9.354412586626125</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286949713583542</v>
+        <v>9.286817291514975</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265008149496456</v>
+        <v>9.264919932515815</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278171900676512</v>
+        <v>9.278106883407709</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240374505499037</v>
+        <v>9.24043912474324</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172611221925104</v>
+        <v>9.172742860439918</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109676169991669</v>
+        <v>9.109877382931487</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.016037429422505</v>
+        <v>9.01627882120402</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.946195731121321</v>
+        <v>8.94649172510327</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.944351818469174</v>
+        <v>8.944718087713602</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.954925741448896</v>
+        <v>8.955342701036242</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.082504841518602</v>
+        <v>9.083083502188595</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.136769552769733</v>
+        <v>9.137374311605994</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.300402589049405</v>
+        <v>9.300870804149806</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.391710821310149</v>
+        <v>9.392075046121073</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.409752930323316</v>
+        <v>9.410054922143665</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.492691502459117</v>
+        <v>9.492944585591264</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606011523517148</v>
+        <v>9.605916746241791</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.595287598500262</v>
+        <v>9.595066724584331</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.609446139404486</v>
+        <v>9.60901756301474</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.60292872662983</v>
+        <v>9.60223559129283</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.582491874912961</v>
+        <v>9.581700274316644</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.616351425650354</v>
+        <v>9.615465560961319</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.485583076540358</v>
+        <v>9.484809434541468</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.418191645709797</v>
+        <v>9.417461050965215</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.276040334557077</v>
+        <v>9.275636958690072</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18205027590859</v>
+        <v>9.181798861975031</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077869942751093</v>
+        <v>9.077954070595233</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052413010582752</v>
+        <v>9.05259309716859</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048899281330822</v>
+        <v>9.04904209127314</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024673728025819</v>
+        <v>9.024887030946541</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.004389839670679</v>
+        <v>9.004602745059547</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013956379076204</v>
+        <v>9.014055742973827</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038616183912136</v>
+        <v>9.038570691530722</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056881653162669</v>
+        <v>9.056761834356859</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.06080710213983</v>
+        <v>9.060814464152445</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048220806560842</v>
+        <v>9.051660813256131</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.04009952137115</v>
+        <v>9.041623141852959</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047384507454908</v>
+        <v>9.04845246714539</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.050978883926437</v>
+        <v>9.05098392877192</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.044805032030368</v>
+        <v>9.043899601895472</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.045060912827156</v>
+        <v>9.044990555145294</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.020156870613269</v>
+        <v>9.021065794181929</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.991276532647642</v>
+        <v>8.993443395256985</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.965995078003198</v>
+        <v>8.969310811868342</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.962359359614146</v>
+        <v>8.970252116107126</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.956017762241387</v>
+        <v>8.967782374372902</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.938962026563027</v>
+        <v>8.953672314196915</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.932184079952332</v>
+        <v>8.951149835282054</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.868605697085606</v>
+        <v>8.893009001394159</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.841376084318322</v>
+        <v>8.837428871153925</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.816611970193094</v>
+        <v>8.82519102963648</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748359014323523</v>
+        <v>9.748386877834356</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723161483713655</v>
+        <v>9.723222714388957</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719868838704929</v>
+        <v>9.719953137234171</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698622537130058</v>
+        <v>9.698756830955547</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.7031513767287</v>
+        <v>9.703284321723928</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696418536076314</v>
+        <v>9.696549820045972</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692234652315625</v>
+        <v>9.69236664534616</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706250745214756</v>
+        <v>9.706386199134316</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718545869476038</v>
+        <v>9.718704085726948</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72576336243786</v>
+        <v>9.72588531207381</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734399705828949</v>
+        <v>9.734523158169496</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710818266035135</v>
+        <v>9.710939138433345</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666431455870109</v>
+        <v>9.666552098829136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.631963119386217</v>
+        <v>9.632113660889534</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.59934333137392</v>
+        <v>9.599443599443077</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56163180876748</v>
+        <v>9.561720018549421</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502541010419307</v>
+        <v>9.502733675296588</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430112519709994</v>
+        <v>9.430379712216185</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354412586626125</v>
+        <v>9.354662432685384</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.286817291514975</v>
+        <v>9.28707835438307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.264919932515815</v>
+        <v>9.265093993906239</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278106883407709</v>
+        <v>9.278235282268758</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24043912474324</v>
+        <v>9.240311946828449</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172742860439918</v>
+        <v>9.172483615262294</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109877382931487</v>
+        <v>9.109481043629776</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01627882120402</v>
+        <v>9.015803309752764</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.94649172510327</v>
+        <v>8.945908614816402</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.944718087713602</v>
+        <v>8.943996457994126</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.955342701036242</v>
+        <v>8.954520890077747</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.083083502188595</v>
+        <v>9.081942801099482</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.137374311605994</v>
+        <v>9.136182154597519</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.300870804149806</v>
+        <v>9.299947449650309</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.392075046121073</v>
+        <v>9.39135664944896</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.410054922143665</v>
+        <v>9.409458987030682</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.492944585591264</v>
+        <v>9.492444880487591</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.605916746241791</v>
+        <v>9.606102827029201</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.595066724584331</v>
+        <v>9.595501223075273</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.60901756301474</v>
+        <v>9.60986163519577</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.60223559129283</v>
+        <v>9.603601700401546</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.581700274316644</v>
+        <v>9.583260646147224</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.615465560961319</v>
+        <v>9.617211972702304</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.484809434541468</v>
+        <v>9.486335215880583</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.417461050965215</v>
+        <v>9.418902275870682</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.275636958690072</v>
+        <v>9.276433051827745</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.181798861975031</v>
+        <v>9.182295260176</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077954070595233</v>
+        <v>9.077788430597062</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05259309716859</v>
+        <v>9.052237958402149</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04904209127314</v>
+        <v>9.048760399403072</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024887030946541</v>
+        <v>9.024466081042968</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.004602745059547</v>
+        <v>9.004182369552495</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.014055742973827</v>
+        <v>9.013859314238132</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038570691530722</v>
+        <v>9.03866014375823</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056761834356859</v>
+        <v>9.056998236021224</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060814464152445</v>
+        <v>9.060800486630535</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051660813256131</v>
+        <v>9.048193081126044</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041623141852959</v>
+        <v>9.040028388242497</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04845246714539</v>
+        <v>9.049374899885025</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.05098392877192</v>
+        <v>9.053071513603443</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.043899601895472</v>
+        <v>9.047487931108925</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.044990555145294</v>
+        <v>9.04739423326042</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.021065794181929</v>
+        <v>9.022855257947967</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.993443395256985</v>
+        <v>8.994382922864766</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.969310811868342</v>
+        <v>8.969534689852832</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.970252116107126</v>
+        <v>8.9659699962444</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967782374372902</v>
+        <v>8.959792028314721</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.953672314196915</v>
+        <v>8.94249963337619</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.951149835282054</v>
+        <v>8.936141132591604</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.893009001394159</v>
+        <v>8.877967131190971</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.837428871153925</v>
+        <v>8.856662908897761</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.82519102963648</v>
+        <v>8.840671044681645</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748386877834356</v>
+        <v>9.74840021263879</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723222714388957</v>
+        <v>9.723252019143452</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719953137234171</v>
+        <v>9.719993486827061</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698756830955547</v>
+        <v>9.698821105791453</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703284321723928</v>
+        <v>9.703347950231475</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696549820045972</v>
+        <v>9.696612653271313</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69236664534616</v>
+        <v>9.69242981557295</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706386199134316</v>
+        <v>9.706451020024844</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718704085726948</v>
+        <v>9.718779815332297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72588531207381</v>
+        <v>9.725943687970688</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734523158169496</v>
+        <v>9.734582253418768</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710939138433345</v>
+        <v>9.710996999375721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666552098829136</v>
+        <v>9.666609870719805</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632113660889534</v>
+        <v>9.632185751224812</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599443599443077</v>
+        <v>9.599491627233682</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561720018549421</v>
+        <v>9.561762247198645</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502733675296588</v>
+        <v>9.502825890229539</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430379712216185</v>
+        <v>9.430507643738146</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354662432685384</v>
+        <v>9.354782048891167</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28707835438307</v>
+        <v>9.28720337343001</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265093993906239</v>
+        <v>9.265177559534122</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278235282268758</v>
+        <v>9.278297087736048</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240311946828449</v>
+        <v>9.240251352749203</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172483615262294</v>
+        <v>9.172359859025775</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109481043629776</v>
+        <v>9.109291733038058</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.015803309752764</v>
+        <v>9.015576139975822</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945908614816402</v>
+        <v>8.945629984546146</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.943996457994126</v>
+        <v>8.943651528355598</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.954520890077747</v>
+        <v>8.954127628395369</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.081942801099482</v>
+        <v>9.081396676998414</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.136182154597519</v>
+        <v>9.135611382208975</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.299947449650309</v>
+        <v>9.299504848040591</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.39135664944896</v>
+        <v>9.39101212233275</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.409458987030682</v>
+        <v>9.409172778343631</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.492444880487591</v>
+        <v>9.492204480771328</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606102827029201</v>
+        <v>9.606190835634155</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.595501223075273</v>
+        <v>9.59570794317805</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.60986163519577</v>
+        <v>9.610264636052566</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.603601700401546</v>
+        <v>9.60425537664905</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.583260646147224</v>
+        <v>9.584007557547039</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.617211972702304</v>
+        <v>9.618048268477317</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.486335215880583</v>
+        <v>9.487066732838846</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.418902275870682</v>
+        <v>9.41959374366466</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.276433051827745</v>
+        <v>9.276815522811322</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.182295260176</v>
+        <v>9.182534054598896</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077788430597062</v>
+        <v>9.077709415875976</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052237958402149</v>
+        <v>9.052067733997742</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048760399403072</v>
+        <v>9.048625287257918</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024466081042968</v>
+        <v>9.024263870461541</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.004182369552495</v>
+        <v>9.003980132669973</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013859314238132</v>
+        <v>9.013764473649621</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03866014375823</v>
+        <v>9.038702644895237</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056998236021224</v>
+        <v>9.057111710863797</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060800486630535</v>
+        <v>9.060794564286745</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048193081126044</v>
+        <v>9.04816630663356</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040028388242497</v>
+        <v>9.039959231865407</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.049374899885025</v>
+        <v>9.049224059671655</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.053071513603443</v>
+        <v>9.055396932693414</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.047487931108925</v>
+        <v>9.049869876791437</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.04739423326042</v>
+        <v>9.049691057638103</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.022855257947967</v>
+        <v>9.024958956774448</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.994382922864766</v>
+        <v>8.996473657169478</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.969534689852832</v>
+        <v>8.972440379945661</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.9659699962444</v>
+        <v>8.968787687525252</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.959792028314721</v>
+        <v>8.962652179436951</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.94249963337619</v>
+        <v>8.945986526623441</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.936141132591604</v>
+        <v>8.938739377604545</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.877967131190971</v>
+        <v>8.884997470958162</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.856662908897761</v>
+        <v>8.867574141159851</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.840671044681645</v>
+        <v>8.855605270283961</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>8.90200904240969</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74840021263879</v>
+        <v>9.748386877834356</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723252019143452</v>
+        <v>9.723222714388957</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719993486827061</v>
+        <v>9.719953137234171</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698821105791453</v>
+        <v>9.698756830955547</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703347950231475</v>
+        <v>9.703284321723928</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696612653271313</v>
+        <v>9.696549820045972</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69242981557295</v>
+        <v>9.69236664534616</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706451020024844</v>
+        <v>9.706386199134316</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718779815332297</v>
+        <v>9.718704085726948</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725943687970688</v>
+        <v>9.72588531207381</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734582253418768</v>
+        <v>9.734523158169496</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710996999375721</v>
+        <v>9.710939138433345</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666609870719805</v>
+        <v>9.666552098829136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632185751224812</v>
+        <v>9.632113660889534</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599491627233682</v>
+        <v>9.599443599443077</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561762247198645</v>
+        <v>9.561720018549421</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502825890229539</v>
+        <v>9.502733675296588</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430507643738146</v>
+        <v>9.430379712216185</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354782048891167</v>
+        <v>9.354662432685384</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28720337343001</v>
+        <v>9.28707835438307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265177559534122</v>
+        <v>9.265093993906239</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278297087736048</v>
+        <v>9.278235282268758</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240251352749203</v>
+        <v>9.240311946828449</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172359859025775</v>
+        <v>9.172483615262294</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109291733038058</v>
+        <v>9.109481043629776</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.015576139975822</v>
+        <v>9.015803309752764</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945629984546146</v>
+        <v>8.945908614816402</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.943651528355598</v>
+        <v>8.943996457994126</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.954127628395369</v>
+        <v>8.954520890077747</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.081396676998414</v>
+        <v>9.081942801099482</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.135611382208975</v>
+        <v>9.136182154597519</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.299504848040591</v>
+        <v>9.299947449650309</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.39101212233275</v>
+        <v>9.39135664944896</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.409172778343631</v>
+        <v>9.409458987030682</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.492204480771328</v>
+        <v>9.492444880487591</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606190835634155</v>
+        <v>9.606102827029201</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59570794317805</v>
+        <v>9.595501223075273</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.610264636052566</v>
+        <v>9.60986163519577</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.60425537664905</v>
+        <v>9.603601700401546</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.584007557547039</v>
+        <v>9.583260646147224</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.618048268477317</v>
+        <v>9.617211972702304</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.487066732838846</v>
+        <v>9.486335215880583</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.41959374366466</v>
+        <v>9.418902275870682</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.276815522811322</v>
+        <v>9.276433051827745</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.182534054598896</v>
+        <v>9.182295260176</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077709415875976</v>
+        <v>9.077788430597062</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052067733997742</v>
+        <v>9.052237958402149</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048625287257918</v>
+        <v>9.048760399403072</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024263870461541</v>
+        <v>9.024466081042968</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.003980132669973</v>
+        <v>9.004182369552495</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013764473649621</v>
+        <v>9.013859314238132</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038702644895237</v>
+        <v>9.03866014375823</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057111710863797</v>
+        <v>9.056998236021224</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060794564286745</v>
+        <v>9.060800486630535</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04816630663356</v>
+        <v>9.051562618872222</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039959231865407</v>
+        <v>9.041460596581434</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.049224059671655</v>
+        <v>9.048140627412762</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.055396932693414</v>
+        <v>9.055899406594801</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.049869876791437</v>
+        <v>9.048993924975536</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.049691057638103</v>
+        <v>9.048951110733018</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.024958956774448</v>
+        <v>9.022692500739332</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.996473657169478</v>
+        <v>8.994277122809411</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.972440379945661</v>
+        <v>8.971712788667109</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.968787687525252</v>
+        <v>8.971380167534328</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.962652179436951</v>
+        <v>8.967586413226735</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.945986526623441</v>
+        <v>8.952789500449207</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.938739377604545</v>
+        <v>8.943651214474977</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.884997470958162</v>
+        <v>8.887685386985888</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.867574141159851</v>
+        <v>8.834956253987389</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.855605270283961</v>
+        <v>8.814458783901131</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.90200904240969</v>
+        <v>8.815764835770723</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748386877834356</v>
+        <v>9.748413171890517</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723222714388957</v>
+        <v>9.723280499337491</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719953137234171</v>
+        <v>9.720032703967821</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698756830955547</v>
+        <v>9.698883573536774</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703284321723928</v>
+        <v>9.703409789348424</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696549820045972</v>
+        <v>9.696673719283497</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69236664534616</v>
+        <v>9.692491207644936</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706386199134316</v>
+        <v>9.706514012776738</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718704085726948</v>
+        <v>9.718853418973762</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.72588531207381</v>
+        <v>9.726000428296929</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734523158169496</v>
+        <v>9.734639692957771</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710939138433345</v>
+        <v>9.711053239613712</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666552098829136</v>
+        <v>9.666666037273771</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632113660889534</v>
+        <v>9.632255838977628</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599443599443077</v>
+        <v>9.599538328358225</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561720018549421</v>
+        <v>9.561803294936317</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502733675296588</v>
+        <v>9.502915514272352</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430379712216185</v>
+        <v>9.430632009019018</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354662432685384</v>
+        <v>9.35489832456885</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28707835438307</v>
+        <v>9.287324921401821</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265093993906239</v>
+        <v>9.265258935328369</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278235282268758</v>
+        <v>9.278357373861613</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240311946828449</v>
+        <v>9.24019263309803</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172483615262294</v>
+        <v>9.172239782461855</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109481043629776</v>
+        <v>9.109107983173901</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.015803309752764</v>
+        <v>9.015355616552087</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945908614816402</v>
+        <v>8.945359471273244</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.943996457994126</v>
+        <v>8.943316579017399</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.954520890077747</v>
+        <v>8.953745466992009</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.081942801099482</v>
+        <v>9.080865804373127</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.136182154597519</v>
+        <v>9.135056541508524</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.299947449650309</v>
+        <v>9.299074275286102</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.39135664944896</v>
+        <v>9.390676853428905</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.409458987030682</v>
+        <v>9.408894006243134</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.492444880487591</v>
+        <v>9.491970075706934</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606102827029201</v>
+        <v>9.606275716491945</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.595501223075273</v>
+        <v>9.595908082445597</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.60986163519577</v>
+        <v>9.610655693406528</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.603601700401546</v>
+        <v>9.604890570900597</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.583260646147224</v>
+        <v>9.584733524726742</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.617211972702304</v>
+        <v>9.618861320482928</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.486335215880583</v>
+        <v>9.48777846050913</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.418902275870682</v>
+        <v>9.420266809186831</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.276433051827745</v>
+        <v>9.27718813909318</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.182295260176</v>
+        <v>9.182766887435681</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077788430597062</v>
+        <v>9.077632787261887</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052237958402149</v>
+        <v>9.051902141807849</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048760399403072</v>
+        <v>9.048493794956965</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024466081042968</v>
+        <v>9.024066887818483</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.004182369552495</v>
+        <v>9.003782936672678</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013859314238132</v>
+        <v>9.013671785448675</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03866014375823</v>
+        <v>9.038743756587506</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.056998236021224</v>
+        <v>9.057222199047867</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060800486630535</v>
+        <v>9.060789285886074</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051562618872222</v>
+        <v>9.048140438930258</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041460596581434</v>
+        <v>9.039891973553953</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048140627412762</v>
+        <v>9.049077045778297</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.055899406594801</v>
+        <v>9.057594369766205</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.048993924975536</v>
+        <v>9.052112557576649</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.048951110733018</v>
+        <v>9.051925244187499</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.022692500739332</v>
+        <v>9.027052330963924</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.994277122809411</v>
+        <v>8.999051490621191</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.971712788667109</v>
+        <v>8.975261412878979</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.971380167534328</v>
+        <v>8.971517991529876</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967586413226735</v>
+        <v>8.965418050199023</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.952789500449207</v>
+        <v>8.949320906657505</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.943651214474977</v>
+        <v>8.941268606801287</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.887685386985888</v>
+        <v>8.891414662956723</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.834956253987389</v>
+        <v>8.876925263432046</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.814458783901131</v>
+        <v>8.867191307421077</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.815764835770723</v>
+        <v>8.903474621546597</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748413171890517</v>
+        <v>9.74840021263879</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723280499337491</v>
+        <v>9.723252019143452</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720032703967821</v>
+        <v>9.719993486827061</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698883573536774</v>
+        <v>9.698821105791453</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703409789348424</v>
+        <v>9.703347950231475</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696673719283497</v>
+        <v>9.696612653271313</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692491207644936</v>
+        <v>9.69242981557295</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706514012776738</v>
+        <v>9.706451020024844</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718853418973762</v>
+        <v>9.718779815332297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726000428296929</v>
+        <v>9.725943687970688</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734639692957771</v>
+        <v>9.734582253418768</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711053239613712</v>
+        <v>9.710996999375721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666666037273771</v>
+        <v>9.666609870719805</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632255838977628</v>
+        <v>9.632185751224812</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599538328358225</v>
+        <v>9.599491627233682</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561803294936317</v>
+        <v>9.561762247198645</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502915514272352</v>
+        <v>9.502825890229539</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430632009019018</v>
+        <v>9.430507643738146</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35489832456885</v>
+        <v>9.354782048891167</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287324921401821</v>
+        <v>9.28720337343001</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265258935328369</v>
+        <v>9.265177559534122</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278357373861613</v>
+        <v>9.278297087736048</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24019263309803</v>
+        <v>9.240251352749203</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172239782461855</v>
+        <v>9.172359859025775</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109107983173901</v>
+        <v>9.109291733038058</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.015355616552087</v>
+        <v>9.015576139975822</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945359471273244</v>
+        <v>8.945629984546146</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.943316579017399</v>
+        <v>8.943651528355598</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.953745466992009</v>
+        <v>8.954127628395369</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.080865804373127</v>
+        <v>9.081396676998414</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.135056541508524</v>
+        <v>9.135611382208975</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.299074275286102</v>
+        <v>9.299504848040591</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.390676853428905</v>
+        <v>9.39101212233275</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408894006243134</v>
+        <v>9.409172778343631</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491970075706934</v>
+        <v>9.492204480771328</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606275716491945</v>
+        <v>9.606190835634155</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.595908082445597</v>
+        <v>9.59570794317805</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.610655693406528</v>
+        <v>9.610264636052566</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.604890570900597</v>
+        <v>9.60425537664905</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.584733524726742</v>
+        <v>9.584007557547039</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.618861320482928</v>
+        <v>9.618048268477317</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.48777846050913</v>
+        <v>9.487066732838846</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.420266809186831</v>
+        <v>9.41959374366466</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.27718813909318</v>
+        <v>9.276815522811322</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.182766887435681</v>
+        <v>9.182534054598896</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077632787261887</v>
+        <v>9.077709415875976</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051902141807849</v>
+        <v>9.052067733997742</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048493794956965</v>
+        <v>9.048625287257918</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024066887818483</v>
+        <v>9.024263870461541</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.003782936672678</v>
+        <v>9.003980132669973</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013671785448675</v>
+        <v>9.013764473649621</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038743756587506</v>
+        <v>9.038702644895237</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057222199047867</v>
+        <v>9.057111710863797</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060789285886074</v>
+        <v>9.060794564286745</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048140438930258</v>
+        <v>9.051516025714783</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039891973553953</v>
+        <v>9.041382769724933</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.049077045778297</v>
+        <v>9.047990749814041</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.057594369766205</v>
+        <v>9.057751039718143</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.052112557576649</v>
+        <v>9.050819104503125</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.051925244187499</v>
+        <v>9.050208187502658</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.027052330963924</v>
+        <v>9.022642737117817</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.999051490621191</v>
+        <v>8.99412270670317</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.975261412878979</v>
+        <v>8.97200321938513</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.971517991529876</v>
+        <v>8.970955256495172</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.965418050199023</v>
+        <v>8.966455606154303</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.949320906657505</v>
+        <v>8.951225339756492</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.941268606801287</v>
+        <v>8.938930942871345</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.891414662956723</v>
+        <v>8.883465261193422</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.876925263432046</v>
+        <v>8.831260323858134</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.867191307421077</v>
+        <v>8.80661367588813</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.903474621546597</v>
+        <v>8.825594001415176</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74840021263879</v>
+        <v>9.748425771233451</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723252019143452</v>
+        <v>9.723308189285325</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.719993486827061</v>
+        <v>9.72007083566084</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698821105791453</v>
+        <v>9.698944309320707</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703347950231475</v>
+        <v>9.703469913487362</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696612653271313</v>
+        <v>9.696733091580409</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69242981557295</v>
+        <v>9.692550895575099</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706451020024844</v>
+        <v>9.70657525362809</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718779815332297</v>
+        <v>9.718924984885851</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.725943687970688</v>
+        <v>9.726055600811959</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734582253418768</v>
+        <v>9.734695545379449</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.710996999375721</v>
+        <v>9.7111079262727</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666609870719805</v>
+        <v>9.66672066443973</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632185751224812</v>
+        <v>9.63232400638323</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599491627233682</v>
+        <v>9.599583756987709</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561762247198645</v>
+        <v>9.56184321058835</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.502825890229539</v>
+        <v>9.503002655017312</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430507643738146</v>
+        <v>9.430752954935368</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.354782048891167</v>
+        <v>9.355011397567321</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.28720337343001</v>
+        <v>9.287443140740189</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265177559534122</v>
+        <v>9.265338205702101</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278297087736048</v>
+        <v>9.278416194812433</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240251352749203</v>
+        <v>9.24013570309943</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172359859025775</v>
+        <v>9.172123224718872</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.109291733038058</v>
+        <v>9.108929553633281</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.015576139975822</v>
+        <v>9.01514145329225</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945629984546146</v>
+        <v>8.945096726964064</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.943651528355598</v>
+        <v>8.942991184912565</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.954127628395369</v>
+        <v>8.953373943564912</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.081396676998414</v>
+        <v>9.080349554802936</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.135611382208975</v>
+        <v>9.134516976402541</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.299504848040591</v>
+        <v>9.298655249513949</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.39101212233275</v>
+        <v>9.390350476466931</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.409172778343631</v>
+        <v>9.408622387634464</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.492204480771328</v>
+        <v>9.491741448358292</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606190835634155</v>
+        <v>9.606357625985925</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59570794317805</v>
+        <v>9.596101944874082</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.610264636052566</v>
+        <v>9.611035326908198</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.60425537664905</v>
+        <v>9.605508053518246</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.584007557547039</v>
+        <v>9.585439413068617</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.618048268477317</v>
+        <v>9.619652081364984</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.487066732838846</v>
+        <v>9.488471187906846</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.41959374366466</v>
+        <v>9.420922193118908</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.276815522811322</v>
+        <v>9.277551272800968</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.182534054598896</v>
+        <v>9.18299397605424</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077709415875976</v>
+        <v>9.077558439865237</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.052067733997742</v>
+        <v>9.05174099661302</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048625287257918</v>
+        <v>9.048365780325593</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.024263870461541</v>
+        <v>9.023874935044942</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.003980132669973</v>
+        <v>9.00359059833664</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013764473649621</v>
+        <v>9.01358118059952</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038702644895237</v>
+        <v>9.038783543878449</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057111710863797</v>
+        <v>9.057329815768071</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060794564286745</v>
+        <v>9.060784605965464</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051516025714783</v>
+        <v>9.048115436393051</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041382769724933</v>
+        <v>9.039826538607477</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047990749814041</v>
+        <v>9.048933718206813</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.057751039718143</v>
+        <v>9.0592954390203</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.050819104503125</v>
+        <v>9.053764523158254</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.050208187502658</v>
+        <v>9.053560729821925</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.022642737117817</v>
+        <v>9.028391023829855</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>8.99412270670317</v>
+        <v>9.000819723071348</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.97200321938513</v>
+        <v>8.97718651640513</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.970955256495172</v>
+        <v>8.973254604693473</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.966455606154303</v>
+        <v>8.967120908494348</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.951225339756492</v>
+        <v>8.951474589765251</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.938930942871345</v>
+        <v>8.942549621653757</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.883465261193422</v>
+        <v>8.895825473272366</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.831260323858134</v>
+        <v>8.882980979750776</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.80661367588813</v>
+        <v>8.87353856699754</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.825594001415176</v>
+        <v>8.896190417268969</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748425771233451</v>
+        <v>9.74843802545459</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723308189285325</v>
+        <v>9.723335121423498</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72007083566084</v>
+        <v>9.720107926345264</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698944309320707</v>
+        <v>9.699003384166021</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703469913487362</v>
+        <v>9.703528392992601</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696733091580409</v>
+        <v>9.696790839641251</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692550895575099</v>
+        <v>9.692608949326342</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70657525362809</v>
+        <v>9.706634814637342</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718924984885851</v>
+        <v>9.71899459648967</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726055600811959</v>
+        <v>9.726109269584825</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734695545379449</v>
+        <v>9.734749875541036</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.7111079262727</v>
+        <v>9.711161122823224</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66672066443973</v>
+        <v>9.666773814605376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63232400638323</v>
+        <v>9.632390331238589</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599583756987709</v>
+        <v>9.599627964386162</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56184321058835</v>
+        <v>9.561882040327013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503002655017312</v>
+        <v>9.503087414185316</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430752954935368</v>
+        <v>9.430870620417839</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355011397567321</v>
+        <v>9.355121398262456</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287443140740189</v>
+        <v>9.287558166205603</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265338205702101</v>
+        <v>9.26541545081621</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278416194812433</v>
+        <v>9.278473602282052</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24013570309943</v>
+        <v>9.24008048297198</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172123224718872</v>
+        <v>9.172010034142673</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.108929553633281</v>
+        <v>9.108756217619167</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01514145329225</v>
+        <v>9.014933380139766</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945096726964064</v>
+        <v>8.944841423121076</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942991184912565</v>
+        <v>8.942674944675757</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.953373943564912</v>
+        <v>8.953012621071645</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.080349554802936</v>
+        <v>9.079847333834937</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.134516976402541</v>
+        <v>9.133992066240648</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.298655249513949</v>
+        <v>9.298247314145394</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.390350476466931</v>
+        <v>9.390032644136342</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408622387634464</v>
+        <v>9.408357653438429</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491741448358292</v>
+        <v>9.491518391861685</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606357625985925</v>
+        <v>9.606436710558594</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596101944874082</v>
+        <v>9.59628981627009</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.611035326908198</v>
+        <v>9.611404026671556</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.605508053518246</v>
+        <v>9.606108552772103</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.585439413068617</v>
+        <v>9.586126041107823</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.619652081364984</v>
+        <v>9.620421452579318</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.488471187906846</v>
+        <v>9.489145662832406</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.420922193118908</v>
+        <v>9.421560579232994</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.277551272800968</v>
+        <v>9.277905277780739</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18299397605424</v>
+        <v>9.183215527559687</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077558439865237</v>
+        <v>9.077486274779435</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05174099661302</v>
+        <v>9.051584122866734</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048365780325593</v>
+        <v>9.04824110846271</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023874935044942</v>
+        <v>9.023687823835612</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.00359059833664</v>
+        <v>9.003402943042969</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01358118059952</v>
+        <v>9.01349259277444</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038783543878449</v>
+        <v>9.038822067901807</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057329815768071</v>
+        <v>9.057434670437205</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060784605965464</v>
+        <v>9.060780482499533</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048115436393051</v>
+        <v>9.048091259759467</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039826538607477</v>
+        <v>9.039762856070691</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048933718206813</v>
+        <v>9.04879394350359</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.0592954390203</v>
+        <v>9.060578052228127</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.053764523158254</v>
+        <v>9.054920734367567</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.053560729821925</v>
+        <v>9.054716632526205</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.028391023829855</v>
+        <v>9.029112585319924</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.000819723071348</v>
+        <v>9.001876444674934</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.97718651640513</v>
+        <v>8.978328117479069</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.973254604693473</v>
+        <v>8.974130379530747</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967120908494348</v>
+        <v>8.967900530865428</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.951474589765251</v>
+        <v>8.952590926993839</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.942549621653757</v>
+        <v>8.942723054975421</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.895825473272366</v>
+        <v>8.898498146918127</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.882980979750776</v>
+        <v>8.886343150419101</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.87353856699754</v>
+        <v>8.875932750300349</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.896190417268969</v>
+        <v>8.885564441501645</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74843802545459</v>
+        <v>9.748449948541872</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723335121423498</v>
+        <v>9.723361326437535</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720107926345264</v>
+        <v>9.720144018067593</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699003384166021</v>
+        <v>9.699060865265764</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703528392992601</v>
+        <v>9.703585294414337</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696790839641251</v>
+        <v>9.696847029197432</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692608949326342</v>
+        <v>9.692665435084688</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706634814637342</v>
+        <v>9.706692763965732</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71899459648967</v>
+        <v>9.719062332716556</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726109269584825</v>
+        <v>9.726161495241954</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734749875541036</v>
+        <v>9.734802744814838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711161122823224</v>
+        <v>9.711212889326266</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666773814605376</v>
+        <v>9.666825546834399</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632390331238589</v>
+        <v>9.63245488719757</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599627964386162</v>
+        <v>9.599670999102884</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561882040327013</v>
+        <v>9.561919827848685</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503087414185316</v>
+        <v>9.503169888020686</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430870620417839</v>
+        <v>9.430985136980642</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355121398262456</v>
+        <v>9.35522845005617</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287558166205603</v>
+        <v>9.287670125387715</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26541545081621</v>
+        <v>9.265490746841561</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278473602282052</v>
+        <v>9.278529645624785</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24008048297198</v>
+        <v>9.240026897568463</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172010034142673</v>
+        <v>9.171900067631164</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.108756217619167</v>
+        <v>9.10858776099564</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014933380139766</v>
+        <v>9.014731142053995</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.944841423121076</v>
+        <v>8.944593249436164</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942674944675757</v>
+        <v>8.942367479020323</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.953012621071645</v>
+        <v>8.952661086031974</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.079847333834937</v>
+        <v>9.079358578725412</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.133992066240648</v>
+        <v>9.133481223460453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.298247314145394</v>
+        <v>9.297850036264759</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.390032644136342</v>
+        <v>9.389723026882965</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408357653438429</v>
+        <v>9.408099547747012</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491518391861685</v>
+        <v>9.491300708868224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606436710558594</v>
+        <v>9.606513107471972</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59628981627009</v>
+        <v>9.596471965576253</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.611404026671556</v>
+        <v>9.61176225533201</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.606108552772103</v>
+        <v>9.606692757667595</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.586126041107823</v>
+        <v>9.58679418364823</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.620421452579318</v>
+        <v>9.621170287773399</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.489145662832406</v>
+        <v>9.489802594515487</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.421560579232994</v>
+        <v>9.422182616708323</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.277905277780739</v>
+        <v>9.278250490690324</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.183215527559687</v>
+        <v>9.183431739380381</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077486274779435</v>
+        <v>9.077416198664832</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051584122866734</v>
+        <v>9.051431354076922</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04824110846271</v>
+        <v>9.048119651286699</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023687823835612</v>
+        <v>9.023505375062623</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.003402943042969</v>
+        <v>9.00321980429068</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01349259277444</v>
+        <v>9.013405958239456</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038822067901807</v>
+        <v>9.038859386166111</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057434670437205</v>
+        <v>9.057536867039779</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060780482499533</v>
+        <v>9.06077687660969</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048091259759467</v>
+        <v>9.048067871970987</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039762856070691</v>
+        <v>9.039700858510097</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04879394350359</v>
+        <v>9.048657594395287</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.060578052228127</v>
+        <v>9.0630354530761</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.054920734367567</v>
+        <v>9.057483232698161</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.054716632526205</v>
+        <v>9.057287167611907</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.029112585319924</v>
+        <v>9.031985262918228</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.001876444674934</v>
+        <v>9.005010206664636</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.978328117479069</v>
+        <v>8.981833992869966</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.974130379530747</v>
+        <v>8.977746127695831</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.967900530865428</v>
+        <v>8.971688977626588</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.952590926993839</v>
+        <v>8.956969505000313</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.942723054975421</v>
+        <v>8.946757527807604</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.898498146918127</v>
+        <v>8.905823865913458</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.886343150419101</v>
+        <v>8.896232158436288</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.875932750300349</v>
+        <v>8.888144200780964</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.885564441501645</v>
+        <v>8.903399333295697</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748449948541872</v>
+        <v>9.748461553737453</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723361326437535</v>
+        <v>9.723386833378523</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720144018067593</v>
+        <v>9.720179150640529</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699060865265764</v>
+        <v>9.699116816237879</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703585294414337</v>
+        <v>9.703640680761007</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696847029197432</v>
+        <v>9.696901722481808</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692665435084688</v>
+        <v>9.692720415510681</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706692763965732</v>
+        <v>9.706749166137195</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719062332716556</v>
+        <v>9.719128268305957</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726161495241954</v>
+        <v>9.726212335195228</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734802744814838</v>
+        <v>9.734854211319121</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711212889326266</v>
+        <v>9.711263282659081</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666825546834399</v>
+        <v>9.6668759170848</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63245488719757</v>
+        <v>9.632517744042936</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599670999102884</v>
+        <v>9.599712907149634</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561919827848685</v>
+        <v>9.561956614537548</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503169888020686</v>
+        <v>9.503250167654571</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430985136980642</v>
+        <v>9.431096629209282</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35522845005617</v>
+        <v>9.355332669836075</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287670125387715</v>
+        <v>9.287779139175624</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265490746841561</v>
+        <v>9.265564166202248</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278529645624785</v>
+        <v>9.278584371981713</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240026897568463</v>
+        <v>9.239974876046507</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171900067631164</v>
+        <v>9.171793190042273</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.10858776099564</v>
+        <v>9.108423981419593</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014731142053995</v>
+        <v>9.014534497984613</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.944593249436164</v>
+        <v>8.944351912553435</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942367479020323</v>
+        <v>8.942068429246399</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.952661086031974</v>
+        <v>8.952318946964631</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.079358578725412</v>
+        <v>9.078882756358635</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.133481223460453</v>
+        <v>9.13298389141716</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.297850036264759</v>
+        <v>9.297463005112398</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.389723026882965</v>
+        <v>9.389421311795225</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408099547747012</v>
+        <v>9.40784782703826</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491300708868224</v>
+        <v>9.491088211021028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606513107471972</v>
+        <v>9.606586945500451</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596471965576253</v>
+        <v>9.596648646083661</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.61176225533201</v>
+        <v>9.612110449935471</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.606692757667595</v>
+        <v>9.607261320548584</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.58679418364823</v>
+        <v>9.587444574633817</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.621170287773399</v>
+        <v>9.621899395904308</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.489802594515487</v>
+        <v>9.490442656059304</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.422182616708323</v>
+        <v>9.422788922277057</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.278250490690324</v>
+        <v>9.278587232016472</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.183431739380381</v>
+        <v>9.183642799815303</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077416198664832</v>
+        <v>9.077348123366608</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051431354076922</v>
+        <v>9.051282532233991</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048119651286699</v>
+        <v>9.048001287114515</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023505375062623</v>
+        <v>9.023327418230515</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.00321980429068</v>
+        <v>9.003041023241128</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013405958239456</v>
+        <v>9.013321215743964</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038859386166111</v>
+        <v>9.038895552815047</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057536867039779</v>
+        <v>9.057636504460337</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.06077687660969</v>
+        <v>9.060773752300767</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048067871970987</v>
+        <v>9.04804523802807</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039700858510097</v>
+        <v>9.039640481805565</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048657594395287</v>
+        <v>9.048524549447489</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.0630354530761</v>
+        <v>9.065339116969595</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.057483232698161</v>
+        <v>9.05986801528304</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.057287167611907</v>
+        <v>9.059553031554366</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.031985262918228</v>
+        <v>9.034545086614575</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.005010206664636</v>
+        <v>9.007848042435363</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.981833992869966</v>
+        <v>8.985044397968299</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.977746127695831</v>
+        <v>8.981060844858076</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.971688977626588</v>
+        <v>8.975171029256185</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.956969505000313</v>
+        <v>8.960998773760302</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.946757527807604</v>
+        <v>8.950457902224539</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.905823865913458</v>
+        <v>8.912432876574492</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.896232158436288</v>
+        <v>8.904851178249206</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.888144200780964</v>
+        <v>8.898311189211586</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.903399333295697</v>
+        <v>8.915360187507058</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748461553737453</v>
+        <v>9.748425771233451</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723386833378523</v>
+        <v>9.723308189285325</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720179150640529</v>
+        <v>9.72007083566084</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699116816237879</v>
+        <v>9.698944309320707</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703640680761007</v>
+        <v>9.703469913487362</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696901722481808</v>
+        <v>9.696733091580409</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692720415510681</v>
+        <v>9.692550895575099</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706749166137195</v>
+        <v>9.70657525362809</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719128268305957</v>
+        <v>9.718924984885851</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726212335195228</v>
+        <v>9.726055600811959</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734854211319121</v>
+        <v>9.734695545379449</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711263282659081</v>
+        <v>9.7111079262727</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.6668759170848</v>
+        <v>9.66672066443973</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632517744042936</v>
+        <v>9.63232400638323</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599712907149634</v>
+        <v>9.599583756987709</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561956614537548</v>
+        <v>9.56184321058835</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503250167654571</v>
+        <v>9.503002655017312</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431096629209282</v>
+        <v>9.430752954935368</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355332669836075</v>
+        <v>9.355011397567321</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287779139175624</v>
+        <v>9.287443140740189</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265564166202248</v>
+        <v>9.265338205702101</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278584371981713</v>
+        <v>9.278416194812433</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239974876046507</v>
+        <v>9.24013570309943</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171793190042273</v>
+        <v>9.172123224718872</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.108423981419593</v>
+        <v>9.108929553633281</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014534497984613</v>
+        <v>9.01514145329225</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.944351912553435</v>
+        <v>8.945096726964064</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942068429246399</v>
+        <v>8.942991184912565</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.952318946964631</v>
+        <v>8.953373943564912</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.078882756358635</v>
+        <v>9.080349554802936</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.13298389141716</v>
+        <v>9.134516976402541</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.297463005112398</v>
+        <v>9.298655249513949</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.389421311795225</v>
+        <v>9.390350476466931</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.40784782703826</v>
+        <v>9.408622387634464</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491088211021028</v>
+        <v>9.491741448358292</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606586945500451</v>
+        <v>9.606357625985925</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596648646083661</v>
+        <v>9.596101944874082</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.612110449935471</v>
+        <v>9.611035326908198</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.607261320548584</v>
+        <v>9.605508053518246</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.587444574633817</v>
+        <v>9.585439413068617</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.621899395904308</v>
+        <v>9.619652081364984</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.490442656059304</v>
+        <v>9.488471187906846</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.422788922277057</v>
+        <v>9.420922193118908</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.278587232016472</v>
+        <v>9.277551272800968</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.183642799815303</v>
+        <v>9.18299397605424</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077348123366608</v>
+        <v>9.077558439865237</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051282532233991</v>
+        <v>9.05174099661302</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048001287114515</v>
+        <v>9.048365780325593</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023327418230515</v>
+        <v>9.023874935044942</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.003041023241128</v>
+        <v>9.00359059833664</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013321215743964</v>
+        <v>9.01358118059952</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038895552815047</v>
+        <v>9.038783543878449</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057636504460337</v>
+        <v>9.057329815768071</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060773752300767</v>
+        <v>9.060784605965464</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04804523802807</v>
+        <v>9.051427458056281</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039640481805565</v>
+        <v>9.041233547068593</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048524549447489</v>
+        <v>9.047702338024463</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.065339116969595</v>
+        <v>9.058957614718082</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.05986801528304</v>
+        <v>9.055263236290294</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.059553031554366</v>
+        <v>9.05480885559628</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.034545086614575</v>
+        <v>9.02722155852044</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.007848042435363</v>
+        <v>9.0000761897155</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.985044397968299</v>
+        <v>8.978184109329584</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.981060844858076</v>
+        <v>8.978425312432259</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.975171029256185</v>
+        <v>8.974294823050272</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.960998773760302</v>
+        <v>8.960044221373051</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.950457902224539</v>
+        <v>8.946805893304049</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.912432876574492</v>
+        <v>8.897700415438718</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.904851178249206</v>
+        <v>8.853682288356985</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.898311189211586</v>
+        <v>8.839203357538114</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.915360187507058</v>
+        <v>8.870120377339486</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>8.994305377339487</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748425771233451</v>
+        <v>9.748472853586735</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723308189285325</v>
+        <v>9.723411669770465</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72007083566084</v>
+        <v>9.720213361789371</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.698944309320707</v>
+        <v>9.699171297359795</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703469913487362</v>
+        <v>9.703694611731718</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696733091580409</v>
+        <v>9.696954978458345</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692550895575099</v>
+        <v>9.692773949970965</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70657525362809</v>
+        <v>9.706804082277703</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.718924984885851</v>
+        <v>9.71919247407993</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726055600811959</v>
+        <v>9.726261843852164</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734695545379449</v>
+        <v>9.734904330130856</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.7111079262727</v>
+        <v>9.711312356723305</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66672066443973</v>
+        <v>9.666924978410226</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63232400638323</v>
+        <v>9.632578967937153</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599583756987709</v>
+        <v>9.599753732164146</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56184321058835</v>
+        <v>9.561992439616434</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503002655017312</v>
+        <v>9.503328339439806</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430752954935368</v>
+        <v>9.431205215210387</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355011397567321</v>
+        <v>9.355434168399254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287443140740189</v>
+        <v>9.287885322191624</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265338205702101</v>
+        <v>9.265635777801386</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278416194812433</v>
+        <v>9.278637826399109</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24013570309943</v>
+        <v>9.239924351566724</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172123224718872</v>
+        <v>9.171689273650239</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.108929553633281</v>
+        <v>9.108264687542675</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.01514145329225</v>
+        <v>9.014343219928637</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.945096726964064</v>
+        <v>8.944117134931309</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942991184912565</v>
+        <v>8.941777455867994</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.953373943564912</v>
+        <v>8.951985832946621</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.080349554802936</v>
+        <v>9.07841936132705</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.134516976402541</v>
+        <v>9.132499542381364</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.298655249513949</v>
+        <v>9.297085830690886</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.390350476466931</v>
+        <v>9.389127201572624</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408622387634464</v>
+        <v>9.407602259445735</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491741448358292</v>
+        <v>9.490880718464892</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606357625985925</v>
+        <v>9.60665834556278</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596101944874082</v>
+        <v>9.596820096542089</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.611035326908198</v>
+        <v>9.612449023674451</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.605508053518246</v>
+        <v>9.607814859496695</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.585439413068617</v>
+        <v>9.588077909797555</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.619652081364984</v>
+        <v>9.622609544116587</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.488471187906846</v>
+        <v>9.491066486702177</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.420922193118908</v>
+        <v>9.423380082213436</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.277551272800968</v>
+        <v>9.278915807021788</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18299397605424</v>
+        <v>9.183848888545654</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077558439865237</v>
+        <v>9.077281965563419</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05174099661302</v>
+        <v>9.051137507281286</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048365780325593</v>
+        <v>9.04788590027122</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023874935044942</v>
+        <v>9.023153790968948</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.00359059833664</v>
+        <v>9.002866448291925</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01358118059952</v>
+        <v>9.013238306414459</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038783543878449</v>
+        <v>9.038930618865955</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057329815768071</v>
+        <v>9.057733676788548</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060784605965464</v>
+        <v>9.060771076222274</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051427458056281</v>
+        <v>9.048023324855933</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041233547068593</v>
+        <v>9.039581664955945</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047702338024463</v>
+        <v>9.048394692744754</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.058957614718082</v>
+        <v>9.065145146943093</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.055263236290294</v>
+        <v>9.062456440150097</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.05480885559628</v>
+        <v>9.062673829005814</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.02722155852044</v>
+        <v>9.03853869758494</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.0000761897155</v>
+        <v>9.012992824668645</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.978184109329584</v>
+        <v>8.991430784922677</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.978425312432259</v>
+        <v>8.987736369878204</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.974294823050272</v>
+        <v>8.982643010925575</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.960044221373051</v>
+        <v>8.969612144235583</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.946805893304049</v>
+        <v>8.960493376415485</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.897700415438718</v>
+        <v>8.926337515260141</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.853682288356985</v>
+        <v>8.923191972284336</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.839203357538114</v>
+        <v>8.92124601974497</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.870120377339486</v>
+        <v>8.950396400526408</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>8.994305377339487</v>
+        <v>9.074581400526409</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748472853586735</v>
+        <v>9.74843802545459</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723411669770465</v>
+        <v>9.723335121423498</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720213361789371</v>
+        <v>9.720107926345264</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699171297359795</v>
+        <v>9.699003384166021</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703694611731718</v>
+        <v>9.703528392992601</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696954978458345</v>
+        <v>9.696790839641251</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692773949970965</v>
+        <v>9.692608949326342</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706804082277703</v>
+        <v>9.706634814637342</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71919247407993</v>
+        <v>9.71899459648967</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726261843852164</v>
+        <v>9.726109269584825</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734904330130856</v>
+        <v>9.734749875541036</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711312356723305</v>
+        <v>9.711161122823224</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666924978410226</v>
+        <v>9.666773814605376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632578967937153</v>
+        <v>9.632390331238589</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599753732164146</v>
+        <v>9.599627964386162</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561992439616434</v>
+        <v>9.561882040327013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503328339439806</v>
+        <v>9.503087414185316</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431205215210387</v>
+        <v>9.430870620417839</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355434168399254</v>
+        <v>9.355121398262456</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287885322191624</v>
+        <v>9.287558166205603</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265635777801386</v>
+        <v>9.26541545081621</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278637826399109</v>
+        <v>9.278473602282052</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239924351566724</v>
+        <v>9.24008048297198</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171689273650239</v>
+        <v>9.172010034142673</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.108264687542675</v>
+        <v>9.108756217619167</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014343219928637</v>
+        <v>9.014933380139766</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.944117134931309</v>
+        <v>8.944841423121076</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.941777455867994</v>
+        <v>8.942674944675757</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.951985832946621</v>
+        <v>8.953012621071645</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.07841936132705</v>
+        <v>9.079847333834937</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.132499542381364</v>
+        <v>9.133992066240648</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.297085830690886</v>
+        <v>9.298247314145394</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.389127201572624</v>
+        <v>9.390032644136342</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.407602259445735</v>
+        <v>9.408357653438429</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490880718464892</v>
+        <v>9.491518391861685</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60665834556278</v>
+        <v>9.606436710558594</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596820096542089</v>
+        <v>9.59628981627009</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.612449023674451</v>
+        <v>9.611404026671556</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.607814859496695</v>
+        <v>9.606108552772103</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.588077909797555</v>
+        <v>9.586126041107823</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.622609544116587</v>
+        <v>9.620421452579318</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.491066486702177</v>
+        <v>9.489145662832406</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.423380082213436</v>
+        <v>9.421560579232994</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.278915807021788</v>
+        <v>9.277905277780739</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.183848888545654</v>
+        <v>9.183215527559687</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077281965563419</v>
+        <v>9.077486274779435</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051137507281286</v>
+        <v>9.051584122866734</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04788590027122</v>
+        <v>9.04824110846271</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023153790968948</v>
+        <v>9.023687823835612</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002866448291925</v>
+        <v>9.003402943042969</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013238306414459</v>
+        <v>9.01349259277444</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038930618865955</v>
+        <v>9.038822067901807</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057733676788548</v>
+        <v>9.057434670437205</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060771076222274</v>
+        <v>9.060780482499533</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048023324855933</v>
+        <v>9.051385341540994</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039581664955945</v>
+        <v>9.041161981240457</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048394692744754</v>
+        <v>9.047563528289233</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.065145146943093</v>
+        <v>9.058764205775731</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.062456440150097</v>
+        <v>9.058030236846276</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.062673829005814</v>
+        <v>9.058160471016159</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.03853869758494</v>
+        <v>9.031620972439423</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.012992824668645</v>
+        <v>9.005310955527314</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.991430784922677</v>
+        <v>8.983686982575058</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.987736369878204</v>
+        <v>8.985611145537062</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.982643010925575</v>
+        <v>8.982348696657095</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.969612144235583</v>
+        <v>8.969272451766297</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.960493376415485</v>
+        <v>8.957549200210085</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.926337515260141</v>
+        <v>8.913099354448782</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.923191972284336</v>
+        <v>8.87497307613847</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.92124601974497</v>
+        <v>8.869193694383595</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.950396400526408</v>
+        <v>8.915083914621102</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.074581400526409</v>
+        <v>9.039268914621102</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74843802545459</v>
+        <v>9.748483859983594</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723335121423498</v>
+        <v>9.723435861709337</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720107926345264</v>
+        <v>9.720246687286988</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699003384166021</v>
+        <v>9.699224365784776</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703528392992601</v>
+        <v>9.703747143930647</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696790839641251</v>
+        <v>9.697006853033894</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692608949326342</v>
+        <v>9.692826094751858</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706634814637342</v>
+        <v>9.706857570335982</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.71899459648967</v>
+        <v>9.719255017196353</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726109269584825</v>
+        <v>9.726310072809829</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734749875541036</v>
+        <v>9.734953153482028</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711161122823224</v>
+        <v>9.711360162636968</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666773814605376</v>
+        <v>9.666972781145882</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632390331238589</v>
+        <v>9.632638621654015</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599627964386162</v>
+        <v>9.59979351556116</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561882040327013</v>
+        <v>9.562027340286056</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503087414185316</v>
+        <v>9.503404485259818</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430870620417839</v>
+        <v>9.431311007026949</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355121398262456</v>
+        <v>9.355533050843466</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287558166205603</v>
+        <v>9.287988783191729</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26541545081621</v>
+        <v>9.26570564723095</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278473602282052</v>
+        <v>9.278690051939691</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.24008048297198</v>
+        <v>9.239875261015792</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.172010034142673</v>
+        <v>9.171588197645722</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.108756217619167</v>
+        <v>9.10810969827701</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014933380139766</v>
+        <v>9.014157092062465</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.944841423121076</v>
+        <v>8.943888653794763</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942674944675757</v>
+        <v>8.94149423734806</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.953012621071645</v>
+        <v>8.951661392284054</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.079847333834937</v>
+        <v>9.077967914158474</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.133992066240648</v>
+        <v>9.132027675690072</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.298247314145394</v>
+        <v>9.296718142474667</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.390032644136342</v>
+        <v>9.388840413569586</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408357653438429</v>
+        <v>9.407362624078255</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491518391861685</v>
+        <v>9.490678059386296</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606436710558594</v>
+        <v>9.606727421299377</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59628981627009</v>
+        <v>9.596986542177881</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.611404026671556</v>
+        <v>9.612778367485381</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.606108552772103</v>
+        <v>9.608353960545173</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.586126041107823</v>
+        <v>9.588694849107583</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.620421452579318</v>
+        <v>9.623301460401237</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.489145662832406</v>
+        <v>9.491674693912072</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.421560579232994</v>
+        <v>9.423956654179426</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.277905277780739</v>
+        <v>9.279236506626907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.183215527559687</v>
+        <v>9.184050177113281</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077486274779435</v>
+        <v>9.077217646443961</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051584122866734</v>
+        <v>9.050996136624438</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.04824110846271</v>
+        <v>9.047773380727428</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023687823835612</v>
+        <v>9.022984338560263</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.003402943042969</v>
+        <v>9.002695934678112</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01349259277444</v>
+        <v>9.013157173652328</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038822067901807</v>
+        <v>9.038964632428621</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057434670437205</v>
+        <v>9.057828473603024</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060780482499533</v>
+        <v>9.060768817451757</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051385341540994</v>
+        <v>9.048002101180213</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041161981240457</v>
+        <v>9.039524349897672</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047563528289233</v>
+        <v>9.048267913590557</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.058764205775731</v>
+        <v>9.064955553529495</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.058030236846276</v>
+        <v>9.064720391466793</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.058160471016159</v>
+        <v>9.065404434928091</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.031620972439423</v>
+        <v>9.042076969081577</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.005310955527314</v>
+        <v>9.017303406309289</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.983686982575058</v>
+        <v>8.996425091325492</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.985611145537062</v>
+        <v>8.993536099533216</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.982348696657095</v>
+        <v>8.989227006586365</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.969272451766297</v>
+        <v>8.977278608690849</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.957549200210085</v>
+        <v>8.96945996839133</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.913099354448782</v>
+        <v>8.938656647101901</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.87497307613847</v>
+        <v>8.938988993873171</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.869193694383595</v>
+        <v>8.940259831187202</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.915083914621102</v>
+        <v>8.97563061924933</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.039268914621102</v>
+        <v>9.09981561924933</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748483859983594</v>
+        <v>9.748449948541872</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723435861709337</v>
+        <v>9.723361326437535</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720246687286988</v>
+        <v>9.720144018067593</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699224365784776</v>
+        <v>9.699060865265764</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703747143930647</v>
+        <v>9.703585294414337</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697006853033894</v>
+        <v>9.696847029197432</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692826094751858</v>
+        <v>9.692665435084688</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706857570335982</v>
+        <v>9.706692763965732</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719255017196353</v>
+        <v>9.719062332716556</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726310072809829</v>
+        <v>9.726161495241954</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734953153482028</v>
+        <v>9.734802744814838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711360162636968</v>
+        <v>9.711212889326266</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666972781145882</v>
+        <v>9.666825546834399</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632638621654015</v>
+        <v>9.63245488719757</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.59979351556116</v>
+        <v>9.599670999102884</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562027340286056</v>
+        <v>9.561919827848685</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503404485259818</v>
+        <v>9.503169888020686</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431311007026949</v>
+        <v>9.430985136980642</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355533050843466</v>
+        <v>9.35522845005617</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287988783191729</v>
+        <v>9.287670125387715</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26570564723095</v>
+        <v>9.265490746841561</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278690051939691</v>
+        <v>9.278529645624785</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239875261015792</v>
+        <v>9.240026897568463</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171588197645722</v>
+        <v>9.171900067631164</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.10810969827701</v>
+        <v>9.10858776099564</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014157092062465</v>
+        <v>9.014731142053995</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.943888653794763</v>
+        <v>8.944593249436164</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.94149423734806</v>
+        <v>8.942367479020323</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.951661392284054</v>
+        <v>8.952661086031974</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.077967914158474</v>
+        <v>9.079358578725412</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.132027675690072</v>
+        <v>9.133481223460453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.296718142474667</v>
+        <v>9.297850036264759</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.388840413569586</v>
+        <v>9.389723026882965</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.407362624078255</v>
+        <v>9.408099547747012</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490678059386296</v>
+        <v>9.491300708868224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606727421299377</v>
+        <v>9.606513107471972</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596986542177881</v>
+        <v>9.596471965576253</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.612778367485381</v>
+        <v>9.61176225533201</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.608353960545173</v>
+        <v>9.606692757667595</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.588694849107583</v>
+        <v>9.58679418364823</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.623301460401237</v>
+        <v>9.621170287773399</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.491674693912072</v>
+        <v>9.489802594515487</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.423956654179426</v>
+        <v>9.422182616708323</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.279236506626907</v>
+        <v>9.278250490690324</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184050177113281</v>
+        <v>9.183431739380381</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077217646443961</v>
+        <v>9.077416198664832</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050996136624438</v>
+        <v>9.051431354076922</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047773380727428</v>
+        <v>9.048119651286699</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022984338560263</v>
+        <v>9.023505375062623</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002695934678112</v>
+        <v>9.00321980429068</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013157173652328</v>
+        <v>9.013405958239456</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038964632428621</v>
+        <v>9.038859386166111</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057828473603024</v>
+        <v>9.057536867039779</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060768817451757</v>
+        <v>9.06077687660969</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.048002101180213</v>
+        <v>9.051344582113689</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039524349897672</v>
+        <v>9.041092339589833</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048267913590557</v>
+        <v>9.047428143002294</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.064955553529495</v>
+        <v>9.058575320178123</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.064720391466793</v>
+        <v>9.061873407368399</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.065404434928091</v>
+        <v>9.062824880210647</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.042076969081577</v>
+        <v>9.037386847350589</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.017303406309289</v>
+        <v>9.011970583187367</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.996425091325492</v>
+        <v>8.992569613196935</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.993536099533216</v>
+        <v>8.994553883037824</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.989227006586365</v>
+        <v>8.992248728988173</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.977278608690849</v>
+        <v>8.980442913342888</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.96945996839133</v>
+        <v>8.970383503860967</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.938656647101901</v>
+        <v>8.930923391488196</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.938988993873171</v>
+        <v>8.898663437717044</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.940259831187202</v>
+        <v>8.901166052292959</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.97563061924933</v>
+        <v>8.959160999144808</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.09981561924933</v>
+        <v>9.150171051835065</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748449948541872</v>
+        <v>9.748494584212139</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723361326437535</v>
+        <v>9.72345943395448</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720144018067593</v>
+        <v>9.720279161078508</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699060865265764</v>
+        <v>9.699276075741698</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703585294414337</v>
+        <v>9.703798331064981</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.696847029197432</v>
+        <v>9.697057399253735</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692665435084688</v>
+        <v>9.692876903256531</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706692763965732</v>
+        <v>9.706909685287259</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719062332716556</v>
+        <v>9.719315961382751</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726161495241954</v>
+        <v>9.726357071033929</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734802744814838</v>
+        <v>9.735000730940914</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711212889326266</v>
+        <v>9.711406748911825</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666825546834399</v>
+        <v>9.66701937308032</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63245488719757</v>
+        <v>9.632696764792692</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599670999102884</v>
+        <v>9.599832296672071</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.561919827848685</v>
+        <v>9.562061351853584</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503169888020686</v>
+        <v>9.503478682813912</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.430985136980642</v>
+        <v>9.431414111022081</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35522845005617</v>
+        <v>9.355629416928565</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287670125387715</v>
+        <v>9.288089625435937</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265490746841561</v>
+        <v>9.265773836966893</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278529645624785</v>
+        <v>9.278741089787216</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.240026897568463</v>
+        <v>9.239827544752048</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171900067631164</v>
+        <v>9.17148984767565</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.10858776099564</v>
+        <v>9.107958842118761</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014731142053995</v>
+        <v>9.013975909942076</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.944593249436164</v>
+        <v>8.943666220169499</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.942367479020323</v>
+        <v>8.941218468931897</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.952661086031974</v>
+        <v>8.951345291284571</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.079358578725412</v>
+        <v>9.077527959677365</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.133481223460453</v>
+        <v>9.131567816037469</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.297850036264759</v>
+        <v>9.296359588214377</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.389723026882965</v>
+        <v>9.388560678908249</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.408099547747012</v>
+        <v>9.407128710386008</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.491300708868224</v>
+        <v>9.490480069581698</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606513107471972</v>
+        <v>9.606794279600273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596471965576253</v>
+        <v>9.597148195628254</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.61176225533201</v>
+        <v>9.613098851519837</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.606692757667595</v>
+        <v>9.608879179723766</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.58679418364823</v>
+        <v>9.589296019028499</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.621170287773399</v>
+        <v>9.623975836054941</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.489802594515487</v>
+        <v>9.492267855328265</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.422182616708323</v>
+        <v>9.424519168938668</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.278250490690324</v>
+        <v>9.279549608232964</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.183431739380381</v>
+        <v>9.184246829368258</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077416198664832</v>
+        <v>9.077155091408931</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.051431354076922</v>
+        <v>9.050858284676352</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.048119651286699</v>
+        <v>9.047663623762389</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.023505375062623</v>
+        <v>9.022818913499162</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.00321980429068</v>
+        <v>9.002529344098754</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013405958239456</v>
+        <v>9.013077763035724</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038859386166111</v>
+        <v>9.03899763890619</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057536867039779</v>
+        <v>9.057920980235419</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.06077687660969</v>
+        <v>9.060766947297925</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051344582113689</v>
+        <v>9.047981537411715</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.041092339589833</v>
+        <v>9.039468481335424</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047428143002294</v>
+        <v>9.048144106225879</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.058575320178123</v>
+        <v>9.064770194241298</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.061873407368399</v>
+        <v>9.06801011042741</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.062824880210647</v>
+        <v>9.06943204554339</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.037386847350589</v>
+        <v>9.046906319351221</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.011970583187367</v>
+        <v>9.022970738986118</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>8.992569613196935</v>
+        <v>9.003051654870056</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>8.994553883037824</v>
+        <v>9.001115563866497</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.992248728988173</v>
+        <v>8.997704033239671</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.980442913342888</v>
+        <v>8.986939813425048</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.970383503860967</v>
+        <v>8.980554638269622</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.930923391488196</v>
+        <v>8.953483731578824</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.898663437717044</v>
+        <v>8.9576789894654</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.901166052292959</v>
+        <v>8.96255156217936</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>8.959160999144808</v>
+        <v>9.004798795932327</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.150171051835065</v>
+        <v>9.151471519813317</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748494584212139</v>
+        <v>9.748505036985293</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72345943395448</v>
+        <v>9.7234824100131</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720279161078508</v>
+        <v>9.720310815396552</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699276075741698</v>
+        <v>9.699326478719662</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703798331064981</v>
+        <v>9.703848224127848</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697057399253735</v>
+        <v>9.697106667482299</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692876903256531</v>
+        <v>9.692926426187213</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706909685287259</v>
+        <v>9.706960479321488</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719315961382751</v>
+        <v>9.719375367152447</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726357071033929</v>
+        <v>9.726402885024374</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735000730940914</v>
+        <v>9.735047109579682</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711406748911825</v>
+        <v>9.711452161617304</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66701937308032</v>
+        <v>9.667064799614398</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632696764792692</v>
+        <v>9.632753453975759</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599832296672071</v>
+        <v>9.599870112874218</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562061351853584</v>
+        <v>9.562094507851571</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503478682813912</v>
+        <v>9.503551005880947</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431414111022081</v>
+        <v>9.431514628234027</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355629416928565</v>
+        <v>9.355723361410803</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288089625435937</v>
+        <v>9.288187947030744</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265773836966893</v>
+        <v>9.265840406550746</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278741089787216</v>
+        <v>9.278790979344805</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239827544752048</v>
+        <v>9.239781146371548</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.17148984767565</v>
+        <v>9.171394115419208</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107958842118761</v>
+        <v>9.107811956524401</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013975909942076</v>
+        <v>9.013799479765254</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.943666220169499</v>
+        <v>8.9434495979907</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.941218468931897</v>
+        <v>8.940949861570076</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.951345291284571</v>
+        <v>8.951037213122431</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.077527959677365</v>
+        <v>9.077099065488509</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.131567816037469</v>
+        <v>9.131119511893303</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.296359588214377</v>
+        <v>9.296009832827856</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.388560678908249</v>
+        <v>9.388287741654619</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.407128710386008</v>
+        <v>9.406900317569459</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490480069581698</v>
+        <v>9.490286592052279</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606794279600273</v>
+        <v>9.606859021088487</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.597148195628254</v>
+        <v>9.597305257799878</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.613098851519837</v>
+        <v>9.613410826501131</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.608879179723766</v>
+        <v>9.60939104494943</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.589296019028499</v>
+        <v>9.589882014613806</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.623975836054941</v>
+        <v>9.624633327956769</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.492267855328265</v>
+        <v>9.492846520562924</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.424519168938668</v>
+        <v>9.425068131949498</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.279549608232964</v>
+        <v>9.279855376488891</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184246829368258</v>
+        <v>9.18443900188797</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077155091408931</v>
+        <v>9.077094229796106</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050858284676352</v>
+        <v>9.050723822434795</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047663623762389</v>
+        <v>9.047556529650659</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022818913499162</v>
+        <v>9.022657375082005</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002529344098754</v>
+        <v>9.002366544367058</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013077763035724</v>
+        <v>9.013000022225462</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03899763890619</v>
+        <v>9.039029681179825</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057920980235419</v>
+        <v>9.058011278016476</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060766947297925</v>
+        <v>9.060765439121639</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047981537411715</v>
+        <v>9.047961605539527</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039468481335424</v>
+        <v>9.039414006583932</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048144106225879</v>
+        <v>9.048023169565038</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.064770194241298</v>
+        <v>9.064588932510127</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.06801011042741</v>
+        <v>9.071406036489687</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.06943204554339</v>
+        <v>9.073601056637242</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.046906319351221</v>
+        <v>9.051788410587196</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.022970738986118</v>
+        <v>9.028678516478658</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.003051654870056</v>
+        <v>9.009647563267402</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.001115563866497</v>
+        <v>9.008603648108815</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>8.997704033239671</v>
+        <v>9.006044193461126</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.986939813425048</v>
+        <v>8.99640063665138</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.980554638269622</v>
+        <v>8.991365376730482</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.953483731578824</v>
+        <v>8.967719987975126</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.9576789894654</v>
+        <v>8.975266010506452</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.96255156217936</v>
+        <v>8.98307664849086</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.004798795932327</v>
+        <v>9.029825312804679</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.151471519813317</v>
+        <v>9.169178687749218</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748505036985293</v>
+        <v>9.748515228480464</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.7234824100131</v>
+        <v>9.723504812218419</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720310815396552</v>
+        <v>9.720341680867854</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699326478719662</v>
+        <v>9.699375623638829</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703848224127848</v>
+        <v>9.703896871567594</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697106667482299</v>
+        <v>9.697154705570368</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692926426187213</v>
+        <v>9.692974711713781</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706960479321488</v>
+        <v>9.707010002017514</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719375367152447</v>
+        <v>9.719433292004611</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726402885024374</v>
+        <v>9.726447558968522</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735047109579682</v>
+        <v>9.735092334129519</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711452161617304</v>
+        <v>9.71149644453225</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667064799614398</v>
+        <v>9.667109103908466</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632753453975759</v>
+        <v>9.63280874303263</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599870112874218</v>
+        <v>9.599906999710635</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562094507851571</v>
+        <v>9.562126840147997</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503551005880947</v>
+        <v>9.503621524563391</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431514628234027</v>
+        <v>9.431612654704924</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355723361410803</v>
+        <v>9.35581497435237</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288187947030744</v>
+        <v>9.288283841246464</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265840406550746</v>
+        <v>9.265905412758762</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278790979344805</v>
+        <v>9.278839758327434</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239781146371548</v>
+        <v>9.239736012492695</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171394115419208</v>
+        <v>9.171300898196709</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107811956524401</v>
+        <v>9.107668887334892</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013799479765254</v>
+        <v>9.013627617690272</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.9434495979907</v>
+        <v>8.943238563279778</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.940949861570076</v>
+        <v>8.940688140922965</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.951037213122431</v>
+        <v>8.950736856788225</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.077099065488509</v>
+        <v>9.076680820572609</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.131119511893303</v>
+        <v>9.13068233403791</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.296009832827856</v>
+        <v>9.295668557370615</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.388287741654619</v>
+        <v>9.388021358052811</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.406900317569459</v>
+        <v>9.406677254027787</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490286592052279</v>
+        <v>9.490097476623314</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606859021088487</v>
+        <v>9.606921740563129</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.597305257799878</v>
+        <v>9.597457918658714</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.613410826501131</v>
+        <v>9.613714624976463</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.60939104494943</v>
+        <v>9.609890057776202</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.589882014613806</v>
+        <v>9.590453401443959</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.624633327956769</v>
+        <v>9.625274560677951</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.492846520562924</v>
+        <v>9.493411212874211</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.425068131949498</v>
+        <v>9.425604024846791</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.279855376488891</v>
+        <v>9.280154064007752</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18443900188797</v>
+        <v>9.184626844369632</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077094229796106</v>
+        <v>9.077034994626491</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050723822434795</v>
+        <v>9.050592627090014</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047556529650659</v>
+        <v>9.047452003370477</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022657375082005</v>
+        <v>9.022499589023512</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002366544367058</v>
+        <v>9.002207409082473</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013000022225462</v>
+        <v>9.012923900874878</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039029681179825</v>
+        <v>9.039060799778706</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058011278016476</v>
+        <v>9.058099444505352</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060765439121639</v>
+        <v>9.060764268172882</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047961605539527</v>
+        <v>9.047942279031805</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039414006583932</v>
+        <v>9.039360875420158</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.048023169565038</v>
+        <v>9.047905006947735</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.064588932510127</v>
+        <v>9.064411637395096</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.071406036489687</v>
+        <v>9.074457799187213</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.073601056637242</v>
+        <v>9.077220630669093</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.051788410587196</v>
+        <v>9.05585232586586</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.028678516478658</v>
+        <v>9.033101664521906</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.009647563267402</v>
+        <v>9.014743848923127</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.008603648108815</v>
+        <v>9.014396190669814</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.006044193461126</v>
+        <v>9.012406945555069</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>8.99640063665138</v>
+        <v>9.00340735241846</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.991365376730482</v>
+        <v>8.999009355953753</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.967719987975126</v>
+        <v>8.976588519076431</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.975266010506452</v>
+        <v>8.984972166903178</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.98307664849086</v>
+        <v>8.993259448870688</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.029825312804679</v>
+        <v>9.038781739169982</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.169178687749218</v>
+        <v>9.156659225633188</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748515228480464</v>
+        <v>9.74852516837262</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723504812218419</v>
+        <v>9.72352666180206</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720341680867854</v>
+        <v>9.720371786612031</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699375623638829</v>
+        <v>9.699423557008616</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703896871567594</v>
+        <v>9.703944319444521</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697154705570368</v>
+        <v>9.69720155900993</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692974711713781</v>
+        <v>9.693021805629868</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707010002017514</v>
+        <v>9.707058300504301</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719433292004611</v>
+        <v>9.719489790609517</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726447558968522</v>
+        <v>9.726491134883112</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735092334129519</v>
+        <v>9.735136447124304</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.71149644453225</v>
+        <v>9.711539639285474</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667109103908466</v>
+        <v>9.667152327018815</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63280874303263</v>
+        <v>9.632862683169567</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599906999710635</v>
+        <v>9.599942991001146</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562126840147997</v>
+        <v>9.56215837904826</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503621524563391</v>
+        <v>9.50369030551332</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431612654704924</v>
+        <v>9.431708281785482</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.35581497435237</v>
+        <v>9.355904341408221</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288283841246464</v>
+        <v>9.288377396811331</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265905412758762</v>
+        <v>9.26596890975957</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278839758327434</v>
+        <v>9.278887462848928</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239736012492695</v>
+        <v>9.239692092557711</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171300898196709</v>
+        <v>9.17121009860837</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107668887334892</v>
+        <v>9.1075294882436</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013627617690272</v>
+        <v>9.013460149206143</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.943238563279778</v>
+        <v>8.943032903383104</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.940688140922965</v>
+        <v>8.940433046439832</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.950736856788225</v>
+        <v>8.95044393611597</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.076680820572609</v>
+        <v>9.076272833984284</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.13068233403791</v>
+        <v>9.130255874204019</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.295668557370615</v>
+        <v>9.295335458079247</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.388021358052811</v>
+        <v>9.387761295812748</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.406677254027787</v>
+        <v>9.406459336843813</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490097476623314</v>
+        <v>9.489912579586608</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606921740563129</v>
+        <v>9.606982527406014</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.597457918658714</v>
+        <v>9.59760635795741</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.613714624976463</v>
+        <v>9.614010562473894</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.609890057776202</v>
+        <v>9.610376695016331</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.590453401443959</v>
+        <v>9.591010717423146</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.625274560677951</v>
+        <v>9.625900128438735</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.493411212874211</v>
+        <v>9.493962430721403</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.425604024846791</v>
+        <v>9.426127306821533</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.280154064007752</v>
+        <v>9.280445912035972</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184626844369632</v>
+        <v>9.184810499998168</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077034994626491</v>
+        <v>9.076977322369681</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050592627090014</v>
+        <v>9.050464581659845</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047452003370477</v>
+        <v>9.047349954332123</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022499589023512</v>
+        <v>9.022345427098756</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002207409082473</v>
+        <v>9.002051817323121</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012923900874878</v>
+        <v>9.012849350543544</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039060799778706</v>
+        <v>9.039091033036581</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058099444505352</v>
+        <v>9.05818555370354</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060764268172882</v>
+        <v>9.060763411442208</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047942279031805</v>
+        <v>9.047923532743667</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039360875420158</v>
+        <v>9.039309039945081</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047905006947735</v>
+        <v>9.04778952590614</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.064411637395096</v>
+        <v>9.064238183307292</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.074457799187213</v>
+        <v>9.077337098754352</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.077220630669093</v>
+        <v>9.080668756704021</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.05585232586586</v>
+        <v>9.059605738404414</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.033101664521906</v>
+        <v>9.03720894005162</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.014743848923127</v>
+        <v>9.019443799604613</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.014396190669814</v>
+        <v>9.019719446951935</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.012406945555069</v>
+        <v>9.018244576577906</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.00340735241846</v>
+        <v>9.009821698002725</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>8.999009355953753</v>
+        <v>9.005977341002737</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.976588519076431</v>
+        <v>8.984530501406219</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.984972166903178</v>
+        <v>8.993440133881133</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.993259448870688</v>
+        <v>9.00187309562677</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.038781739169982</v>
+        <v>9.045618444494874</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.156659225633188</v>
+        <v>9.14711052921897</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74852516837262</v>
+        <v>9.748483859983594</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72352666180206</v>
+        <v>9.723435861709337</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720371786612031</v>
+        <v>9.720246687286988</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699423557008616</v>
+        <v>9.699224365784776</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703944319444521</v>
+        <v>9.703747143930647</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69720155900993</v>
+        <v>9.697006853033894</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693021805629868</v>
+        <v>9.692826094751858</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707058300504301</v>
+        <v>9.706857570335982</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719489790609517</v>
+        <v>9.719255017196353</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726491134883112</v>
+        <v>9.726310072809829</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735136447124304</v>
+        <v>9.734953153482028</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711539639285474</v>
+        <v>9.711360162636968</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667152327018815</v>
+        <v>9.666972781145882</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632862683169567</v>
+        <v>9.632638621654015</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599942991001146</v>
+        <v>9.59979351556116</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56215837904826</v>
+        <v>9.562027340286056</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50369030551332</v>
+        <v>9.503404485259818</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431708281785482</v>
+        <v>9.431311007026949</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355904341408221</v>
+        <v>9.355533050843466</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288377396811331</v>
+        <v>9.287988783191729</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26596890975957</v>
+        <v>9.26570564723095</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278887462848928</v>
+        <v>9.278690051939691</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239692092557711</v>
+        <v>9.239875261015792</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.17121009860837</v>
+        <v>9.171588197645722</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.1075294882436</v>
+        <v>9.10810969827701</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013460149206143</v>
+        <v>9.014157092062465</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.943032903383104</v>
+        <v>8.943888653794763</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.940433046439832</v>
+        <v>8.94149423734806</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.95044393611597</v>
+        <v>8.951661392284054</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.076272833984284</v>
+        <v>9.077967914158474</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.130255874204019</v>
+        <v>9.132027675690072</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.295335458079247</v>
+        <v>9.296718142474667</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.387761295812748</v>
+        <v>9.388840413569586</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.406459336843813</v>
+        <v>9.407362624078255</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.489912579586608</v>
+        <v>9.490678059386296</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606982527406014</v>
+        <v>9.606727421299377</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.59760635795741</v>
+        <v>9.596986542177881</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.614010562473894</v>
+        <v>9.612778367485381</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.610376695016331</v>
+        <v>9.608353960545173</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.591010717423146</v>
+        <v>9.588694849107583</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.625900128438735</v>
+        <v>9.623301460401237</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.493962430721403</v>
+        <v>9.491674693912072</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.426127306821533</v>
+        <v>9.423956654179426</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.280445912035972</v>
+        <v>9.279236506626907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184810499998168</v>
+        <v>9.184050177113281</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076977322369681</v>
+        <v>9.077217646443961</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050464581659845</v>
+        <v>9.050996136624438</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047349954332123</v>
+        <v>9.047773380727428</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022345427098756</v>
+        <v>9.022984338560263</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002051817323121</v>
+        <v>9.002695934678112</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012849350543544</v>
+        <v>9.013157173652328</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039091033036581</v>
+        <v>9.038964632428621</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.05818555370354</v>
+        <v>9.057828473603024</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060763411442208</v>
+        <v>9.060768817451757</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047923532743667</v>
+        <v>9.051229852445029</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039309039945081</v>
+        <v>9.040894231901373</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04778952590614</v>
+        <v>9.04704133900572</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.064238183307292</v>
+        <v>9.058034313698819</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.077337098754352</v>
+        <v>9.069038970078967</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.080668756704021</v>
+        <v>9.075204433032283</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.059605738404414</v>
+        <v>9.053123278526911</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.03720894005162</v>
+        <v>9.030054205861292</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.019443799604613</v>
+        <v>9.014624649768272</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.019719446951935</v>
+        <v>9.018797346826103</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.018244576577906</v>
+        <v>9.018520771196151</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.009821698002725</v>
+        <v>9.009568703476404</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.005977341002737</v>
+        <v>9.003221309919072</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.984530501406219</v>
+        <v>8.975079571030985</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.993440133881133</v>
+        <v>8.954583246174346</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.00187309562677</v>
+        <v>8.970079552268247</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.045618444494874</v>
+        <v>9.036233259401275</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.14711052921897</v>
+        <v>9.172002879656823</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>9.155728657113055</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748483859983594</v>
+        <v>9.74853486586488</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723435861709337</v>
+        <v>9.723547978961125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720246687286988</v>
+        <v>9.72040116033314</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699224365784776</v>
+        <v>9.699470323074349</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703747143930647</v>
+        <v>9.703990611576195</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697006853033894</v>
+        <v>9.697247271077703</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692826094751858</v>
+        <v>9.693067751497569</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706857570335982</v>
+        <v>9.707105419610373</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719255017196353</v>
+        <v>9.719544914980331</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726310072809829</v>
+        <v>9.726533652745903</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.734953153482028</v>
+        <v>9.735179489033865</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711360162636968</v>
+        <v>9.711581785486121</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.666972781145882</v>
+        <v>9.667194508024282</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632638621654015</v>
+        <v>9.632915323127447</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.59979351556116</v>
+        <v>9.599978118945447</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562027340286056</v>
+        <v>9.562189153389744</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503404485259818</v>
+        <v>9.503757412142015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431311007026949</v>
+        <v>9.431801596417708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355533050843466</v>
+        <v>9.355991544092152</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.287988783191729</v>
+        <v>9.288468698184481</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.26570564723095</v>
+        <v>9.266030949261269</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278690051939691</v>
+        <v>9.278934127503842</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239875261015792</v>
+        <v>9.239649338649503</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171588197645722</v>
+        <v>9.171121624200467</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.10810969827701</v>
+        <v>9.107393620304091</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.014157092062465</v>
+        <v>9.013296908549876</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.943888653794763</v>
+        <v>8.94283241626742</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.94149423734806</v>
+        <v>8.940184330506014</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.951661392284054</v>
+        <v>8.950158178880979</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.077967914158474</v>
+        <v>9.075874733643895</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.132027675690072</v>
+        <v>9.129839743816348</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.296718142474667</v>
+        <v>9.295010245481864</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.388840413569586</v>
+        <v>9.387507333447004</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.407362624078255</v>
+        <v>9.406246391302759</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490678059386296</v>
+        <v>9.489731763364421</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606727421299377</v>
+        <v>9.60704146595522</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.596986542177881</v>
+        <v>9.597750745905927</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.612778367485381</v>
+        <v>9.61429893857242</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.608353960545173</v>
+        <v>9.610851410243519</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.588694849107583</v>
+        <v>9.591554474446596</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.623301460401237</v>
+        <v>9.626510596925121</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.491674693912072</v>
+        <v>9.494500649211634</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.423956654179426</v>
+        <v>9.426638415906176</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.279236506626907</v>
+        <v>9.280731151078943</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184050177113281</v>
+        <v>9.184990105791217</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077217646443961</v>
+        <v>9.076921152726801</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050996136624438</v>
+        <v>9.050339574650209</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047773380727428</v>
+        <v>9.047250296124712</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022984338560263</v>
+        <v>9.02219476680856</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002695934678112</v>
+        <v>9.001899653357233</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013157173652328</v>
+        <v>9.012776324614769</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.038964632428621</v>
+        <v>9.039120417236154</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057828473603024</v>
+        <v>9.058269676254575</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060768817451757</v>
+        <v>9.060762847525179</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051229852445029</v>
+        <v>9.047905342831591</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040894231901373</v>
+        <v>9.039258454454384</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04704133900572</v>
+        <v>9.047676637946061</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.058034313698819</v>
+        <v>9.06406844974941</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.069038970078967</v>
+        <v>9.07707924395298</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.075204433032283</v>
+        <v>9.083387154314728</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.053123278526911</v>
+        <v>9.063400981858301</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.030054205861292</v>
+        <v>9.041793815722752</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.014624649768272</v>
+        <v>9.02549984116423</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.018797346826103</v>
+        <v>9.02601009669651</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.018520771196151</v>
+        <v>9.024747233525384</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.009568703476404</v>
+        <v>9.016648457898963</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.003221309919072</v>
+        <v>9.013219663940756</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.975079571030985</v>
+        <v>8.993572633959978</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.954583246174346</v>
+        <v>9.003013022719923</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.970079552268247</v>
+        <v>9.011785024477833</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.036233259401275</v>
+        <v>9.05425739764031</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.172002879656823</v>
+        <v>9.144761780592406</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.155728657113055</v>
+        <v>9.123978081704209</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74853486586488</v>
+        <v>9.748494584212139</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723547978961125</v>
+        <v>9.72345943395448</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72040116033314</v>
+        <v>9.720279161078508</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699470323074349</v>
+        <v>9.699276075741698</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703990611576195</v>
+        <v>9.703798331064981</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697247271077703</v>
+        <v>9.697057399253735</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693067751497569</v>
+        <v>9.692876903256531</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707105419610373</v>
+        <v>9.706909685287259</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719544914980331</v>
+        <v>9.719315961382751</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726533652745903</v>
+        <v>9.726357071033929</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735179489033865</v>
+        <v>9.735000730940914</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711581785486121</v>
+        <v>9.711406748911825</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667194508024282</v>
+        <v>9.66701937308032</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632915323127447</v>
+        <v>9.632696764792692</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599978118945447</v>
+        <v>9.599832296672071</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562189153389744</v>
+        <v>9.562061351853584</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503757412142015</v>
+        <v>9.503478682813912</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431801596417708</v>
+        <v>9.431414111022081</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355991544092152</v>
+        <v>9.355629416928565</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288468698184481</v>
+        <v>9.288089625435937</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266030949261269</v>
+        <v>9.265773836966893</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278934127503842</v>
+        <v>9.278741089787216</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239649338649503</v>
+        <v>9.239827544752048</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171121624200467</v>
+        <v>9.17148984767565</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107393620304091</v>
+        <v>9.107958842118761</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013296908549876</v>
+        <v>9.013975909942076</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.94283241626742</v>
+        <v>8.943666220169499</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.940184330506014</v>
+        <v>8.941218468931897</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.950158178880979</v>
+        <v>8.951345291284571</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.075874733643895</v>
+        <v>9.077527959677365</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.129839743816348</v>
+        <v>9.131567816037469</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.295010245481864</v>
+        <v>9.296359588214377</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.387507333447004</v>
+        <v>9.388560678908249</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.406246391302759</v>
+        <v>9.407128710386008</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.489731763364421</v>
+        <v>9.490480069581698</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60704146595522</v>
+        <v>9.606794279600273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.597750745905927</v>
+        <v>9.597148195628254</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.61429893857242</v>
+        <v>9.613098851519837</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.610851410243519</v>
+        <v>9.608879179723766</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.591554474446596</v>
+        <v>9.589296019028499</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.626510596925121</v>
+        <v>9.623975836054941</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.494500649211634</v>
+        <v>9.492267855328265</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.426638415906176</v>
+        <v>9.424519168938668</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.280731151078943</v>
+        <v>9.279549608232964</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184990105791217</v>
+        <v>9.184246829368258</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076921152726801</v>
+        <v>9.077155091408931</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050339574650209</v>
+        <v>9.050858284676352</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047250296124712</v>
+        <v>9.047663623762389</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.02219476680856</v>
+        <v>9.022818913499162</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.001899653357233</v>
+        <v>9.002529344098754</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012776324614769</v>
+        <v>9.013077763035724</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039120417236154</v>
+        <v>9.03899763890619</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058269676254575</v>
+        <v>9.057920980235419</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060762847525179</v>
+        <v>9.060766947297925</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047905342831591</v>
+        <v>9.051193943907103</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039258454454384</v>
+        <v>9.040831576848046</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047676637946061</v>
+        <v>9.046918483465934</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.06406844974941</v>
+        <v>9.057862062952276</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.07707924395298</v>
+        <v>9.06877180610457</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.083387154314728</v>
+        <v>9.078671004537789</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.063400981858301</v>
+        <v>9.057908759057067</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.041793815722752</v>
+        <v>9.035839179151564</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.02549984116423</v>
+        <v>9.021925973534614</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.02601009669651</v>
+        <v>9.026396476933485</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.024747233525384</v>
+        <v>9.02642628668624</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.016648457898963</v>
+        <v>9.018049419021812</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.013219663940756</v>
+        <v>9.012509864377991</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.993572633959978</v>
+        <v>8.987278975011437</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.003013022719923</v>
+        <v>8.969250909320705</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.011785024477833</v>
+        <v>8.986602895832373</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.05425739764031</v>
+        <v>9.051339152619336</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.144761780592406</v>
+        <v>9.172931580991428</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.123978081704209</v>
+        <v>9.166623315703577</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748494584212139</v>
+        <v>9.748544329716964</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.72345943395448</v>
+        <v>9.723568782920447</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720279161078508</v>
+        <v>9.720429828404654</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699276075741698</v>
+        <v>9.699515963953351</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.703798331064981</v>
+        <v>9.704035789672275</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697057399253735</v>
+        <v>9.697291882968342</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.692876903256531</v>
+        <v>9.693112590781697</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.706909685287259</v>
+        <v>9.707151402002445</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719315961382751</v>
+        <v>9.719598714632534</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726357071033929</v>
+        <v>9.726575150617819</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735000730940914</v>
+        <v>9.735221498387626</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711406748911825</v>
+        <v>9.711622920844617</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.66701937308032</v>
+        <v>9.667235684143806</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632696764792692</v>
+        <v>9.632966709328279</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.599832296672071</v>
+        <v>9.600012414218927</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562061351853584</v>
+        <v>9.562219190629605</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503478682813912</v>
+        <v>9.503822904814436</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431414111022081</v>
+        <v>9.431892681397422</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.355629416928565</v>
+        <v>9.356076660023874</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288089625435937</v>
+        <v>9.288557825809441</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.265773836966893</v>
+        <v>9.266091580648729</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278741089787216</v>
+        <v>9.278979785444546</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239827544752048</v>
+        <v>9.23960770532252</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.17148984767565</v>
+        <v>9.171035387156351</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107958842118761</v>
+        <v>9.107261151474411</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013975909942076</v>
+        <v>9.013137738166776</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.943666220169499</v>
+        <v>8.942636909867032</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.941218468931897</v>
+        <v>8.939941757652463</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.951345291284571</v>
+        <v>8.94987932596265</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.077527959677365</v>
+        <v>9.075486165215398</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.131567816037469</v>
+        <v>9.129433572820925</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.296359588214377</v>
+        <v>9.294692643570102</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.388560678908249</v>
+        <v>9.387259259652913</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.407128710386008</v>
+        <v>9.406038250442219</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.490480069581698</v>
+        <v>9.48955489619345</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.606794279600273</v>
+        <v>9.60709863584864</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.597148195628254</v>
+        <v>9.597891243790434</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.613098851519837</v>
+        <v>9.614580037892654</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.608879179723766</v>
+        <v>9.611314635188165</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.589296019028499</v>
+        <v>9.592085159949168</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.623975836054941</v>
+        <v>9.627106504976963</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.492267855328265</v>
+        <v>9.495026321446861</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.424519168938668</v>
+        <v>9.427137770173182</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.279549608232964</v>
+        <v>9.281010001486287</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.184246829368258</v>
+        <v>9.18516579292281</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.077155091408931</v>
+        <v>9.076866428429492</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050858284676352</v>
+        <v>9.05021749973886</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047663623762389</v>
+        <v>9.047152946279969</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022818913499162</v>
+        <v>9.022047491066562</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.002529344098754</v>
+        <v>9.001750806372225</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.013077763035724</v>
+        <v>9.012704778216719</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.03899763890619</v>
+        <v>9.039148986742385</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.057920980235419</v>
+        <v>9.058351879630575</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060766947297925</v>
+        <v>9.060762556498577</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.051193943907103</v>
+        <v>9.047887686673835</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.040831576848046</v>
+        <v>9.03920907531743</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046918483465934</v>
+        <v>9.04756625834121</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.057862062952276</v>
+        <v>9.063902321069694</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.06877180610457</v>
+        <v>9.076826765181757</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.078671004537789</v>
+        <v>9.086230146823755</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.057908759057067</v>
+        <v>9.067314561244881</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.035839179151564</v>
+        <v>9.046494638082358</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.021925973534614</v>
+        <v>9.031061391824188</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.026396476933485</v>
+        <v>9.03188394671821</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.02642628668624</v>
+        <v>9.03099398465532</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.018049419021812</v>
+        <v>9.023346995626763</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.012509864377991</v>
+        <v>9.020431724822972</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>8.987278975011437</v>
+        <v>9.002563583964502</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>8.969250909320705</v>
+        <v>9.012603660928477</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>8.986602895832373</v>
+        <v>9.021793707379768</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.051339152619336</v>
+        <v>9.063301429406009</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.172931580991428</v>
+        <v>9.14593689795419</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.166623315703577</v>
+        <v>9.135577415084761</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748544329716964</v>
+        <v>9.748553568271559</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723568782920447</v>
+        <v>9.723589091990389</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720429828404654</v>
+        <v>9.720457815948368</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699515963953351</v>
+        <v>9.69956051976132</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704035789672275</v>
+        <v>9.704079893459737</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697291882968342</v>
+        <v>9.69733543391812</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693112590781697</v>
+        <v>9.693156362974474</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707151402002445</v>
+        <v>9.707196288314158</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719598714632534</v>
+        <v>9.719651236732009</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726575150617819</v>
+        <v>9.726615664756451</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735221498387626</v>
+        <v>9.735262511889502</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711622920844617</v>
+        <v>9.711663081285083</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667235684143806</v>
+        <v>9.667275890845744</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.632966709328279</v>
+        <v>9.633016886011408</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600012414218927</v>
+        <v>9.600045906061725</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562219190629605</v>
+        <v>9.562248516926344</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503822904814436</v>
+        <v>9.503886841029878</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431892681397422</v>
+        <v>9.431981615618263</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356076660023874</v>
+        <v>9.356159763158582</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288557825809441</v>
+        <v>9.288644856349825</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266091580648729</v>
+        <v>9.266150851111856</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.278979785444546</v>
+        <v>9.279024468453834</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23960770532252</v>
+        <v>9.239567149446353</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.171035387156351</v>
+        <v>9.170951304010329</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107261151474411</v>
+        <v>9.107131956194696</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.013137738166776</v>
+        <v>9.012982488210062</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.942636909867032</v>
+        <v>8.94244620147845</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.939941757652463</v>
+        <v>8.939705103822329</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.94987932596265</v>
+        <v>8.949607130566744</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.075486165215398</v>
+        <v>9.075106791063199</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.129433572820925</v>
+        <v>9.129037008596789</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.294692643570102</v>
+        <v>9.294382389027868</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.387259259652913</v>
+        <v>9.38701687273641</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.406038250442219</v>
+        <v>9.405834754631121</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.48955489619345</v>
+        <v>9.489381851827599</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60709863584864</v>
+        <v>9.607154112340275</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.597891243790434</v>
+        <v>9.598028004545014</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.614580037892654</v>
+        <v>9.614854131014871</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.611314635188165</v>
+        <v>9.611766781033495</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.592085159949168</v>
+        <v>9.592603238344907</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.627106504976963</v>
+        <v>9.62768836615796</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.495026321446861</v>
+        <v>9.495539879779024</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.427137770173182</v>
+        <v>9.42762576885346</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.281010001486287</v>
+        <v>9.281282673999687</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18516579292281</v>
+        <v>9.185337687027259</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076866428429492</v>
+        <v>9.076813095053577</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.05021749973886</v>
+        <v>9.050098255480655</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047152946279969</v>
+        <v>9.047057826051741</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.022047491066562</v>
+        <v>9.021903487906364</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.001750806372225</v>
+        <v>9.00160517022023</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012704778216719</v>
+        <v>9.012634668147101</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039148986742385</v>
+        <v>9.039176774125615</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058351879630575</v>
+        <v>9.058432228306611</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060762556498577</v>
+        <v>9.060762519807245</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047887686673835</v>
+        <v>9.047870542796407</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.03920907531743</v>
+        <v>9.03916086086393</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.04756625834121</v>
+        <v>9.047458305939749</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.063902321069694</v>
+        <v>9.063739686229301</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.076826765181757</v>
+        <v>9.076579500021829</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.086230146823755</v>
+        <v>9.087821832443588</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.067314561244881</v>
+        <v>9.069610922415663</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.046494638082358</v>
+        <v>9.049443413384868</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.031061391824188</v>
+        <v>9.034620158794711</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.03188394671821</v>
+        <v>9.035353719958088</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.03099398465532</v>
+        <v>9.034673512823066</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.023346995626763</v>
+        <v>9.027273671458875</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.020431724822972</v>
+        <v>9.024592758437612</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.002563583964502</v>
+        <v>9.007798500880581</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.012603660928477</v>
+        <v>9.017326644175558</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.021793707379768</v>
+        <v>9.025878597888067</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.063301429406009</v>
+        <v>9.064267333371735</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.14593689795419</v>
+        <v>9.135596755492095</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.135577415084761</v>
+        <v>9.106248279963456</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748553568271559</v>
+        <v>9.748562589478844</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723589091990389</v>
+        <v>9.723608923620578</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720457815948368</v>
+        <v>9.720485146907786</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.69956051976132</v>
+        <v>9.699604028729821</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704079893459737</v>
+        <v>9.704122960799262</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69733543391812</v>
+        <v>9.69737796131991</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693156362974474</v>
+        <v>9.693199105711425</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707196288314158</v>
+        <v>9.707240117265711</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719651236732009</v>
+        <v>9.719702526232711</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726615664756451</v>
+        <v>9.726655229721565</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735262511889502</v>
+        <v>9.735302564524691</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711663081285083</v>
+        <v>9.711702301049813</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667275890845744</v>
+        <v>9.667315161949514</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633016886011408</v>
+        <v>9.633065895360216</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600045906061725</v>
+        <v>9.60007862236167</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562248516926344</v>
+        <v>9.562277157215647</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503886841029878</v>
+        <v>9.503949275589941</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.431981615618263</v>
+        <v>9.432068474298681</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356159763158582</v>
+        <v>9.356240924000527</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288644856349825</v>
+        <v>9.288729862908594</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266150851111856</v>
+        <v>9.266208805765524</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279024468453834</v>
+        <v>9.279068207013301</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239567149446353</v>
+        <v>9.23952763006104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170951304010329</v>
+        <v>9.170869295382381</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107131956194696</v>
+        <v>9.107005914995355</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012982488210062</v>
+        <v>9.012831016076596</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.94244620147845</v>
+        <v>8.942260117198485</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.939705103822329</v>
+        <v>8.939474155689958</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.949607130566744</v>
+        <v>8.949341357502309</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.075106791063199</v>
+        <v>9.074736289281603</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.129037008596789</v>
+        <v>9.128649714943352</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.294382389027868</v>
+        <v>9.294079230512306</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.38701687273641</v>
+        <v>9.386779980074355</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.405834754631121</v>
+        <v>9.405635751175494</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.489381851827599</v>
+        <v>9.489212509258273</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607154112340275</v>
+        <v>9.607207966591695</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598028004545014</v>
+        <v>9.598161173280367</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.614854131014871</v>
+        <v>9.615121475330515</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.611766781033495</v>
+        <v>9.61220823962072</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.592603238344907</v>
+        <v>9.59310915236642</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.62768836615796</v>
+        <v>9.628256670216995</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.495539879779024</v>
+        <v>9.496041736980558</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.42762576885346</v>
+        <v>9.428102793380827</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.281282673999687</v>
+        <v>9.281549370266038</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.185337687027259</v>
+        <v>9.185505908484586</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076813095053577</v>
+        <v>9.076761100846241</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.050098255480655</v>
+        <v>9.049981745032644</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.047057826051741</v>
+        <v>9.046964860209961</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.021903487906364</v>
+        <v>9.02176265020727</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.00160517022023</v>
+        <v>9.001462643178961</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012634668147101</v>
+        <v>9.012565952801211</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039176774125615</v>
+        <v>9.039203810275495</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058432228306611</v>
+        <v>9.058510783923833</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060762519807245</v>
+        <v>9.060762720160536</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047870542796407</v>
+        <v>9.047853890804141</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.03916086086393</v>
+        <v>9.039113771277728</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047458305939749</v>
+        <v>9.047352702982259</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.063739686229301</v>
+        <v>9.063580438582367</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.076579500021829</v>
+        <v>9.076337292350424</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.087821832443588</v>
+        <v>9.089160339289423</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.069610922415663</v>
+        <v>9.071561614706891</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.049443413384868</v>
+        <v>9.051994767505043</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.034620158794711</v>
+        <v>9.037772173402523</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.035353719958088</v>
+        <v>9.038293370153614</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.034673512823066</v>
+        <v>9.037788011262055</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.027273671458875</v>
+        <v>9.030595985240751</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.024592758437612</v>
+        <v>9.028097227712101</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.007798500880581</v>
+        <v>9.012197382971138</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.017326644175558</v>
+        <v>9.021056075344925</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.025878597888067</v>
+        <v>9.028834545808714</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.064267333371735</v>
+        <v>9.064075456216397</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.135596755492095</v>
+        <v>9.125646867099253</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.106248279963456</v>
+        <v>9.087193800830773</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748562589478844</v>
+        <v>9.748571400919314</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723608923620578</v>
+        <v>9.723628294449883</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720485146907786</v>
+        <v>9.720511844116384</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699604028729821</v>
+        <v>9.699646527315588</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704122960799262</v>
+        <v>9.704165027793549</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.69737796131991</v>
+        <v>9.697419500830172</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693199105711425</v>
+        <v>9.6932408548792</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707240117265711</v>
+        <v>9.707282925775173</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719702526232711</v>
+        <v>9.719752626004773</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726655229721565</v>
+        <v>9.726693878473311</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735302564524691</v>
+        <v>9.735341689659119</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711702301049813</v>
+        <v>9.711740612796541</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667315161949514</v>
+        <v>9.667353529720286</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633065895360216</v>
+        <v>9.63311377762013</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.60007862236167</v>
+        <v>9.600110589731488</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562277157215647</v>
+        <v>9.562305135280997</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.503949275589941</v>
+        <v>9.504010260754789</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432068474298681</v>
+        <v>9.432153329193277</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356240924000527</v>
+        <v>9.356320209801801</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288729862908594</v>
+        <v>9.288812915232278</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266208805765524</v>
+        <v>9.266265487761757</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279068207013301</v>
+        <v>9.279111030367824</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.23952763006104</v>
+        <v>9.239489108243001</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170869295382381</v>
+        <v>9.170789285731992</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.107005914995355</v>
+        <v>9.106882914133241</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012831016076596</v>
+        <v>9.012683185975625</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.942260117198485</v>
+        <v>8.942078491402206</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.939474155689958</v>
+        <v>8.939248710027902</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.949341357502309</v>
+        <v>8.949081782508845</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.074736289281603</v>
+        <v>9.074374352791033</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.128649714943352</v>
+        <v>9.128271371137414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.294079230512306</v>
+        <v>9.293782927982951</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.386779980074355</v>
+        <v>9.386548397612392</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.405635751175494</v>
+        <v>9.405441093949147</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.489212509258273</v>
+        <v>9.489046752451019</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607207966591695</v>
+        <v>9.607260265940941</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598161173280367</v>
+        <v>9.598290887773132</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.615121475330515</v>
+        <v>9.615382315832738</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.61220823962072</v>
+        <v>9.612639384570533</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.59310915236642</v>
+        <v>9.59360332431206</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.628256670216995</v>
+        <v>9.628811884449497</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.496041736980558</v>
+        <v>9.496532287336819</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.428102793380827</v>
+        <v>9.428569208368128</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.281549370266038</v>
+        <v>9.281810283318411</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.185505908484586</v>
+        <v>9.18567057268878</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076761100846241</v>
+        <v>9.076710396565513</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049981745032644</v>
+        <v>9.04986787589738</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046964860209961</v>
+        <v>9.046873976848079</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.02176265020727</v>
+        <v>9.021624875437272</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.001462643178961</v>
+        <v>9.001323127726828</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012565952801211</v>
+        <v>9.012498592103288</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039203810275495</v>
+        <v>9.039230124506375</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058510783923833</v>
+        <v>9.058587605442142</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060762720160536</v>
+        <v>9.060763141437512</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047853890804141</v>
+        <v>9.047837711316523</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039113771277728</v>
+        <v>9.039067768497272</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047352702982259</v>
+        <v>9.047249374930416</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.063580438582367</v>
+        <v>9.063424475667933</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.076337292350424</v>
+        <v>9.076099992049025</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089160339289423</v>
+        <v>9.089639695095535</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.071561614706891</v>
+        <v>9.072478637934516</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.051994767505043</v>
+        <v>9.053381851911709</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.037772173402523</v>
+        <v>9.039233501181492</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.038293370153614</v>
+        <v>9.039481615803881</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.037788011262055</v>
+        <v>9.039061188500677</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.030595985240751</v>
+        <v>9.032197724458555</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.028097227712101</v>
+        <v>9.030119435819067</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.012197382971138</v>
+        <v>9.015337344477446</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.021056075344925</v>
+        <v>9.024016720909671</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.028834545808714</v>
+        <v>9.030986062826869</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.064075456216397</v>
+        <v>9.062731400954155</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.125646867099253</v>
+        <v>9.115046666590219</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.087193800830773</v>
+        <v>9.069956467177137</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748571400919314</v>
+        <v>9.748580009825005</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723628294449883</v>
+        <v>9.723647220352968</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720511844116384</v>
+        <v>9.720537929361191</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699646527315588</v>
+        <v>9.699688050302317</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704165027793549</v>
+        <v>9.704206128888137</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697419500830172</v>
+        <v>9.697460086468558</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.6932408548792</v>
+        <v>9.69328164471597</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707282925775173</v>
+        <v>9.707324749062082</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719752626004773</v>
+        <v>9.719801576953838</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726693878473311</v>
+        <v>9.726731642463683</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735341689659119</v>
+        <v>9.73537991913199</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711740612796541</v>
+        <v>9.711778047689018</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667353529720286</v>
+        <v>9.667391024957222</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63311377762013</v>
+        <v>9.633160571208581</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600110589731488</v>
+        <v>9.600141833580821</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562305135280997</v>
+        <v>9.562332473819433</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504010260754789</v>
+        <v>9.504069846388738</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432153329193277</v>
+        <v>9.432236248789749</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356320209801801</v>
+        <v>9.356397684747577</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288812915232278</v>
+        <v>9.288894079901272</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266265487761757</v>
+        <v>9.266320938394788</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279111030367824</v>
+        <v>9.279152966586327</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239489108243001</v>
+        <v>9.239451546980764</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170789285731992</v>
+        <v>9.170711203129537</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106882914133241</v>
+        <v>9.106762845253561</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012683185975625</v>
+        <v>9.012538868527949</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.942078491402206</v>
+        <v>8.941901166257566</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.939248710027902</v>
+        <v>8.939028573118097</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.949081782508845</v>
+        <v>8.948828191629628</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.074374352791033</v>
+        <v>9.074020688495747</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.128271371137414</v>
+        <v>9.127901671054312</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.293782927982951</v>
+        <v>9.293493252075351</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.386548397612392</v>
+        <v>9.386321949395654</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.405441093949147</v>
+        <v>9.405250643047435</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.489046752451019</v>
+        <v>9.488884470097522</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607260265940941</v>
+        <v>9.6073110741508</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598290887773132</v>
+        <v>9.598417278919241</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.615382315832738</v>
+        <v>9.615636885850961</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.612639384570533</v>
+        <v>9.613060572327658</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.59360332431206</v>
+        <v>9.594086157208261</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.628811884449497</v>
+        <v>9.629354454966698</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.496532287336819</v>
+        <v>9.49701190766643</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.428569208368128</v>
+        <v>9.429025362520127</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.281810283318411</v>
+        <v>9.282065598027131</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18567057268878</v>
+        <v>9.185831790300037</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076710396565513</v>
+        <v>9.076660935331146</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04986787589738</v>
+        <v>9.049756559683185</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046873976848079</v>
+        <v>9.046785107202872</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.021624875437272</v>
+        <v>9.021490065412081</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.001323127726828</v>
+        <v>9.001186530331413</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012498592103288</v>
+        <v>9.012432547440984</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039230124506375</v>
+        <v>9.039255744655041</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058587605442142</v>
+        <v>9.058662749283208</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060763141437512</v>
+        <v>9.060763768599998</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047837711316523</v>
+        <v>9.047821985907852</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039067768497272</v>
+        <v>9.039022816122227</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047249374930416</v>
+        <v>9.047148250305662</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.063424475667933</v>
+        <v>9.063271699013125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.076099992049025</v>
+        <v>9.0758674547269</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089639695095535</v>
+        <v>9.090098909465201</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.072478637934516</v>
+        <v>9.073336161129772</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.053381851911709</v>
+        <v>9.054676904458249</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.039233501181492</v>
+        <v>9.040369971452476</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.039481615803881</v>
+        <v>9.040584901158509</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.039061188500677</v>
+        <v>9.040247377055788</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.032197724458555</v>
+        <v>9.033694577771685</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.030119435819067</v>
+        <v>9.032010714843382</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.015337344477446</v>
+        <v>9.018258986641378</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.024016720909671</v>
+        <v>9.026736073544463</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.030986062826869</v>
+        <v>9.032929822314443</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.062731400954155</v>
+        <v>9.061510662130187</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.115046666590219</v>
+        <v>9.106179708423388</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.069956467177137</v>
+        <v>9.0583424615818</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748580009825005</v>
+        <v>9.74858842309931</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723647220352968</v>
+        <v>9.723665716483655</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720537929361191</v>
+        <v>9.720563423442048</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699688050302317</v>
+        <v>9.699728630895521</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704206128888137</v>
+        <v>9.704246296965403</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697460086468558</v>
+        <v>9.697499750710755</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.69328164471597</v>
+        <v>9.693321507904988</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707324749062082</v>
+        <v>9.707365620744</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719801576953838</v>
+        <v>9.719849418132251</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726731642463683</v>
+        <v>9.726768551721779</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.73537991913199</v>
+        <v>9.735417283342112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711778047689018</v>
+        <v>9.711814635481449</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667391024957222</v>
+        <v>9.667427677075732</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633160571208581</v>
+        <v>9.633206312817576</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600141833580821</v>
+        <v>9.600172378183418</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562332473819433</v>
+        <v>9.562359194502868</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504069846388738</v>
+        <v>9.504128080095906</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432236248789749</v>
+        <v>9.43231729849254</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356397684747577</v>
+        <v>9.356473410128809</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288894079901272</v>
+        <v>9.288973420507379</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266320938394788</v>
+        <v>9.266375197199446</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279152966586327</v>
+        <v>9.279194042619132</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239451546980764</v>
+        <v>9.239414911059635</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170711203129537</v>
+        <v>9.170634979043731</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106762845253561</v>
+        <v>9.106645605075354</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012538868527949</v>
+        <v>9.012397940392924</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.941901166257566</v>
+        <v>8.941727991273654</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.939028573118097</v>
+        <v>8.93881356020367</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.948828191629628</v>
+        <v>8.948580380627659</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.074020688495747</v>
+        <v>9.073675016498226</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.127901671054312</v>
+        <v>9.127540322348155</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.293493252075351</v>
+        <v>9.293209983515743</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.386321949395654</v>
+        <v>9.386100467129847</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.405250643047435</v>
+        <v>9.405064264462462</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.488884470097522</v>
+        <v>9.488725555381901</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.6073110741508</v>
+        <v>9.607360451638295</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598417278919241</v>
+        <v>9.598540471154312</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.615636885850961</v>
+        <v>9.615885407734027</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.613060572327658</v>
+        <v>9.613472143134475</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.594086157208261</v>
+        <v>9.594558035893609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.629354454966698</v>
+        <v>9.62988480787995</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.49701190766643</v>
+        <v>9.497480958274988</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.429025362520127</v>
+        <v>9.429471589487887</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.282065598027131</v>
+        <v>9.282315491523104</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.185831790300037</v>
+        <v>9.18598966748209</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076660935331146</v>
+        <v>9.076612672485872</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049756559683185</v>
+        <v>9.049647711880009</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046785107202872</v>
+        <v>9.046698185485784</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.021490065412081</v>
+        <v>9.021358126069018</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.001186530331413</v>
+        <v>9.001052761250371</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012432547440984</v>
+        <v>9.012367781602869</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039255744655041</v>
+        <v>9.039280697171279</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058662749283208</v>
+        <v>9.058736269464516</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060763768599998</v>
+        <v>9.060764587612844</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047821985907852</v>
+        <v>9.047806697051453</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.039022816122227</v>
+        <v>9.03897887932585</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047148250305662</v>
+        <v>9.047049260537193</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.063271699013125</v>
+        <v>9.063122013946856</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.0758674547269</v>
+        <v>9.075639541459154</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.090098909465201</v>
+        <v>9.089919275862014</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.073336161129772</v>
+        <v>9.074060079496334</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.054676904458249</v>
+        <v>9.055969135471861</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.040369971452476</v>
+        <v>9.042305966019473</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.040584901158509</v>
+        <v>9.04345002501077</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.040247377055788</v>
+        <v>9.042987859830429</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.033694577771685</v>
+        <v>9.03661404262586</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.032010714843382</v>
+        <v>9.03526866562791</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.018258986641378</v>
+        <v>9.022552168319979</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.026736073544463</v>
+        <v>9.031166187738766</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.032929822314443</v>
+        <v>9.037047125070352</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.061510662130187</v>
+        <v>9.063522253019123</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.106179708423388</v>
+        <v>9.103303635074452</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.0583424615818</v>
+        <v>9.058807017214844</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>9.070908557463326</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74858842309931</v>
+        <v>9.748596647335408</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723665716483655</v>
+        <v>9.723683797315381</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720563423442048</v>
+        <v>9.720588346226887</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699728630895521</v>
+        <v>9.699768300811025</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704246296965403</v>
+        <v>9.704285563432222</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697499750710755</v>
+        <v>9.697538524575066</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693321507904988</v>
+        <v>9.693360475661846</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707365620744</v>
+        <v>9.707405572926564</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719849418132251</v>
+        <v>9.719896186842812</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726768551721779</v>
+        <v>9.726804634933341</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735417283342112</v>
+        <v>9.735453811328421</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711814635481449</v>
+        <v>9.711850404597277</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667427677075732</v>
+        <v>9.667463514184311</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633206312817576</v>
+        <v>9.63325103750943</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600172378183418</v>
+        <v>9.600202246739844</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562359194502868</v>
+        <v>9.562385318035286</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504128080095906</v>
+        <v>9.50418500734677</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.43231729849254</v>
+        <v>9.432396540794283</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356473410128809</v>
+        <v>9.356547444503438</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.288973420507379</v>
+        <v>9.289050997819515</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266375197199446</v>
+        <v>9.266428302043405</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279194042619132</v>
+        <v>9.279234284352023</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239414911059635</v>
+        <v>9.239379166954546</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170634979043731</v>
+        <v>9.170560548143914</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106645605075354</v>
+        <v>9.106531095098727</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012397940392924</v>
+        <v>9.012260283921206</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.941727991273654</v>
+        <v>8.941558822879946</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.93881356020367</v>
+        <v>8.938603494978102</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.948580380627659</v>
+        <v>8.948338154440759</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.073675016498226</v>
+        <v>9.073337069365827</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.127540322348155</v>
+        <v>9.127187045686586</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.293209983515743</v>
+        <v>9.292932912573729</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.386100467129847</v>
+        <v>9.385883789770432</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.405064264462462</v>
+        <v>9.404881829778246</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.488725555381901</v>
+        <v>9.488569905760402</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607360451638295</v>
+        <v>9.607408455686967</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598540471154312</v>
+        <v>9.598660582843799</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.615885407734027</v>
+        <v>9.616128093486056</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.613472143134475</v>
+        <v>9.613874421939354</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.594558035893609</v>
+        <v>9.595019328030762</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.62988480787995</v>
+        <v>9.630403350406647</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.497480958274988</v>
+        <v>9.497939783847169</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.429471589487887</v>
+        <v>9.429908208668914</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.282315491523104</v>
+        <v>9.282560133595291</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.18598966748209</v>
+        <v>9.186144306125588</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076612672485872</v>
+        <v>9.076565565466275</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049647711880009</v>
+        <v>9.04954125164971</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046698185485784</v>
+        <v>9.046613148724902</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.021358126069018</v>
+        <v>9.021228967254743</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.001052761250371</v>
+        <v>9.000921734343912</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012367781602869</v>
+        <v>9.012304258718798</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039280697171279</v>
+        <v>9.039305007201982</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058736269464516</v>
+        <v>9.058808217725067</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060764587612844</v>
+        <v>9.060765585370714</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047806697051453</v>
+        <v>9.04779182806762</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.03897887932585</v>
+        <v>9.038935924772709</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.047049260537193</v>
+        <v>9.046952339818716</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.063122013946856</v>
+        <v>9.062975329423514</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.075639541459154</v>
+        <v>9.075416118538433</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089919275862014</v>
+        <v>9.089743297250662</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.074060079496334</v>
+        <v>9.074234971682731</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055969135471861</v>
+        <v>9.05650744834602</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.042305966019473</v>
+        <v>9.043397687797112</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.04345002501077</v>
+        <v>9.044523156851257</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.042987859830429</v>
+        <v>9.044163190791309</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.03661404262586</v>
+        <v>9.038104679756035</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.03526866562791</v>
+        <v>9.037158572587668</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.022552168319979</v>
+        <v>9.025345900703503</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.031166187738766</v>
+        <v>9.033922052733606</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.037047125070352</v>
+        <v>9.039281893259263</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.063522253019123</v>
+        <v>9.063407857263588</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.103303635074452</v>
+        <v>9.098203567355167</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.058807017214844</v>
+        <v>9.054648842456203</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>9.070908557463326</v>
+        <v>9.053230601663813</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748596647335408</v>
+        <v>9.748604688833524</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723683797315381</v>
+        <v>9.723701476678952</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720588346226887</v>
+        <v>9.72061271670333</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699768300811025</v>
+        <v>9.699807090357551</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704285563432222</v>
+        <v>9.704323958301783</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697538524575066</v>
+        <v>9.697576437703246</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693360475661846</v>
+        <v>9.693398577815936</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707405572926564</v>
+        <v>9.707444636287507</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719896186842812</v>
+        <v>9.719941918735625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726804634933341</v>
+        <v>9.726839919515029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735453811328421</v>
+        <v>9.735489530845149</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711850404597277</v>
+        <v>9.711885382202734</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667463514184311</v>
+        <v>9.667498563156284</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.63325103750943</v>
+        <v>9.633294778806201</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600202246739844</v>
+        <v>9.600231461436129</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562385318035286</v>
+        <v>9.56241086420618</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.50418500734677</v>
+        <v>9.504240671596321</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432396540794283</v>
+        <v>9.432474035435909</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356547444503438</v>
+        <v>9.356619843846925</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289050997819515</v>
+        <v>9.289126869938531</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266428302043405</v>
+        <v>9.266480289213739</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279234284352023</v>
+        <v>9.27927371665735</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239379166954546</v>
+        <v>9.239344282730492</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170560548143914</v>
+        <v>9.170487848115904</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106531095098727</v>
+        <v>9.106419221332077</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012260283921206</v>
+        <v>9.012125786831049</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.941558822879946</v>
+        <v>8.941393524034083</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.938603494978102</v>
+        <v>8.938398209108888</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.948338154440759</v>
+        <v>8.948101326672912</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.073337069365827</v>
+        <v>9.073006591445738</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.127187045686586</v>
+        <v>9.126841574035911</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.292932912573729</v>
+        <v>9.292661838550071</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.385883789770432</v>
+        <v>9.385671763137882</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.404881829778246</v>
+        <v>9.404703215884394</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.488569905760402</v>
+        <v>9.488417422753646</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607408455686967</v>
+        <v>9.60745514064347</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598660582843799</v>
+        <v>9.598777726645466</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.616128093486056</v>
+        <v>9.616365145358795</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.613874421939354</v>
+        <v>9.614267719244635</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.595019328030762</v>
+        <v>9.595470385051698</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.630403350406647</v>
+        <v>9.630910471903707</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.497939783847169</v>
+        <v>9.498388714281784</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.429908208668914</v>
+        <v>9.430335525957073</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.282560133595291</v>
+        <v>9.282799687064205</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.186144306125588</v>
+        <v>9.186295804058489</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076565565466275</v>
+        <v>9.076519573682507</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.04954125164971</v>
+        <v>9.049437101629753</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046613148724902</v>
+        <v>9.046529936616849</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.021228967254743</v>
+        <v>9.021102502525844</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000921734343912</v>
+        <v>9.000793366898169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012304258718798</v>
+        <v>9.012241944203062</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039305007201982</v>
+        <v>9.039328698669255</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058808217725067</v>
+        <v>9.058878643643354</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060765585370714</v>
+        <v>9.060766749630764</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.04779182806762</v>
+        <v>9.047777363075015</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038935924772709</v>
+        <v>9.038893920541408</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046952339818716</v>
+        <v>9.046857424973378</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062975329423514</v>
+        <v>9.062831557855954</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.075416118538433</v>
+        <v>9.075197057239528</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089743297250662</v>
+        <v>9.089570865674158</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.074234971682731</v>
+        <v>9.073542934760649</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.05650744834602</v>
+        <v>9.055910544055397</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.043397687797112</v>
+        <v>9.043207855591065</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.044523156851257</v>
+        <v>9.044074501642687</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.044163190791309</v>
+        <v>9.043723129132569</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.038104679756035</v>
+        <v>9.037857213388737</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.037158572587668</v>
+        <v>9.037148572271597</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.025345900703503</v>
+        <v>9.025909469461222</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.033922052733606</v>
+        <v>9.034084136872659</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.039281893259263</v>
+        <v>9.038493146278235</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.063407857263588</v>
+        <v>9.059802558360893</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.098203567355167</v>
+        <v>9.089121582117265</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.054648842456203</v>
+        <v>9.043974443382607</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>9.053230601663813</v>
+        <v>9.025980550455316</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748604688833524</v>
+        <v>9.748612553616997</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723701476678952</v>
+        <v>9.723718767797827</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.72061271670333</v>
+        <v>9.720636553026917</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699807090357551</v>
+        <v>9.699845028513881</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704323958301783</v>
+        <v>9.704361510270033</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697576437703246</v>
+        <v>9.697613518436002</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693398577815936</v>
+        <v>9.693435842886522</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707444636287507</v>
+        <v>9.70748284015515</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719941918735625</v>
+        <v>9.719986647898599</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726839919515029</v>
+        <v>9.726874431683816</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735489530845149</v>
+        <v>9.735524468432081</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711885382202734</v>
+        <v>9.711919594275585</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667498563156284</v>
+        <v>9.667532849696881</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633294778806201</v>
+        <v>9.633337568773324</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600231461436129</v>
+        <v>9.600260043498571</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56241086420618</v>
+        <v>9.562435851940462</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504240671596321</v>
+        <v>9.504295114394466</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432474035435909</v>
+        <v>9.432549839556332</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356619843846925</v>
+        <v>9.356690661692959</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289126869938531</v>
+        <v>9.289201092441971</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266480289213739</v>
+        <v>9.266531193498135</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.27927371665735</v>
+        <v>9.279312363442234</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239344282730492</v>
+        <v>9.239310227949865</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170487848115904</v>
+        <v>9.170416819490423</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106419221332077</v>
+        <v>9.106309894037718</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.012125786831049</v>
+        <v>9.011994341906485</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.941393524034083</v>
+        <v>8.941231963855973</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.938398209108888</v>
+        <v>8.938197541792952</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.948101326672912</v>
+        <v>8.947869719119005</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.073006591445738</v>
+        <v>9.072683338224518</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.126841574035911</v>
+        <v>9.126503651992731</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.292661838550071</v>
+        <v>9.292396569297052</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.385671763137882</v>
+        <v>9.38546423955707</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.404703215884394</v>
+        <v>9.404528304707053</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.488417422753646</v>
+        <v>9.488268011750607</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.60745514064347</v>
+        <v>9.607500558099726</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598777726645466</v>
+        <v>9.598892009846343</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.616365145358795</v>
+        <v>9.616596756403879</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.614267719244635</v>
+        <v>9.614652331898958</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.595470385051698</v>
+        <v>9.595911543041419</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.630910471903707</v>
+        <v>9.631406544834144</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.498388714281784</v>
+        <v>9.498828065474001</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.430335525957073</v>
+        <v>9.43075383444582</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.282799687064205</v>
+        <v>9.283034308133015</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.186295804058489</v>
+        <v>9.186444255244311</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076519573682507</v>
+        <v>9.07647465840612</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049437101629753</v>
+        <v>9.049335187749264</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046529936616849</v>
+        <v>9.046448491387839</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.021102502525844</v>
+        <v>9.020978648961414</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000793366898169</v>
+        <v>9.000667579458657</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012241944203062</v>
+        <v>9.012180804700151</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039328698669255</v>
+        <v>9.039351794343045</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058878643643354</v>
+        <v>9.058947594748146</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060766749630764</v>
+        <v>9.060768068950768</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047777363075015</v>
+        <v>9.047763286945251</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038893920541408</v>
+        <v>9.038852836051937</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046857424973378</v>
+        <v>9.046764455326317</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062831557855954</v>
+        <v>9.062690614957351</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.075197057239528</v>
+        <v>9.074982233596112</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089570865674158</v>
+        <v>9.089401877275574</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.073542934760649</v>
+        <v>9.073677139874089</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.055910544055397</v>
+        <v>9.056347567290068</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.043207855591065</v>
+        <v>9.044141480507681</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.044074501642687</v>
+        <v>9.044965492924424</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.043723129132569</v>
+        <v>9.044705553005407</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.037857213388737</v>
+        <v>9.039125098199957</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.037148572271597</v>
+        <v>9.03876819016827</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.025909469461222</v>
+        <v>9.028297023096314</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.034084136872659</v>
+        <v>9.036378383580713</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.038493146278235</v>
+        <v>9.040267555976957</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.059802558360893</v>
+        <v>9.059542657895072</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.089121582117265</v>
+        <v>9.085060134750108</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.043974443382607</v>
+        <v>9.041197706275007</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>9.025980550455316</v>
+        <v>9.025687499081368</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.748612553616997</v>
+        <v>9.74862024744734</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723718767797827</v>
+        <v>9.723735683321067</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720636553026917</v>
+        <v>9.720659872566173</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699845028513881</v>
+        <v>9.699882143001009</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704361510270033</v>
+        <v>9.704398246787152</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697613518436002</v>
+        <v>9.697649793883599</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693435842886522</v>
+        <v>9.693472298153885</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.70748284015515</v>
+        <v>9.707520212581795</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.719986647898599</v>
+        <v>9.720030406942049</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726874431683816</v>
+        <v>9.726908196521865</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735524468432081</v>
+        <v>9.735558649480236</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711919594275585</v>
+        <v>9.711953065669368</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667532849696881</v>
+        <v>9.667566398405993</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633337568773324</v>
+        <v>9.633379438097824</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600260043498571</v>
+        <v>9.600288013245063</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.562435851940462</v>
+        <v>9.56246029934516</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504295114394466</v>
+        <v>9.504348375489226</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432549839556332</v>
+        <v>9.432624007832468</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356690661692959</v>
+        <v>9.356759949265065</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289201092441971</v>
+        <v>9.289273718519478</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266531193498135</v>
+        <v>9.266581048261209</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279312363442234</v>
+        <v>9.279350247694124</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239310227949865</v>
+        <v>9.239276973586156</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170416819490423</v>
+        <v>9.170347405483025</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106309894037718</v>
+        <v>9.106203027494523</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.011994341906485</v>
+        <v>9.011865846715503</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.941231963855973</v>
+        <v>8.941074017286164</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.938197541792952</v>
+        <v>8.938001339341415</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.947869719119005</v>
+        <v>8.947643161320464</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.072683338224518</v>
+        <v>9.072367075728915</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.126503651992731</v>
+        <v>9.126173035158637</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.292396569297052</v>
+        <v>9.292136920768989</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.38546423955707</v>
+        <v>9.385261077519045</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.404528304707053</v>
+        <v>9.404356982955896</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.488268011750607</v>
+        <v>9.488121581823588</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607500558099726</v>
+        <v>9.607544757061955</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.598892009846343</v>
+        <v>9.599003534676276</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.616596756403879</v>
+        <v>9.616823110988097</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.614652331898958</v>
+        <v>9.615028543838093</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.595911543041419</v>
+        <v>9.596343123564619</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.631406544834144</v>
+        <v>9.63189192567161</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.498828065474001</v>
+        <v>9.499258140048562</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.43075383444582</v>
+        <v>9.431163415088173</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.283034308133015</v>
+        <v>9.283264146717826</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.186444255244311</v>
+        <v>9.186589749969045</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.07647465840612</v>
+        <v>9.076430782665394</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049335187749264</v>
+        <v>9.049235439056638</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046448491387839</v>
+        <v>9.046368757663261</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020978648961414</v>
+        <v>9.020857326986759</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000667579458657</v>
+        <v>9.000544295673231</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.012180804700151</v>
+        <v>9.01212080803305</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039351794343045</v>
+        <v>9.039374315908717</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.058947594748146</v>
+        <v>9.059015116622573</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060768068950768</v>
+        <v>9.060769532632147</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047763286945251</v>
+        <v>9.047749585260473</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038852836051937</v>
+        <v>9.038812641997367</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046764455326317</v>
+        <v>9.046673372584426</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062690614957351</v>
+        <v>9.062552419591327</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.074982233596112</v>
+        <v>9.074771528188982</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089401877275574</v>
+        <v>9.089236232111398</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.073677139874089</v>
+        <v>9.073396960594753</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056347567290068</v>
+        <v>9.056362370076091</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.044141480507681</v>
+        <v>9.044837996213026</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.044965492924424</v>
+        <v>9.045979635621418</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.044705553005407</v>
+        <v>9.045683086541118</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.039125098199957</v>
+        <v>9.039998968884639</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.03876819016827</v>
+        <v>9.039377368828212</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.028297023096314</v>
+        <v>9.028892128670407</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.036378383580713</v>
+        <v>9.036183326799939</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.040267555976957</v>
+        <v>9.039012371291861</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.059542657895072</v>
+        <v>9.056162782056568</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.085060134750108</v>
+        <v>9.077748673610245</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.041197706275007</v>
+        <v>9.033246133233424</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>9.025687499081368</v>
+        <v>9.011275005932275</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/GBPCNH_forecast.xlsx
+++ b/public/data/files/GBPCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>9.74862024744734</v>
+        <v>9.748627775838305</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>9.723735683321067</v>
+        <v>9.723752235354221</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>9.720659872566173</v>
+        <v>9.720682691944798</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>9.699882143001009</v>
+        <v>9.699918460349625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>9.704398246787152</v>
+        <v>9.704434194124415</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>9.697649793883599</v>
+        <v>9.697685289991899</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>9.693472298153885</v>
+        <v>9.693507969725866</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>9.707520212581795</v>
+        <v>9.707556780412339</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>9.720030406942049</v>
+        <v>9.720073227077886</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>9.726908196521865</v>
+        <v>9.726941238037284</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>9.735558649480236</v>
+        <v>9.735592098293354</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>9.711953065669368</v>
+        <v>9.711985820173588</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>9.667566398405993</v>
+        <v>9.667599232836935</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>9.633379438097824</v>
+        <v>9.633420416161568</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>9.600288013245063</v>
+        <v>9.60031539013313</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>9.56246029934516</v>
+        <v>9.562484223753113</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>9.504348375489226</v>
+        <v>9.504400492923331</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>9.432624007832468</v>
+        <v>9.432696592610315</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>9.356759949265065</v>
+        <v>9.356827755599804</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>9.289273718519478</v>
+        <v>9.289344799099631</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>9.266581048261209</v>
+        <v>9.266629885516199</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>9.279350247694124</v>
+        <v>9.279387391523883</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>9.239276973586156</v>
+        <v>9.239244491943554</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>9.170347405483025</v>
+        <v>9.170279551844729</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>9.106203027494523</v>
+        <v>9.106098539776211</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>9.011865846715503</v>
+        <v>9.011740203346863</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.941074017286164</v>
+        <v>8.940919564766633</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.938001339341415</v>
+        <v>8.937809454791473</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.947643161320464</v>
+        <v>8.947421490149447</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>9.072367075728915</v>
+        <v>9.072057579964898</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>9.126173035158637</v>
+        <v>9.125849489554756</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>9.292136920768989</v>
+        <v>9.291882716600716</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>9.385261077519045</v>
+        <v>9.385062141363665</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>9.404356982955896</v>
+        <v>9.404189141886107</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>9.488121581823588</v>
+        <v>9.487978045553497</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>9.607544757061955</v>
+        <v>9.607587784107515</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>9.599003534676276</v>
+        <v>9.599112398599924</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>9.616823110988097</v>
+        <v>9.61704438527453</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>9.615028543838093</v>
+        <v>9.615396626778153</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>9.596343123564619</v>
+        <v>9.596765434439678</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>9.63189192567161</v>
+        <v>9.632366955747599</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>9.499258140048562</v>
+        <v>9.499679228047544</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>9.431163415088173</v>
+        <v>9.431564537316429</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>9.283264146717826</v>
+        <v>9.283489346758552</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>9.186589749969045</v>
+        <v>9.186732375017447</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>9.076430782665394</v>
+        <v>9.076387911147666</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>9.049235439056638</v>
+        <v>9.049137787557768</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>9.046368757663261</v>
+        <v>9.046290682345209</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>9.020857326986759</v>
+        <v>9.020738460207511</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>9.000544295673231</v>
+        <v>9.0004234421439</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>9.01212080803305</v>
+        <v>9.012061923153922</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>9.039374315908717</v>
+        <v>9.039396284029989</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>9.059015116622573</v>
+        <v>9.059081253001995</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>9.060769532632147</v>
+        <v>9.060771130667474</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>9.047749585260473</v>
+        <v>9.047736244273624</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>9.038812641997367</v>
+        <v>9.038773310279577</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>9.046673372584426</v>
+        <v>9.046584120722809</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>9.062552419591327</v>
+        <v>9.062416893629912</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>9.074771528188982</v>
+        <v>9.074564825945071</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>9.089236232111398</v>
+        <v>9.08907383397456</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>9.073396960594753</v>
+        <v>9.073135576968106</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>9.056362370076091</v>
+        <v>9.056235443844706</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>9.044837996213026</v>
+        <v>9.04504199725883</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>9.045979635621418</v>
+        <v>9.045883602366183</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>9.045683086541118</v>
+        <v>9.045567027057766</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>9.039998968884639</v>
+        <v>9.040034208037754</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>9.039377368828212</v>
+        <v>9.039571500646911</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>9.028892128670407</v>
+        <v>9.029522142268695</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>9.036183326799939</v>
+        <v>9.036397305382522</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>9.039012371291861</v>
+        <v>9.038186095079737</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>9.056162782056568</v>
+        <v>9.052888751432723</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>9.077748673610245</v>
+        <v>9.070232417937531</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>9.033246133233424</v>
+        <v>9.024285654891738</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>9.011275005932275</v>
+        <v>8.996708320824576</v>
       </c>
     </row>
   </sheetData>
